--- a/results/cuda_performance.xlsx
+++ b/results/cuda_performance.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ncu metrics" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="RTX 3090" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RTX 4090" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ncu metrics (RTX 3090)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ncu metrics (RTX 4090)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -100,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -139,10 +141,14 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -529,14 +535,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CUDA performance results (latest runs)</t>
+          <t>CUDA performance results (latest runs): RTX 3090</t>
         </is>
       </c>
     </row>
     <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB). Times in microseconds (lower is better). Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so ncu kernel times barely change with launch mode; the CUDA Graph benefit (launch overhead) shows in end-to-end rows.</t>
+          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB), binaries built with CUDA 13.3 GPU (outputs in rtx3090/). Times in microseconds (lower is better). Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so ncu kernel times barely change with launch mode; the CUDA Graph benefit (launch overhead) shows in end-to-end rows.</t>
         </is>
       </c>
     </row>
@@ -1347,6 +1353,813 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CUDA performance results (latest runs): RTX 4090</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="45" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>GPU: NVIDIA GeForce RTX 4090 (sm_89, 24 GB), binaries built with CUDA 12.5 GPU (outputs in rtx4090/). Times in microseconds (lower is better). Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so ncu kernel times barely change with launch mode; the CUDA Graph benefit (launch overhead) shows in end-to-end rows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Workload</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Kernel / stage</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Problem size</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GPU</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>CUDA Graph</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Direct launch (no graph)</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="n"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Graph speedup
+(Direct / Graph)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n"/>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Time (us)</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>ncu-rep</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>nsys sqlite</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Time (us)</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>ncu-rep</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>nsys sqlite</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>llama2c (coalesced matmul)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>matmul_coalesced_kernel</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>batch=1024, dim=16384, rows=8192</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>nsys-node-graph-20261015-091930.sqlite</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>nsys-node-direct-20261015-091935.sqlite</t>
+        </is>
+      </c>
+      <c r="L6" s="10">
+        <f>IF(AND(ISNUMBER(F6),ISNUMBER(I6)),I6/F6,"")</f>
+        <v/>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Largest kernel. It is a matrix-vector product, so its time does not grow with batch; the three kernels run concurrently on separate streams, so their times overlap. </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>llama2c (coalesced matmul)</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (rmsnorm + softmax + matmul iteration)</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>batch=1024, dim=16384, rows=8192</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Iteration time (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>962.42</v>
+      </c>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>nsys-node-graph-20261015-091930.sqlite</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>963.302</v>
+      </c>
+      <c r="J7" s="12" t="n"/>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>nsys-node-direct-20261015-091935.sqlite</t>
+        </is>
+      </c>
+      <c r="L7" s="10">
+        <f>IF(AND(ISNUMBER(F7),ISNUMBER(I7)),I7/F7,"")</f>
+        <v/>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Mean of 3 interleaved trials from the GPU-filling sweep; no per-iteration copies. The nsys traces rerun this configuration (963.0 / 962.1 us per iteration).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>loom_msa (multi-sensor attention)</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>fuse_attention_kernel</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>25,000 queries x 250,000 context</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
+        </is>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="10">
+        <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9)),I9/F9,"")</f>
+        <v/>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). </t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>loom_msa (multi-sensor attention)</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (graph replay)</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>25,000 queries x 250,000 context</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Replay time (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>3835.57</v>
+      </c>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
+        </is>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="10">
+        <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10)),I10/F10,"")</f>
+        <v/>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>benchmark.py: median of 5 runs, random inputs. Includes H2D input and D2H output copies.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>pagerank (GAPBS)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>pagerank_update (one iteration)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>nsys-20261015-091708.sqlite</t>
+        </is>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="10">
+        <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12)),I12/F12,"")</f>
+        <v/>
+      </c>
+      <c r="M12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks. </t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>pagerank (GAPBS)</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (graph replay: H2D + 20 iterations)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Replay time (nsys)</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>5754.945</v>
+      </c>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>nsys-20261015-091708.sqlite</t>
+        </is>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="10">
+        <f>IF(AND(ISNUMBER(F13),ISNUMBER(I13)),I13/F13,"")</f>
+        <v/>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>Median span of the 1693 replays with transfers in the nsys node trace. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny anomaly</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>mse_partial_kernel</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>64M elements</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
+        </is>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J15" s="12" t="n"/>
+      <c r="K15" s="12" t="n"/>
+      <c r="L15" s="10">
+        <f>IF(AND(ISNUMBER(F15),ISNUMBER(I15)),I15/F15,"")</f>
+        <v/>
+      </c>
+      <c r="M15" s="5" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny anomaly</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>64M elements</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>Replay time (nsys)</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>13698.465</v>
+      </c>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
+        </is>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="10">
+        <f>IF(AND(ISNUMBER(F16),ISNUMBER(I16)),I16/F16,"")</f>
+        <v/>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>kws_postprocess_kernel</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 4M rows</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+        </is>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="10">
+        <f>IF(AND(ISNUMBER(F18),ISNUMBER(I18)),I18/F18,"")</f>
+        <v/>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only kernel in the application. </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 4M rows</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Replay time (nsys)</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>11226.082</v>
+      </c>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+        </is>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="10">
+        <f>IF(AND(ISNUMBER(F19),ISNUMBER(I19)),I19/F19,"")</f>
+        <v/>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>vww_preprocess_kernel</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu)</t>
+        </is>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
+        </is>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="10">
+        <f>IF(AND(ISNUMBER(F21),ISNUMBER(I21)),I21/F21,"")</f>
+        <v/>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Only kernel in the application. </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>Replay time (nsys)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>21789.123</v>
+      </c>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
+        </is>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>n/a (graph-only harness)</t>
+        </is>
+      </c>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="10">
+        <f>IF(AND(ISNUMBER(F22),ISNUMBER(I22)),I22/F22,"")</f>
+        <v/>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="M4:M5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A2:M2"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1368,84 +2181,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>ncu report</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Launch #</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>SM throughput %</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="15" t="inlineStr">
         <is>
           <t>Memory throughput %</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="15" t="inlineStr">
         <is>
           <t>DRAM throughput %</t>
         </is>
       </c>
-      <c r="H1" s="14" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Achieved occupancy %</t>
         </is>
       </c>
-      <c r="I1" s="14" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Theoretical occupancy %</t>
         </is>
       </c>
-      <c r="J1" s="14" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Registers / thread</t>
         </is>
       </c>
-      <c r="K1" s="14" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Grid</t>
         </is>
       </c>
-      <c r="L1" s="14" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="M1" s="14" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Waves / SM</t>
         </is>
       </c>
-      <c r="N1" s="14" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>DRAM read</t>
         </is>
       </c>
-      <c r="O1" s="14" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>DRAM write</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1496,7 +2309,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1547,7 +2360,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1598,7 +2411,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1649,7 +2462,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1700,7 +2513,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1751,7 +2564,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1802,7 +2615,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1853,7 +2666,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -1904,7 +2717,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -1955,7 +2768,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2006,7 +2819,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2057,7 +2870,7 @@
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2108,7 +2921,7 @@
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2159,7 +2972,7 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2210,7 +3023,7 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2261,7 +3074,7 @@
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2312,7 +3125,7 @@
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2363,7 +3176,7 @@
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -2414,7 +3227,7 @@
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -2465,7 +3278,7 @@
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -2516,7 +3329,7 @@
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -2567,7 +3380,7 @@
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2626,7 +3439,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2685,7 +3498,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2744,7 +3557,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2803,7 +3616,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2862,7 +3675,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2921,7 +3734,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -2980,7 +3793,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3039,7 +3852,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3098,7 +3911,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3157,7 +3970,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3216,7 +4029,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3275,7 +4088,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="15" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3334,7 +4147,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3393,7 +4206,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3452,7 +4265,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3511,7 +4324,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3570,7 +4383,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="A41" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3629,7 +4442,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3688,7 +4501,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3747,7 +4560,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3806,7 +4619,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3865,7 +4678,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3924,7 +4737,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3983,7 +4796,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4042,7 +4855,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4101,7 +4914,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4160,7 +4973,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4219,7 +5032,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
         </is>
@@ -4278,7 +5091,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
         </is>
@@ -4337,7 +5150,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="15" t="inlineStr">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>ncu-kws_postprocess-20261007-144950.ncu-rep</t>
         </is>
@@ -4396,7 +5209,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="15" t="inlineStr">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>ncu-vww_preprocess-20261007-144958.ncu-rep</t>
         </is>
@@ -4513,4 +5326,119 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="15" t="inlineStr">
+        <is>
+          <t>ncu report</t>
+        </is>
+      </c>
+      <c r="B1" s="15" t="inlineStr">
+        <is>
+          <t>Launch #</t>
+        </is>
+      </c>
+      <c r="C1" s="15" t="inlineStr">
+        <is>
+          <t>Kernel</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Duration</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>SM throughput %</t>
+        </is>
+      </c>
+      <c r="F1" s="15" t="inlineStr">
+        <is>
+          <t>Memory throughput %</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>DRAM throughput %</t>
+        </is>
+      </c>
+      <c r="H1" s="15" t="inlineStr">
+        <is>
+          <t>Achieved occupancy %</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Theoretical occupancy %</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>Registers / thread</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>Grid</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>Block</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>Waves / SM</t>
+        </is>
+      </c>
+      <c r="N1" s="15" t="inlineStr">
+        <is>
+          <t>DRAM read</t>
+        </is>
+      </c>
+      <c r="O1" s="15" t="inlineStr">
+        <is>
+          <t>DRAM write</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/results/cuda_performance.xlsx
+++ b/results/cuda_performance.xlsx
@@ -102,7 +102,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,6 +142,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -223,6 +227,76 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>build_spreadsheet.py</author>
+  </authors>
+  <commentList>
+    <comment ref="L6" authorId="0" shapeId="0">
+      <text>
+        <t>DRAM-bound (DRAM 94% busy; SM 5%, L1/L2 94%): data rate 21 / 18.98 Gbps = 1.11x.</t>
+      </text>
+    </comment>
+    <comment ref="L7" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels overlap (their summed ncu time is 105% of this time), so all of it scales with the kernels' 1.11x.</t>
+      </text>
+    </comment>
+    <comment ref="L9" authorId="0" shapeId="0">
+      <text>
+        <t>SM-bound (SM 81% busy; L1/L2 39%, DRAM 0%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
+      </text>
+    </comment>
+    <comment ref="L10" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels are 94% of the RTX 3090 time and predicted 2.29x faster; the other 6% (copies, gaps) is unchanged.</t>
+      </text>
+    </comment>
+    <comment ref="L12" authorId="0" shapeId="0">
+      <text>
+        <t>L1/L2-bound (L1/L2 96% busy; SM 7%, DRAM 38%): assumed to scale with SMs x clock, 2.32x.</t>
+      </text>
+    </comment>
+    <comment ref="L13" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels are 70% of the RTX 3090 time and predicted 2.28x faster; the other 30% (copies, gaps) is unchanged.</t>
+      </text>
+    </comment>
+    <comment ref="L15" authorId="0" shapeId="0">
+      <text>
+        <t>DRAM-bound (DRAM 96% busy; SM 10%, L1/L2 96%): data rate 21 / 18.98 Gbps = 1.11x.</t>
+      </text>
+    </comment>
+    <comment ref="L16" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
+      </text>
+    </comment>
+    <comment ref="L18" authorId="0" shapeId="0">
+      <text>
+        <t>SM-bound (SM 81% busy; L1/L2 76%, DRAM 26%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.32x.</t>
+      </text>
+    </comment>
+    <comment ref="L19" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels are 10% of the RTX 3090 time and predicted 2.32x faster; the other 90% (copies, gaps) is unchanged.</t>
+      </text>
+    </comment>
+    <comment ref="L21" authorId="0" shapeId="0">
+      <text>
+        <t>DRAM-bound (DRAM 88% busy; SM 3%, L1/L2 88%): data rate 21 / 18.98 Gbps = 1.11x.</t>
+      </text>
+    </comment>
+    <comment ref="L22" authorId="0" shapeId="0">
+      <text>
+        <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1353,7 +1427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1367,8 +1441,9 @@
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1427,11 +1502,11 @@
       <c r="K4" s="3" t="n"/>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Graph speedup
-(Direct / Graph)</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
+          <t>Speedup vs RTX 3090 (CUDA Graph time)</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -1473,8 +1548,18 @@
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n"/>
-      <c r="M5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Predicted</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Measured
+(RTX 3090 / RTX 4090)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1524,11 +1609,14 @@
           <t>nsys-node-direct-20261015-091935.sqlite</t>
         </is>
       </c>
-      <c r="L6" s="10">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER(I6)),I6/F6,"")</f>
+      <c r="L6" s="10" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="M6" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F6),ISNUMBER(F6)),'RTX 3090'!F6/F6,"pending")</f>
         <v/>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Largest kernel. It is a matrix-vector product, so its time does not grow with batch; the three kernels run concurrently on separate streams, so their times overlap. </t>
         </is>
@@ -1578,11 +1666,14 @@
           <t>nsys-node-direct-20261015-091935.sqlite</t>
         </is>
       </c>
-      <c r="L7" s="10">
-        <f>IF(AND(ISNUMBER(F7),ISNUMBER(I7)),I7/F7,"")</f>
+      <c r="L7" s="10" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="M7" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F7),ISNUMBER(F7)),'RTX 3090'!F7/F7,"pending")</f>
         <v/>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Mean of 3 interleaved trials from the GPU-filling sweep; no per-iteration copies. The nsys traces rerun this configuration (963.0 / 962.1 us per iteration).</t>
         </is>
@@ -1632,11 +1723,14 @@
       </c>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
-      <c r="L9" s="10">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9)),I9/F9,"")</f>
+      <c r="L9" s="10" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="M9" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F9),ISNUMBER(F9)),'RTX 3090'!F9/F9,"pending")</f>
         <v/>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). </t>
         </is>
@@ -1684,11 +1778,14 @@
       </c>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
-      <c r="L10" s="10">
-        <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10)),I10/F10,"")</f>
+      <c r="L10" s="10" t="n">
+        <v>2.137</v>
+      </c>
+      <c r="M10" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F10),ISNUMBER(F10)),'RTX 3090'!F10/F10,"pending")</f>
         <v/>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>benchmark.py: median of 5 runs, random inputs. Includes H2D input and D2H output copies.</t>
         </is>
@@ -1738,11 +1835,14 @@
       </c>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
-      <c r="L12" s="10">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12)),I12/F12,"")</f>
+      <c r="L12" s="10" t="n">
+        <v>2.323</v>
+      </c>
+      <c r="M12" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F12),ISNUMBER(F12)),'RTX 3090'!F12/F12,"pending")</f>
         <v/>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks. </t>
         </is>
@@ -1790,11 +1890,14 @@
       </c>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
-      <c r="L13" s="10">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER(I13)),I13/F13,"")</f>
+      <c r="L13" s="10" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="M13" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F13),ISNUMBER(F13)),'RTX 3090'!F13/F13,"pending")</f>
         <v/>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Median span of the 1693 replays with transfers in the nsys node trace. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
         </is>
@@ -1844,11 +1947,14 @@
       </c>
       <c r="J15" s="12" t="n"/>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="10">
-        <f>IF(AND(ISNUMBER(F15),ISNUMBER(I15)),I15/F15,"")</f>
+      <c r="L15" s="10" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="M15" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F15),ISNUMBER(F15)),'RTX 3090'!F15/F15,"pending")</f>
         <v/>
       </c>
-      <c r="M15" s="5" t="inlineStr"/>
+      <c r="N15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1892,11 +1998,14 @@
       </c>
       <c r="J16" s="12" t="n"/>
       <c r="K16" s="12" t="n"/>
-      <c r="L16" s="10">
-        <f>IF(AND(ISNUMBER(F16),ISNUMBER(I16)),I16/F16,"")</f>
+      <c r="L16" s="10" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="M16" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F16),ISNUMBER(F16)),'RTX 3090'!F16/F16,"pending")</f>
         <v/>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
         </is>
@@ -1946,11 +2055,14 @@
       </c>
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
-      <c r="L18" s="10">
-        <f>IF(AND(ISNUMBER(F18),ISNUMBER(I18)),I18/F18,"")</f>
+      <c r="L18" s="10" t="n">
+        <v>2.322</v>
+      </c>
+      <c r="M18" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F18),ISNUMBER(F18)),'RTX 3090'!F18/F18,"pending")</f>
         <v/>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Only kernel in the application. </t>
         </is>
@@ -1998,11 +2110,14 @@
       </c>
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
-      <c r="L19" s="10">
-        <f>IF(AND(ISNUMBER(F19),ISNUMBER(I19)),I19/F19,"")</f>
+      <c r="L19" s="10" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="M19" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F19),ISNUMBER(F19)),'RTX 3090'!F19/F19,"pending")</f>
         <v/>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
         </is>
@@ -2052,11 +2167,14 @@
       </c>
       <c r="J21" s="12" t="n"/>
       <c r="K21" s="12" t="n"/>
-      <c r="L21" s="10">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER(I21)),I21/F21,"")</f>
+      <c r="L21" s="10" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="M21" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F21),ISNUMBER(F21)),'RTX 3090'!F21/F21,"pending")</f>
         <v/>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Only kernel in the application. </t>
         </is>
@@ -2104,27 +2222,69 @@
       </c>
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
-      <c r="L22" s="10">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER(I22)),I22/F22,"")</f>
+      <c r="L22" s="10" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="M22" s="10">
+        <f>IF(AND(ISNUMBER('RTX 3090'!F22),ISNUMBER(F22)),'RTX 3090'!F22/F22,"pending")</f>
         <v/>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>How the predicted speedup is calculated (hover a Predicted value for that row's reason)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="48" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>The predicted speedup uses only the RTX 3090's ncu reports and the two GPUs' published specs (RTX 3090: 82 SMs, 1.695 GHz boost, 19.5 Gbps GDDR6X; RTX 4090: 128 SMs, 2.52 GHz boost, 21 Gbps GDDR6X; both 384-bit, PCIe 4.0 x16), so it is fixed before any 4090 measurement. Each unit's peak scales by its hardware ratio: SM compute by SMs x SM clock, L1/L2 cache throughput assumed to scale the same way, DRAM by memory data rate (the 3090's own SM and memory clocks come from its ncu report: 1.69 GHz and 18.98 Gbps, so the ratios are about 2.32x and 1.11x).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="48" customHeight="1">
+      <c r="A26" s="16" t="inlineStr">
+        <is>
+          <t>Kernel rows: ncu gives each launch's SM, memory (L1/L2) and DRAM throughput as a percent of the 3090's peak. Keeping the work per unit fixed, a unit at u% that is r times faster needs u/r% of the old time, and the slowest unit sets the new time: speedup = max(u) / max(u / r). So a DRAM-bound kernel gets ~1.11x and a compute- or cache-bound one ~2.32x. A launch below 60% on every unit is latency-bound and gets the SM clock ratio (1.49x). A kernel with several launches combines them weighted by time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="48" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Whole-application rows: the kernels in that workload's ncu report (one run of the application) scale by their predicted speedups; the rest of the 3090 time (H2D/D2H copies over the same PCIe 4.0 link, launch gaps) is assumed unchanged. Where the kernels overlap (llama2c's three streams; their summed time exceeds the iteration time), the whole time scales with the kernels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="48" customHeight="1">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Not modelled: cache capacity (the 4090's L2 is 72 MB vs 6 MB, so data that spilled to DRAM on the 3090 can stay in L2), kernels overlapping copies (pagerank's first iteration), clocks above rated boost, and compiler differences (CUDA 13.3 vs 12.5). Measured = 3090 time / 4090 time for the CUDA Graph column; kernel rows read pending until the 4090 ncu reports exist.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="M4:M5"/>
+  <mergeCells count="14">
+    <mergeCell ref="A27:N27"/>
     <mergeCell ref="B4:B5"/>
+    <mergeCell ref="L4:M4"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A26:N26"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="E4:E5"/>
-    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="N4:N5"/>
+    <mergeCell ref="A25:N25"/>
     <mergeCell ref="F4:H4"/>
     <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A28:N28"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <hyperlinks>
@@ -2151,6 +2311,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -2181,84 +2342,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>ncu report</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Launch #</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>SM throughput %</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Memory throughput %</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>DRAM throughput %</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Achieved occupancy %</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>Theoretical occupancy %</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Registers / thread</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="17" t="inlineStr">
         <is>
           <t>Grid</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="17" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="17" t="inlineStr">
         <is>
           <t>Waves / SM</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
+      <c r="N1" s="17" t="inlineStr">
         <is>
           <t>DRAM read</t>
         </is>
       </c>
-      <c r="O1" s="15" t="inlineStr">
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>DRAM write</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="16" t="inlineStr">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2309,7 +2470,7 @@
       <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2360,7 +2521,7 @@
       <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2411,7 +2572,7 @@
       <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2462,7 +2623,7 @@
       <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2513,7 +2674,7 @@
       <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2564,7 +2725,7 @@
       <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2615,7 +2776,7 @@
       <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2666,7 +2827,7 @@
       <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
@@ -2717,7 +2878,7 @@
       <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2768,7 +2929,7 @@
       <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2819,7 +2980,7 @@
       <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2870,7 +3031,7 @@
       <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2921,7 +3082,7 @@
       <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -2972,7 +3133,7 @@
       <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -3023,7 +3184,7 @@
       <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -3074,7 +3235,7 @@
       <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -3125,7 +3286,7 @@
       <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
@@ -3176,7 +3337,7 @@
       <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -3227,7 +3388,7 @@
       <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -3278,7 +3439,7 @@
       <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="16" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -3329,7 +3490,7 @@
       <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
         </is>
@@ -3380,7 +3541,7 @@
       <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3439,7 +3600,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3498,7 +3659,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3557,7 +3718,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3616,7 +3777,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3675,7 +3836,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
+      <c r="A29" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3734,7 +3895,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3793,7 +3954,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3852,7 +4013,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3911,7 +4072,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="16" t="inlineStr">
+      <c r="A33" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -3970,7 +4131,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="16" t="inlineStr">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4029,7 +4190,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="16" t="inlineStr">
+      <c r="A35" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4088,7 +4249,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4147,7 +4308,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4206,7 +4367,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4265,7 +4426,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
+      <c r="A39" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4324,7 +4485,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
+      <c r="A40" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4383,7 +4544,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
+      <c r="A41" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4442,7 +4603,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4501,7 +4662,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+      <c r="A43" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4560,7 +4721,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="16" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4619,7 +4780,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="16" t="inlineStr">
+      <c r="A45" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4678,7 +4839,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="16" t="inlineStr">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4737,7 +4898,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="16" t="inlineStr">
+      <c r="A47" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4796,7 +4957,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="16" t="inlineStr">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4855,7 +5016,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="16" t="inlineStr">
+      <c r="A49" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4914,7 +5075,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="16" t="inlineStr">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -4973,7 +5134,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="16" t="inlineStr">
+      <c r="A51" s="18" t="inlineStr">
         <is>
           <t>ncu-pagerank-20261007-152417.ncu-rep</t>
         </is>
@@ -5032,7 +5193,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="16" t="inlineStr">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
         </is>
@@ -5091,7 +5252,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="16" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
         </is>
@@ -5150,7 +5311,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="16" t="inlineStr">
+      <c r="A54" s="18" t="inlineStr">
         <is>
           <t>ncu-kws_postprocess-20261007-144950.ncu-rep</t>
         </is>
@@ -5209,7 +5370,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="16" t="inlineStr">
+      <c r="A55" s="18" t="inlineStr">
         <is>
           <t>ncu-vww_preprocess-20261007-144958.ncu-rep</t>
         </is>
@@ -5355,84 +5516,84 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>ncu report</t>
         </is>
       </c>
-      <c r="B1" s="15" t="inlineStr">
+      <c r="B1" s="17" t="inlineStr">
         <is>
           <t>Launch #</t>
         </is>
       </c>
-      <c r="C1" s="15" t="inlineStr">
+      <c r="C1" s="17" t="inlineStr">
         <is>
           <t>Kernel</t>
         </is>
       </c>
-      <c r="D1" s="15" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>Duration</t>
         </is>
       </c>
-      <c r="E1" s="15" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>SM throughput %</t>
         </is>
       </c>
-      <c r="F1" s="15" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Memory throughput %</t>
         </is>
       </c>
-      <c r="G1" s="15" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>DRAM throughput %</t>
         </is>
       </c>
-      <c r="H1" s="15" t="inlineStr">
+      <c r="H1" s="17" t="inlineStr">
         <is>
           <t>Achieved occupancy %</t>
         </is>
       </c>
-      <c r="I1" s="15" t="inlineStr">
+      <c r="I1" s="17" t="inlineStr">
         <is>
           <t>Theoretical occupancy %</t>
         </is>
       </c>
-      <c r="J1" s="15" t="inlineStr">
+      <c r="J1" s="17" t="inlineStr">
         <is>
           <t>Registers / thread</t>
         </is>
       </c>
-      <c r="K1" s="15" t="inlineStr">
+      <c r="K1" s="17" t="inlineStr">
         <is>
           <t>Grid</t>
         </is>
       </c>
-      <c r="L1" s="15" t="inlineStr">
+      <c r="L1" s="17" t="inlineStr">
         <is>
           <t>Block</t>
         </is>
       </c>
-      <c r="M1" s="15" t="inlineStr">
+      <c r="M1" s="17" t="inlineStr">
         <is>
           <t>Waves / SM</t>
         </is>
       </c>
-      <c r="N1" s="15" t="inlineStr">
+      <c r="N1" s="17" t="inlineStr">
         <is>
           <t>DRAM read</t>
         </is>
       </c>
-      <c r="O1" s="15" t="inlineStr">
+      <c r="O1" s="17" t="inlineStr">
         <is>
           <t>DRAM write</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>

--- a/results/cuda_performance.xlsx
+++ b/results/cuda_performance.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="RTX 3090" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="RTX 4090" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ncu metrics (RTX 3090)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ncu metrics (RTX 4090)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTX 3090" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTX 4090" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ncu metrics (RTX 3090)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ncu metrics (RTX 4090)" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -138,10 +138,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -247,12 +247,12 @@
     </comment>
     <comment ref="L9" authorId="0" shapeId="0">
       <text>
-        <t>SM-bound (SM 81% busy; L1/L2 39%, DRAM 0%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
+        <t>SM-bound (SM 80% busy; L1/L2 39%, DRAM 0%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
     <comment ref="L10" authorId="0" shapeId="0">
       <text>
-        <t>Kernels are 94% of the RTX 3090 time and predicted 2.29x faster; the other 6% (copies, gaps) is unchanged.</t>
+        <t>Kernels are 95% of the RTX 3090 time and predicted 2.29x faster; the other 5% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
     <comment ref="L12" authorId="0" shapeId="0">
@@ -262,7 +262,7 @@
     </comment>
     <comment ref="L13" authorId="0" shapeId="0">
       <text>
-        <t>Kernels are 70% of the RTX 3090 time and predicted 2.28x faster; the other 30% (copies, gaps) is unchanged.</t>
+        <t>Kernels are 70% of the RTX 3090 time and predicted 2.29x faster; the other 30% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
     <comment ref="L15" authorId="0" shapeId="0">
@@ -277,12 +277,12 @@
     </comment>
     <comment ref="L18" authorId="0" shapeId="0">
       <text>
-        <t>SM-bound (SM 81% busy; L1/L2 76%, DRAM 26%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.32x.</t>
+        <t>SM-bound (SM 81% busy; L1/L2 76%, DRAM 26%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
     <comment ref="L19" authorId="0" shapeId="0">
       <text>
-        <t>Kernels are 10% of the RTX 3090 time and predicted 2.32x faster; the other 90% (copies, gaps) is unchanged.</t>
+        <t>Kernels are 10% of the RTX 3090 time and predicted 2.33x faster; the other 90% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
     <comment ref="L21" authorId="0" shapeId="0">
@@ -854,25 +854,31 @@
         </is>
       </c>
       <c r="F9" s="6" t="n">
-        <v>8154.912</v>
+        <v>8174.304</v>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>nsys-msa_optimized_large-20260925-142045.sqlite</t>
-        </is>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
+          <t>nsys-msa_optimized_large-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>8174.176</v>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>nsys-msa_optimized_large-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L9" s="10">
         <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9)),I9/F9,"")</f>
         <v/>
@@ -891,7 +897,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -906,32 +912,34 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Replay time (cudaEvent)</t>
+          <t>Iteration time (cudaEvent)</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
-        <v>8870.139999999999</v>
+        <v>8885.450000000001</v>
       </c>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>nsys-msa_optimized_large-20260925-142045.sqlite</t>
-        </is>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
+          <t>nsys-msa_optimized_large-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="n">
+        <v>8889.35</v>
       </c>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="12" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>nsys-msa_optimized_large-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L10" s="10">
         <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10)),I10/F10,"")</f>
         <v/>
       </c>
       <c r="M10" s="5" t="inlineStr">
         <is>
-          <t>benchmark.py: median of 5 runs, random inputs. Includes H2D input and D2H output copies.</t>
+          <t>benchmark.py: median of 5 runs, random inputs, both launch modes. Includes H2D input and D2H output copies.</t>
         </is>
       </c>
     </row>
@@ -962,25 +970,31 @@
         </is>
       </c>
       <c r="F12" s="6" t="n">
-        <v>262.784</v>
+        <v>262.754</v>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>nsys-20261007-152346.sqlite</t>
-        </is>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
-      </c>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
+          <t>nsys-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>262.621</v>
+      </c>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>nsys-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L12" s="10">
         <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12)),I12/F12,"")</f>
         <v/>
@@ -999,7 +1013,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + 20 iterations)</t>
+          <t>Whole application (H2D + 20 iterations + D2H)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1014,32 +1028,34 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
-        <v>7670.435</v>
+        <v>7648.935</v>
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>nsys-20261007-152346.sqlite</t>
-        </is>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
+          <t>nsys-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>7678.598</v>
       </c>
       <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>nsys-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L13" s="10">
         <f>IF(AND(ISNUMBER(F13),ISNUMBER(I13)),I13/F13,"")</f>
         <v/>
       </c>
       <c r="M13" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 1296 replays with transfers in the nsys node trace. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. The binary's own cudaEvent timing in the same run: 7.684 ms with transfers, 4.841 ms compute only.</t>
+          <t>Median GPU span of the 1292 / 1251 (graph / direct) pagerank.full NVTX ranges in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. The binary's own cudaEvent timing in the same runs: 7.658 / 7.686 ms (graph / direct) with transfers, 4.862 / 4.885 ms compute only.</t>
         </is>
       </c>
     </row>
@@ -1070,25 +1086,31 @@
         </is>
       </c>
       <c r="F15" s="6" t="n">
-        <v>385.248</v>
+        <v>384.288</v>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>nsys-anomaly_mse-20261007-144939.sqlite</t>
-        </is>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
-      </c>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
+          <t>nsys-anomaly_mse-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>nsys-anomaly_mse-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L15" s="10">
         <f>IF(AND(ISNUMBER(F15),ISNUMBER(I15)),I15/F15,"")</f>
         <v/>
@@ -1107,7 +1129,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1122,32 +1144,34 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
-        <v>14194.555</v>
+        <v>14200.376</v>
       </c>
       <c r="G16" s="11" t="n"/>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>nsys-anomaly_mse-20261007-144939.sqlite</t>
-        </is>
-      </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
+          <t>nsys-anomaly_mse-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I16" s="8" t="n">
+        <v>14212.283</v>
       </c>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>nsys-anomaly_mse-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L16" s="10">
         <f>IF(AND(ISNUMBER(F16),ISNUMBER(I16)),I16/F16,"")</f>
         <v/>
       </c>
       <c r="M16" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 20 / 20 (graph / direct) anomaly.end_to_end NVTX ranges in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -1178,25 +1202,31 @@
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>1118.784</v>
+        <v>1120.224</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-20261007-144950.ncu-rep</t>
+          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>nsys-kws_postprocess-20261007-144947.sqlite</t>
-        </is>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
-      </c>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
+          <t>nsys-kws_postprocess-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>1119.968</v>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>nsys-kws_postprocess-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L18" s="10">
         <f>IF(AND(ISNUMBER(F18),ISNUMBER(I18)),I18/F18,"")</f>
         <v/>
@@ -1215,7 +1245,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1230,32 +1260,34 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>11451.737</v>
+        <v>11451.704</v>
       </c>
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>nsys-kws_postprocess-20261007-144947.sqlite</t>
-        </is>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
+          <t>nsys-kws_postprocess-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>11446.14</v>
       </c>
       <c r="J19" s="12" t="n"/>
-      <c r="K19" s="12" t="n"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>nsys-kws_postprocess-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L19" s="10">
         <f>IF(AND(ISNUMBER(F19),ISNUMBER(I19)),I19/F19,"")</f>
         <v/>
       </c>
       <c r="M19" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 20 / 20 (graph / direct) kws.end_to_end NVTX ranges in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -1286,25 +1318,31 @@
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>665.984</v>
+        <v>664.96</v>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>ncu-vww_preprocess-20261007-144958.ncu-rep</t>
+          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>nsys-vww_preprocess-20261007-144953.sqlite</t>
-        </is>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
-      </c>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
+          <t>nsys-vww_preprocess-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>659.456</v>
+      </c>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L21" s="10">
         <f>IF(AND(ISNUMBER(F21),ISNUMBER(I21)),I21/F21,"")</f>
         <v/>
@@ -1323,7 +1361,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1338,32 +1376,34 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
-        <v>21886.776</v>
+        <v>21910.811</v>
       </c>
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>nsys-vww_preprocess-20261007-144953.sqlite</t>
-        </is>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
-        </is>
+          <t>nsys-vww_preprocess-graph-20261015-224015.sqlite</t>
+        </is>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>21886.066</v>
       </c>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="12" t="n"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-direct-20261015-224015.sqlite</t>
+        </is>
+      </c>
       <c r="L22" s="10">
         <f>IF(AND(ISNUMBER(F22),ISNUMBER(I22)),I22/F22,"")</f>
         <v/>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 20 / 20 (graph / direct) vww.end_to_end NVTX ranges in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -1394,28 +1434,53 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId60"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1587,7 +1652,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -1598,7 +1663,7 @@
           <t>nsys-node-graph-20261015-091930.sqlite</t>
         </is>
       </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -1705,7 +1770,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -1716,15 +1781,15 @@
           <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
         </is>
       </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I9" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J9" s="12" t="n"/>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="10" t="n">
-        <v>2.325</v>
+        <v>2.327</v>
       </c>
       <c r="M9" s="10">
         <f>IF(AND(ISNUMBER('RTX 3090'!F9),ISNUMBER(F9)),'RTX 3090'!F9/F9,"pending")</f>
@@ -1744,7 +1809,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1759,7 +1824,7 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Replay time (cudaEvent)</t>
+          <t>Iteration time (cudaEvent)</t>
         </is>
       </c>
       <c r="F10" s="6" t="n">
@@ -1771,15 +1836,15 @@
           <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
         </is>
       </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I10" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J10" s="12" t="n"/>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="10" t="n">
-        <v>2.137</v>
+        <v>2.14</v>
       </c>
       <c r="M10" s="10">
         <f>IF(AND(ISNUMBER('RTX 3090'!F10),ISNUMBER(F10)),'RTX 3090'!F10/F10,"pending")</f>
@@ -1787,7 +1852,7 @@
       </c>
       <c r="N10" s="5" t="inlineStr">
         <is>
-          <t>benchmark.py: median of 5 runs, random inputs. Includes H2D input and D2H output copies.</t>
+          <t>benchmark.py: median of 5 runs, random inputs, CUDA graph only. Includes H2D input and D2H output copies.</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1882,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -1828,15 +1893,15 @@
           <t>nsys-20261015-091708.sqlite</t>
         </is>
       </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J12" s="12" t="n"/>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="10" t="n">
-        <v>2.323</v>
+        <v>2.325</v>
       </c>
       <c r="M12" s="10">
         <f>IF(AND(ISNUMBER('RTX 3090'!F12),ISNUMBER(F12)),'RTX 3090'!F12/F12,"pending")</f>
@@ -1856,7 +1921,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + 20 iterations)</t>
+          <t>Whole application (H2D + 20 iterations + D2H)</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -1871,7 +1936,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -1883,15 +1948,15 @@
           <t>nsys-20261015-091708.sqlite</t>
         </is>
       </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="10" t="n">
-        <v>1.644</v>
+        <v>1.647</v>
       </c>
       <c r="M13" s="10">
         <f>IF(AND(ISNUMBER('RTX 3090'!F13),ISNUMBER(F13)),'RTX 3090'!F13/F13,"pending")</f>
@@ -1899,7 +1964,7 @@
       </c>
       <c r="N13" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 1693 replays with transfers in the nsys node trace. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
+          <t>Median GPU span of the 1693 graph replays with copies in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
         </is>
       </c>
     </row>
@@ -1929,7 +1994,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -1940,9 +2005,9 @@
           <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I15" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J15" s="12" t="n"/>
@@ -1964,7 +2029,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1979,7 +2044,7 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F16" s="6" t="n">
@@ -1991,9 +2056,9 @@
           <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I16" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J16" s="12" t="n"/>
@@ -2007,7 +2072,7 @@
       </c>
       <c r="N16" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -2037,7 +2102,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -2048,15 +2113,15 @@
           <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
         </is>
       </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I18" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J18" s="12" t="n"/>
       <c r="K18" s="12" t="n"/>
       <c r="L18" s="10" t="n">
-        <v>2.322</v>
+        <v>2.325</v>
       </c>
       <c r="M18" s="10">
         <f>IF(AND(ISNUMBER('RTX 3090'!F18),ISNUMBER(F18)),'RTX 3090'!F18/F18,"pending")</f>
@@ -2076,7 +2141,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2091,7 +2156,7 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
@@ -2103,9 +2168,9 @@
           <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
         </is>
       </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I19" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J19" s="12" t="n"/>
@@ -2119,7 +2184,7 @@
       </c>
       <c r="N19" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2214,7 @@
           <t>Kernel time (ncu)</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
@@ -2160,9 +2225,9 @@
           <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
         </is>
       </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I21" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J21" s="12" t="n"/>
@@ -2188,7 +2253,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Whole application (graph replay: H2D + kernels + D2H)</t>
+          <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2203,7 +2268,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Replay time (nsys)</t>
+          <t>Iteration time (nsys)</t>
         </is>
       </c>
       <c r="F22" s="6" t="n">
@@ -2215,9 +2280,9 @@
           <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
         </is>
       </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>n/a (graph-only harness)</t>
+      <c r="I22" s="14" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
       <c r="J22" s="12" t="n"/>
@@ -2231,7 +2296,7 @@
       </c>
       <c r="N22" s="5" t="inlineStr">
         <is>
-          <t>Median span of the 41 end-to-end replays in the nsys node trace.</t>
+          <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O55"/>
+  <dimension ref="A1:O91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -3339,7 +3404,7 @@
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -3352,20 +3417,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.002624 ms</t>
+          <t>0.002656 ms</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3.514486</v>
+        <v>3.47518</v>
       </c>
       <c r="F20" t="n">
-        <v>13.008218</v>
+        <v>12.842466</v>
       </c>
       <c r="G20" t="n">
-        <v>13.008218</v>
+        <v>12.842466</v>
       </c>
       <c r="H20" t="n">
-        <v>17.140889</v>
+        <v>17.177384</v>
       </c>
       <c r="I20" t="n">
         <v>100</v>
@@ -3390,7 +3455,7 @@
     <row r="21">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -3403,20 +3468,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.008256 ms</t>
+          <t>0.008 ms</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>13.656464</v>
+        <v>13.299701</v>
       </c>
       <c r="F21" t="n">
-        <v>76.784981</v>
+        <v>78.633516</v>
       </c>
       <c r="G21" t="n">
-        <v>76.784981</v>
+        <v>78.633516</v>
       </c>
       <c r="H21" t="n">
-        <v>62.012325</v>
+        <v>62.987278</v>
       </c>
       <c r="I21" t="n">
         <v>100</v>
@@ -3441,7 +3506,7 @@
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -3454,20 +3519,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>8.154912 ms</t>
+          <t>8.174304 ms</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>80.57264600000001</v>
+        <v>80.44577700000001</v>
       </c>
       <c r="F22" t="n">
-        <v>38.976691</v>
+        <v>38.915152</v>
       </c>
       <c r="G22" t="n">
-        <v>0.116162</v>
+        <v>0.116579</v>
       </c>
       <c r="H22" t="n">
-        <v>41.258669</v>
+        <v>41.259225</v>
       </c>
       <c r="I22" t="n">
         <v>41.666667</v>
@@ -3492,7 +3557,7 @@
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-20260925-142052.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3505,20 +3570,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.215616 ms</t>
+          <t>0.21552 ms</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.169713</v>
+        <v>0.16962</v>
       </c>
       <c r="F23" t="n">
-        <v>3.179019</v>
+        <v>3.184194</v>
       </c>
       <c r="G23" t="n">
-        <v>3.179019</v>
+        <v>3.184194</v>
       </c>
       <c r="H23" t="n">
-        <v>16.65479</v>
+        <v>16.654817</v>
       </c>
       <c r="I23" t="n">
         <v>83.333333</v>
@@ -3543,7 +3608,7 @@
     <row r="24">
       <c r="A24" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -3551,28 +3616,28 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>initialize_scores</t>
+          <t>project_audio_kernel</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>25.76 us</t>
+          <t>0.002688 ms</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>10.921542</v>
+        <v>3.556429</v>
       </c>
       <c r="F24" t="n">
-        <v>49.339404</v>
+        <v>13.110017</v>
       </c>
       <c r="G24" t="n">
-        <v>49.339404</v>
+        <v>13.110017</v>
       </c>
       <c r="H24" t="n">
-        <v>19.758186</v>
+        <v>17.134164</v>
       </c>
       <c r="I24" t="n">
-        <v>33.333333</v>
+        <v>100</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -3580,29 +3645,21 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>32768</v>
+        <v>196</v>
       </c>
       <c r="L24" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="M24" t="n">
-        <v>24.98</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>4.202496 Mbyte</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>7.365376 Mbyte</t>
-        </is>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -3610,58 +3667,50 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>pagerank_update</t>
+          <t>project_imu_kernel</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>40.256 us</t>
+          <t>0.008032 ms</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5.747545</v>
+        <v>13.564387</v>
       </c>
       <c r="F25" t="n">
-        <v>79.22566399999999</v>
+        <v>78.51781699999999</v>
       </c>
       <c r="G25" t="n">
-        <v>46.557748</v>
+        <v>78.51781699999999</v>
       </c>
       <c r="H25" t="n">
-        <v>30.343936</v>
+        <v>62.51766</v>
       </c>
       <c r="I25" t="n">
-        <v>33.333333</v>
+        <v>100</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>39.0 register/thread</t>
+          <t>16.0 register/thread</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>4096</v>
+        <v>1954</v>
       </c>
       <c r="L25" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="M25" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>14.329088 Mbyte</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>2.727168 Mbyte</t>
-        </is>
-      </c>
+        <v>1.99</v>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -3669,58 +3718,50 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>pagerank_update</t>
+          <t>void fuse_attention_kernel&lt;16, 4, 128, 256&gt;</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>40.8 us</t>
+          <t>8.174176 ms</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5.789358</v>
+        <v>80.459727</v>
       </c>
       <c r="F26" t="n">
-        <v>78.136639</v>
+        <v>38.921768</v>
       </c>
       <c r="G26" t="n">
-        <v>46.363129</v>
+        <v>0.118669</v>
       </c>
       <c r="H26" t="n">
-        <v>30.305666</v>
+        <v>41.258928</v>
       </c>
       <c r="I26" t="n">
-        <v>33.333333</v>
+        <v>41.666667</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>39.0 register/thread</t>
+          <t>90.0 register/thread</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>4096</v>
+        <v>12504</v>
       </c>
       <c r="L26" t="n">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="M26" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>14.476416 Mbyte</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>2.740224 Mbyte</t>
-        </is>
-      </c>
+        <v>30.5</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -3728,121 +3769,113 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>pagerank_update</t>
+          <t>reduce_statistics_kernel</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>40.704 us</t>
+          <t>0.216288 ms</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5.735559</v>
+        <v>0.169864</v>
       </c>
       <c r="F27" t="n">
-        <v>78.808885</v>
+        <v>3.213787</v>
       </c>
       <c r="G27" t="n">
-        <v>46.288329</v>
+        <v>3.213787</v>
       </c>
       <c r="H27" t="n">
-        <v>30.313736</v>
+        <v>16.654818</v>
       </c>
       <c r="I27" t="n">
-        <v>33.333333</v>
+        <v>83.333333</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>39.0 register/thread</t>
+          <t>48.0 register/thread</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>4096</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>32</v>
+        <v>256</v>
       </c>
       <c r="M27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>14.410112 Mbyte</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>2.748416 Mbyte</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>pagerank_update</t>
+          <t>initialize_scores</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>40.8 us</t>
+          <t>25.728 us</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5.749982</v>
+        <v>10.890063</v>
       </c>
       <c r="F28" t="n">
-        <v>77.825661</v>
+        <v>49.26792</v>
       </c>
       <c r="G28" t="n">
-        <v>46.603216</v>
+        <v>49.26792</v>
       </c>
       <c r="H28" t="n">
-        <v>30.311327</v>
+        <v>19.760892</v>
       </c>
       <c r="I28" t="n">
         <v>33.333333</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>39.0 register/thread</t>
+          <t>16.0 register/thread</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>4096</v>
+        <v>32768</v>
       </c>
       <c r="L28" t="n">
         <v>32</v>
       </c>
       <c r="M28" t="n">
-        <v>3.12</v>
+        <v>24.98</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>14.547968 Mbyte</t>
+          <t>4.201856 Mbyte</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2.76928 Mbyte</t>
+          <t>7.341184 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3851,20 +3884,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>40.832 us</t>
+          <t>40.416 us</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5.770563</v>
+        <v>5.773206</v>
       </c>
       <c r="F29" t="n">
-        <v>78.50193</v>
+        <v>78.87038200000001</v>
       </c>
       <c r="G29" t="n">
-        <v>45.725931</v>
+        <v>46.605831</v>
       </c>
       <c r="H29" t="n">
-        <v>30.347913</v>
+        <v>30.340962</v>
       </c>
       <c r="I29" t="n">
         <v>33.333333</v>
@@ -3885,23 +3918,23 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>14.250624 Mbyte</t>
+          <t>14.420864 Mbyte</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>2.751872 Mbyte</t>
+          <t>2.733184 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3914,16 +3947,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5.757007</v>
+        <v>5.764894</v>
       </c>
       <c r="F30" t="n">
-        <v>78.385526</v>
+        <v>78.376588</v>
       </c>
       <c r="G30" t="n">
-        <v>46.945866</v>
+        <v>46.713255</v>
       </c>
       <c r="H30" t="n">
-        <v>30.313364</v>
+        <v>30.371009</v>
       </c>
       <c r="I30" t="n">
         <v>33.333333</v>
@@ -3944,23 +3977,23 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>14.580608 Mbyte</t>
+          <t>14.519424 Mbyte</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.802432 Mbyte</t>
+          <t>2.781312 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3969,20 +4002,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>41.024 us</t>
+          <t>40.448 us</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5.779708</v>
+        <v>5.800137</v>
       </c>
       <c r="F31" t="n">
-        <v>78.19292</v>
+        <v>79.203608</v>
       </c>
       <c r="G31" t="n">
-        <v>45.441394</v>
+        <v>46.456225</v>
       </c>
       <c r="H31" t="n">
-        <v>30.368289</v>
+        <v>30.361409</v>
       </c>
       <c r="I31" t="n">
         <v>33.333333</v>
@@ -4003,23 +4036,23 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>14.206848 Mbyte</t>
+          <t>14.40832 Mbyte</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2.760576 Mbyte</t>
+          <t>2.70208 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4028,20 +4061,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.8 us</t>
+          <t>40.992 us</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5.704606</v>
+        <v>5.775927</v>
       </c>
       <c r="F32" t="n">
-        <v>78.62662899999999</v>
+        <v>77.786952</v>
       </c>
       <c r="G32" t="n">
-        <v>46.416212</v>
+        <v>46.38541</v>
       </c>
       <c r="H32" t="n">
-        <v>30.342626</v>
+        <v>30.322205</v>
       </c>
       <c r="I32" t="n">
         <v>33.333333</v>
@@ -4062,23 +4095,23 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>14.507264 Mbyte</t>
+          <t>14.534656 Mbyte</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.729088 Mbyte</t>
+          <t>2.758656 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4087,20 +4120,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>263.68 us</t>
+          <t>41.088 us</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6.842585</v>
+        <v>5.656753</v>
       </c>
       <c r="F33" t="n">
-        <v>96.350821</v>
+        <v>78.029509</v>
       </c>
       <c r="G33" t="n">
-        <v>38.31591</v>
+        <v>45.854221</v>
       </c>
       <c r="H33" t="n">
-        <v>32.571334</v>
+        <v>30.384827</v>
       </c>
       <c r="I33" t="n">
         <v>33.333333</v>
@@ -4111,33 +4144,33 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="L33" t="n">
         <v>32</v>
       </c>
       <c r="M33" t="n">
-        <v>24.98</v>
+        <v>3.12</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>81.935616 Mbyte</t>
+          <t>14.370048 Mbyte</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>10.110848 Mbyte</t>
+          <t>2.770304 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4146,20 +4179,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>262.624 us</t>
+          <t>40.864 us</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6.890881</v>
+        <v>5.78772</v>
       </c>
       <c r="F34" t="n">
-        <v>96.04748499999999</v>
+        <v>78.104333</v>
       </c>
       <c r="G34" t="n">
-        <v>38.504652</v>
+        <v>46.460881</v>
       </c>
       <c r="H34" t="n">
-        <v>32.57196</v>
+        <v>30.333385</v>
       </c>
       <c r="I34" t="n">
         <v>33.333333</v>
@@ -4170,33 +4203,33 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="L34" t="n">
         <v>32</v>
       </c>
       <c r="M34" t="n">
-        <v>24.98</v>
+        <v>3.12</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>81.83168 Mbyte</t>
+          <t>14.488064 Mbyte</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>10.308608 Mbyte</t>
+          <t>2.787712 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4205,20 +4238,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>262.144 us</t>
+          <t>40.832 us</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6.838216</v>
+        <v>5.761913</v>
       </c>
       <c r="F35" t="n">
-        <v>96.22165099999999</v>
+        <v>78.049094</v>
       </c>
       <c r="G35" t="n">
-        <v>38.461765</v>
+        <v>45.86879</v>
       </c>
       <c r="H35" t="n">
-        <v>32.573901</v>
+        <v>30.304531</v>
       </c>
       <c r="I35" t="n">
         <v>33.333333</v>
@@ -4229,33 +4262,33 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="L35" t="n">
         <v>32</v>
       </c>
       <c r="M35" t="n">
-        <v>24.98</v>
+        <v>3.12</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>81.744768 Mbyte</t>
+          <t>14.347776 Mbyte</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>10.122752 Mbyte</t>
+          <t>2.70784 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4264,20 +4297,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>262.144 us</t>
+          <t>40.832 us</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6.839503</v>
+        <v>5.750203</v>
       </c>
       <c r="F36" t="n">
-        <v>96.21314099999999</v>
+        <v>78.529796</v>
       </c>
       <c r="G36" t="n">
-        <v>38.410605</v>
+        <v>46.471641</v>
       </c>
       <c r="H36" t="n">
-        <v>32.571073</v>
+        <v>30.319598</v>
       </c>
       <c r="I36" t="n">
         <v>33.333333</v>
@@ -4288,33 +4321,33 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>32768</v>
+        <v>4096</v>
       </c>
       <c r="L36" t="n">
         <v>32</v>
       </c>
       <c r="M36" t="n">
-        <v>24.98</v>
+        <v>3.12</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>81.65184 Mbyte</t>
+          <t>14.502272 Mbyte</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>10.080896 Mbyte</t>
+          <t>2.781312 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4323,20 +4356,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>261.984 us</t>
+          <t>264.064 us</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6.89154</v>
+        <v>6.889017</v>
       </c>
       <c r="F37" t="n">
-        <v>96.279512</v>
+        <v>96.29396199999999</v>
       </c>
       <c r="G37" t="n">
-        <v>38.487274</v>
+        <v>38.144759</v>
       </c>
       <c r="H37" t="n">
-        <v>32.562819</v>
+        <v>32.574188</v>
       </c>
       <c r="I37" t="n">
         <v>33.333333</v>
@@ -4357,23 +4390,23 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>81.739392 Mbyte</t>
+          <t>81.698944 Mbyte</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>10.129152 Mbyte</t>
+          <t>10.073856 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4382,20 +4415,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>264.064 us</t>
+          <t>261.984 us</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6.829113</v>
+        <v>6.895241</v>
       </c>
       <c r="F38" t="n">
-        <v>96.173174</v>
+        <v>96.26137199999999</v>
       </c>
       <c r="G38" t="n">
-        <v>38.240658</v>
+        <v>38.440095</v>
       </c>
       <c r="H38" t="n">
-        <v>32.570992</v>
+        <v>32.571375</v>
       </c>
       <c r="I38" t="n">
         <v>33.333333</v>
@@ -4416,23 +4449,23 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>81.859584 Mbyte</t>
+          <t>81.69344 Mbyte</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>10.147072 Mbyte</t>
+          <t>10.071936 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4441,20 +4474,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>261.952 us</t>
+          <t>262.208 us</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6.879384</v>
+        <v>6.895088</v>
       </c>
       <c r="F39" t="n">
-        <v>96.382761</v>
+        <v>96.188607</v>
       </c>
       <c r="G39" t="n">
-        <v>38.477568</v>
+        <v>38.499539</v>
       </c>
       <c r="H39" t="n">
-        <v>32.575274</v>
+        <v>32.564324</v>
       </c>
       <c r="I39" t="n">
         <v>33.333333</v>
@@ -4475,23 +4508,23 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>81.632768 Mbyte</t>
+          <t>81.865728 Mbyte</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>10.212608 Mbyte</t>
+          <t>10.117248 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4500,20 +4533,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>264.352 us</t>
+          <t>263.552 us</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6.845313</v>
+        <v>6.889272</v>
       </c>
       <c r="F40" t="n">
-        <v>96.071521</v>
+        <v>96.323176</v>
       </c>
       <c r="G40" t="n">
-        <v>38.10164</v>
+        <v>38.365225</v>
       </c>
       <c r="H40" t="n">
-        <v>32.570552</v>
+        <v>32.574026</v>
       </c>
       <c r="I40" t="n">
         <v>33.333333</v>
@@ -4534,23 +4567,23 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>81.715072 Mbyte</t>
+          <t>81.79584 Mbyte</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>10.063232 Mbyte</t>
+          <t>10.337664 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4559,20 +4592,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>263.648 us</t>
+          <t>261.792 us</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.849033</v>
+        <v>6.886739</v>
       </c>
       <c r="F41" t="n">
-        <v>96.289919</v>
+        <v>96.343954</v>
       </c>
       <c r="G41" t="n">
-        <v>38.268248</v>
+        <v>38.49865</v>
       </c>
       <c r="H41" t="n">
-        <v>32.57112</v>
+        <v>32.569317</v>
       </c>
       <c r="I41" t="n">
         <v>33.333333</v>
@@ -4593,23 +4626,23 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>81.781632 Mbyte</t>
+          <t>81.744384 Mbyte</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>10.140928 Mbyte</t>
+          <t>10.091392 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4618,20 +4651,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>262.208 us</t>
+          <t>263.744 us</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6.841281</v>
+        <v>6.843444</v>
       </c>
       <c r="F42" t="n">
-        <v>96.18399700000001</v>
+        <v>96.26432699999999</v>
       </c>
       <c r="G42" t="n">
-        <v>38.452801</v>
+        <v>38.237625</v>
       </c>
       <c r="H42" t="n">
-        <v>32.571622</v>
+        <v>32.569524</v>
       </c>
       <c r="I42" t="n">
         <v>33.333333</v>
@@ -4652,23 +4685,23 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>81.751552 Mbyte</t>
+          <t>81.754624 Mbyte</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>10.116608 Mbyte</t>
+          <t>10.131968 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4677,20 +4710,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>262.08 us</t>
+          <t>261.984 us</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.885764</v>
+        <v>6.884972</v>
       </c>
       <c r="F43" t="n">
-        <v>96.26073599999999</v>
+        <v>96.290837</v>
       </c>
       <c r="G43" t="n">
-        <v>38.451416</v>
+        <v>38.501948</v>
       </c>
       <c r="H43" t="n">
-        <v>32.566573</v>
+        <v>32.568833</v>
       </c>
       <c r="I43" t="n">
         <v>33.333333</v>
@@ -4711,23 +4744,23 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>81.73888 Mbyte</t>
+          <t>81.774592 Mbyte</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10.07872 Mbyte</t>
+          <t>10.125824 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4736,20 +4769,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>262.208 us</t>
+          <t>261.824 us</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6.885595</v>
+        <v>6.884805</v>
       </c>
       <c r="F44" t="n">
-        <v>96.174879</v>
+        <v>96.37597</v>
       </c>
       <c r="G44" t="n">
-        <v>38.426773</v>
+        <v>38.426951</v>
       </c>
       <c r="H44" t="n">
-        <v>32.5699</v>
+        <v>32.569863</v>
       </c>
       <c r="I44" t="n">
         <v>33.333333</v>
@@ -4770,23 +4803,23 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>81.703552 Mbyte</t>
+          <t>81.599488 Mbyte</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>10.096128 Mbyte</t>
+          <t>10.071552 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -4795,20 +4828,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>263.744 us</t>
+          <t>263.936 us</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.880016</v>
+        <v>6.840552</v>
       </c>
       <c r="F45" t="n">
-        <v>96.241539</v>
+        <v>96.298384</v>
       </c>
       <c r="G45" t="n">
-        <v>38.257519</v>
+        <v>38.219401</v>
       </c>
       <c r="H45" t="n">
-        <v>32.570354</v>
+        <v>32.572821</v>
       </c>
       <c r="I45" t="n">
         <v>33.333333</v>
@@ -4829,23 +4862,23 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>81.750528 Mbyte</t>
+          <t>81.804416 Mbyte</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>10.180736 Mbyte</t>
+          <t>10.107264 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -4854,20 +4887,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>261.728 us</t>
+          <t>261.824 us</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.844845</v>
+        <v>6.879849</v>
       </c>
       <c r="F46" t="n">
-        <v>96.37342700000001</v>
+        <v>96.347562</v>
       </c>
       <c r="G46" t="n">
-        <v>38.485057</v>
+        <v>38.630291</v>
       </c>
       <c r="H46" t="n">
-        <v>32.566478</v>
+        <v>32.565578</v>
       </c>
       <c r="I46" t="n">
         <v>33.333333</v>
@@ -4888,23 +4921,23 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>81.703424 Mbyte</t>
+          <t>81.864832 Mbyte</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>10.071552 Mbyte</t>
+          <t>10.288128 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -4913,20 +4946,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>263.904 us</t>
+          <t>263.712 us</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.847247</v>
+        <v>6.885424</v>
       </c>
       <c r="F47" t="n">
-        <v>96.174414</v>
+        <v>96.36948</v>
       </c>
       <c r="G47" t="n">
-        <v>38.21061</v>
+        <v>38.214683</v>
       </c>
       <c r="H47" t="n">
-        <v>32.572843</v>
+        <v>32.579621</v>
       </c>
       <c r="I47" t="n">
         <v>33.333333</v>
@@ -4947,23 +4980,23 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>81.746176 Mbyte</t>
+          <t>81.745664 Mbyte</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>10.13184 Mbyte</t>
+          <t>10.070144 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -4972,20 +5005,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>262.048 us</t>
+          <t>263.616 us</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.887087</v>
+        <v>6.838532</v>
       </c>
       <c r="F48" t="n">
-        <v>96.239237</v>
+        <v>96.31980299999999</v>
       </c>
       <c r="G48" t="n">
-        <v>38.462912</v>
+        <v>38.213066</v>
       </c>
       <c r="H48" t="n">
-        <v>32.572405</v>
+        <v>32.580223</v>
       </c>
       <c r="I48" t="n">
         <v>33.333333</v>
@@ -5006,23 +5039,23 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>81.706496 Mbyte</t>
+          <t>81.690368 Mbyte</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10.125952 Mbyte</t>
+          <t>10.096512 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5035,16 +5068,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.891398</v>
+        <v>6.837447</v>
       </c>
       <c r="F49" t="n">
-        <v>96.24030399999999</v>
+        <v>96.248293</v>
       </c>
       <c r="G49" t="n">
-        <v>38.475069</v>
+        <v>38.715689</v>
       </c>
       <c r="H49" t="n">
-        <v>32.563501</v>
+        <v>32.568851</v>
       </c>
       <c r="I49" t="n">
         <v>33.333333</v>
@@ -5065,23 +5098,23 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>81.785344 Mbyte</t>
+          <t>82.05184 Mbyte</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>10.107648 Mbyte</t>
+          <t>10.412672 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5090,20 +5123,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>264.0 us</t>
+          <t>262.272 us</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.837552</v>
+        <v>6.888228</v>
       </c>
       <c r="F50" t="n">
-        <v>96.219886</v>
+        <v>96.173063</v>
       </c>
       <c r="G50" t="n">
-        <v>38.15776</v>
+        <v>38.452885</v>
       </c>
       <c r="H50" t="n">
-        <v>32.574448</v>
+        <v>32.560925</v>
       </c>
       <c r="I50" t="n">
         <v>33.333333</v>
@@ -5124,23 +5157,23 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>81.711488 Mbyte</t>
+          <t>81.747584 Mbyte</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>10.067584 Mbyte</t>
+          <t>10.133376 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
         <is>
-          <t>ncu-pagerank-20261007-152417.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5149,20 +5182,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>262.24 us</t>
+          <t>261.696 us</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.888579</v>
+        <v>6.882413</v>
       </c>
       <c r="F51" t="n">
-        <v>96.21982800000001</v>
+        <v>96.3886</v>
       </c>
       <c r="G51" t="n">
-        <v>38.46029</v>
+        <v>38.485446</v>
       </c>
       <c r="H51" t="n">
-        <v>32.563086</v>
+        <v>32.566455</v>
       </c>
       <c r="I51" t="n">
         <v>33.333333</v>
@@ -5183,248 +5216,2372 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>81.737856 Mbyte</t>
+          <t>81.679488 Mbyte</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>10.154496 Mbyte</t>
+          <t>10.090112 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>&lt;unnamed&gt;::mse_partial_kernel</t>
+          <t>pagerank_update</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>385.248 us</t>
+          <t>263.776 us</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10.299178</v>
+        <v>6.833415</v>
       </c>
       <c r="F52" t="n">
-        <v>96.16788200000001</v>
+        <v>96.259393</v>
       </c>
       <c r="G52" t="n">
-        <v>96.16788200000001</v>
+        <v>38.287428</v>
       </c>
       <c r="H52" t="n">
-        <v>86.776482</v>
+        <v>32.569779</v>
       </c>
       <c r="I52" t="n">
-        <v>100</v>
+        <v>33.333333</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>24.0 register/thread</t>
+          <t>39.0 register/thread</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>656</v>
+        <v>32768</v>
       </c>
       <c r="L52" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="M52" t="n">
-        <v>1.33</v>
+        <v>24.98</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>335.561472 Mbyte</t>
+          <t>81.737088 Mbyte</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>2.013952 Mbyte</t>
+          <t>10.288 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-20261007-144943.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>&lt;unnamed&gt;::mse_finalize_kernel</t>
+          <t>pagerank_update</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3.168 us</t>
+          <t>262.368 us</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.03828</v>
+        <v>6.884495</v>
       </c>
       <c r="F53" t="n">
-        <v>1.087102</v>
+        <v>96.145937</v>
       </c>
       <c r="G53" t="n">
-        <v>0.307081</v>
+        <v>38.449581</v>
       </c>
       <c r="H53" t="n">
-        <v>15.627367</v>
+        <v>32.563338</v>
       </c>
       <c r="I53" t="n">
-        <v>100</v>
+        <v>33.333333</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>16.0 register/thread</t>
+          <t>39.0 register/thread</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>32768</v>
       </c>
       <c r="L53" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>24.98</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>0.008448 Mbyte</t>
+          <t>81.785088 Mbyte</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>0.000256 Mbyte</t>
+          <t>10.122624 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-20261007-144950.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>&lt;unnamed&gt;::kws_postprocess_kernel</t>
+          <t>pagerank_update</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.118784 ms</t>
+          <t>261.952 us</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>80.972021</v>
+        <v>6.892467</v>
       </c>
       <c r="F54" t="n">
-        <v>75.573886</v>
+        <v>96.30693599999999</v>
       </c>
       <c r="G54" t="n">
-        <v>26.25334</v>
+        <v>38.429724</v>
       </c>
       <c r="H54" t="n">
-        <v>84.79490800000001</v>
+        <v>32.570514</v>
       </c>
       <c r="I54" t="n">
-        <v>100</v>
+        <v>33.333333</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>24.0 register/thread</t>
+          <t>39.0 register/thread</t>
         </is>
       </c>
       <c r="K54" t="n">
-        <v>524288</v>
+        <v>32768</v>
       </c>
       <c r="L54" t="n">
-        <v>256</v>
+        <v>32</v>
       </c>
       <c r="M54" t="n">
-        <v>1065.63</v>
+        <v>24.98</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>50.345728 Mbyte</t>
+          <t>81.664512 Mbyte</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>217.3056 Mbyte</t>
+          <t>10.057216 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
         <is>
-          <t>ncu-vww_preprocess-20261007-144958.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B55" t="n">
+        <v>27</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>263.872 us</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6.833276</v>
+      </c>
+      <c r="F55" t="n">
+        <v>96.264078</v>
+      </c>
+      <c r="G55" t="n">
+        <v>38.34479</v>
+      </c>
+      <c r="H55" t="n">
+        <v>32.574914</v>
+      </c>
+      <c r="I55" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L55" t="n">
+        <v>32</v>
+      </c>
+      <c r="M55" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>81.928192 Mbyte</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>10.26304 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
         <v>0</v>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>initialize_scores</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>25.824 us</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>10.877459</v>
+      </c>
+      <c r="F56" t="n">
+        <v>49.056943</v>
+      </c>
+      <c r="G56" t="n">
+        <v>49.056943</v>
+      </c>
+      <c r="H56" t="n">
+        <v>19.739888</v>
+      </c>
+      <c r="I56" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>16.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L56" t="n">
+        <v>32</v>
+      </c>
+      <c r="M56" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>4.206592 Mbyte</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>7.319168 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>40.736 us</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>5.805545</v>
+      </c>
+      <c r="F57" t="n">
+        <v>78.169856</v>
+      </c>
+      <c r="G57" t="n">
+        <v>46.249516</v>
+      </c>
+      <c r="H57" t="n">
+        <v>30.350646</v>
+      </c>
+      <c r="I57" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L57" t="n">
+        <v>32</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>14.387584 Mbyte</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2.752768 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>40.48 us</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>5.74774</v>
+      </c>
+      <c r="F58" t="n">
+        <v>78.652164</v>
+      </c>
+      <c r="G58" t="n">
+        <v>46.496623</v>
+      </c>
+      <c r="H58" t="n">
+        <v>30.34208</v>
+      </c>
+      <c r="I58" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L58" t="n">
+        <v>32</v>
+      </c>
+      <c r="M58" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>14.400768 Mbyte</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2.72832 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>3</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>40.864 us</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>5.763605</v>
+      </c>
+      <c r="F59" t="n">
+        <v>78.299513</v>
+      </c>
+      <c r="G59" t="n">
+        <v>46.192525</v>
+      </c>
+      <c r="H59" t="n">
+        <v>30.342844</v>
+      </c>
+      <c r="I59" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K59" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L59" t="n">
+        <v>32</v>
+      </c>
+      <c r="M59" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>14.428544 Mbyte</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2.751232 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>40.832 us</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>5.712442</v>
+      </c>
+      <c r="F60" t="n">
+        <v>77.951116</v>
+      </c>
+      <c r="G60" t="n">
+        <v>46.345444</v>
+      </c>
+      <c r="H60" t="n">
+        <v>30.3306</v>
+      </c>
+      <c r="I60" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K60" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L60" t="n">
+        <v>32</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>14.486656 Mbyte</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2.7424 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>41.6 us</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>5.759529</v>
+      </c>
+      <c r="F61" t="n">
+        <v>76.955658</v>
+      </c>
+      <c r="G61" t="n">
+        <v>45.410515</v>
+      </c>
+      <c r="H61" t="n">
+        <v>30.344492</v>
+      </c>
+      <c r="I61" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K61" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L61" t="n">
+        <v>32</v>
+      </c>
+      <c r="M61" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>14.378624 Mbyte</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2.819072 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>41.504 us</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5.784515</v>
+      </c>
+      <c r="F62" t="n">
+        <v>76.66707599999999</v>
+      </c>
+      <c r="G62" t="n">
+        <v>46.270598</v>
+      </c>
+      <c r="H62" t="n">
+        <v>30.328672</v>
+      </c>
+      <c r="I62" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L62" t="n">
+        <v>32</v>
+      </c>
+      <c r="M62" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>14.650496 Mbyte</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2.831232 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>7</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>40.736 us</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>5.786246</v>
+      </c>
+      <c r="F63" t="n">
+        <v>78.139859</v>
+      </c>
+      <c r="G63" t="n">
+        <v>45.437417</v>
+      </c>
+      <c r="H63" t="n">
+        <v>30.348963</v>
+      </c>
+      <c r="I63" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K63" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L63" t="n">
+        <v>32</v>
+      </c>
+      <c r="M63" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>14.163072 Mbyte</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2.6912 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>8</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>40.832 us</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>5.799694</v>
+      </c>
+      <c r="F64" t="n">
+        <v>77.920129</v>
+      </c>
+      <c r="G64" t="n">
+        <v>46.611313</v>
+      </c>
+      <c r="H64" t="n">
+        <v>30.346429</v>
+      </c>
+      <c r="I64" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K64" t="n">
+        <v>4096</v>
+      </c>
+      <c r="L64" t="n">
+        <v>32</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>14.597376 Mbyte</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2.734336 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>9</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>262.24 us</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6.895505</v>
+      </c>
+      <c r="F65" t="n">
+        <v>96.16476900000001</v>
+      </c>
+      <c r="G65" t="n">
+        <v>38.424835</v>
+      </c>
+      <c r="H65" t="n">
+        <v>32.571271</v>
+      </c>
+      <c r="I65" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K65" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L65" t="n">
+        <v>32</v>
+      </c>
+      <c r="M65" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>81.701504 Mbyte</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>10.09984 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>10</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>263.648 us</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6.849166</v>
+      </c>
+      <c r="F66" t="n">
+        <v>96.19049099999999</v>
+      </c>
+      <c r="G66" t="n">
+        <v>38.224158</v>
+      </c>
+      <c r="H66" t="n">
+        <v>32.571055</v>
+      </c>
+      <c r="I66" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K66" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L66" t="n">
+        <v>32</v>
+      </c>
+      <c r="M66" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>81.751552 Mbyte</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>10.074496 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>11</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>261.792 us</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6.886829</v>
+      </c>
+      <c r="F67" t="n">
+        <v>96.325785</v>
+      </c>
+      <c r="G67" t="n">
+        <v>38.537803</v>
+      </c>
+      <c r="H67" t="n">
+        <v>32.569066</v>
+      </c>
+      <c r="I67" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K67" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L67" t="n">
+        <v>32</v>
+      </c>
+      <c r="M67" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>81.801856 Mbyte</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>10.12416 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>12</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>263.552 us</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6.850185</v>
+      </c>
+      <c r="F68" t="n">
+        <v>96.245718</v>
+      </c>
+      <c r="G68" t="n">
+        <v>38.24335</v>
+      </c>
+      <c r="H68" t="n">
+        <v>32.568792</v>
+      </c>
+      <c r="I68" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K68" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L68" t="n">
+        <v>32</v>
+      </c>
+      <c r="M68" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>81.698304 Mbyte</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>10.13312 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>13</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>263.552 us</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6.894557</v>
+      </c>
+      <c r="F69" t="n">
+        <v>96.27703</v>
+      </c>
+      <c r="G69" t="n">
+        <v>38.290364</v>
+      </c>
+      <c r="H69" t="n">
+        <v>32.568962</v>
+      </c>
+      <c r="I69" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K69" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L69" t="n">
+        <v>32</v>
+      </c>
+      <c r="M69" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>81.828992 Mbyte</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>10.127872 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>14</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>261.824 us</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6.885321</v>
+      </c>
+      <c r="F70" t="n">
+        <v>96.31959000000001</v>
+      </c>
+      <c r="G70" t="n">
+        <v>38.503123</v>
+      </c>
+      <c r="H70" t="n">
+        <v>32.567834</v>
+      </c>
+      <c r="I70" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K70" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L70" t="n">
+        <v>32</v>
+      </c>
+      <c r="M70" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>81.778048 Mbyte</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>10.071552 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>15</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>261.76 us</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6.898733</v>
+      </c>
+      <c r="F71" t="n">
+        <v>96.291757</v>
+      </c>
+      <c r="G71" t="n">
+        <v>38.518161</v>
+      </c>
+      <c r="H71" t="n">
+        <v>32.568335</v>
+      </c>
+      <c r="I71" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L71" t="n">
+        <v>32</v>
+      </c>
+      <c r="M71" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>81.760896 Mbyte</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>10.1088 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>16</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>263.68 us</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6.879953</v>
+      </c>
+      <c r="F72" t="n">
+        <v>96.201206</v>
+      </c>
+      <c r="G72" t="n">
+        <v>38.239644</v>
+      </c>
+      <c r="H72" t="n">
+        <v>32.570855</v>
+      </c>
+      <c r="I72" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K72" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L72" t="n">
+        <v>32</v>
+      </c>
+      <c r="M72" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>81.771392 Mbyte</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>10.10752 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>17</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>262.016 us</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6.85042</v>
+      </c>
+      <c r="F73" t="n">
+        <v>96.233647</v>
+      </c>
+      <c r="G73" t="n">
+        <v>38.467428</v>
+      </c>
+      <c r="H73" t="n">
+        <v>32.574187</v>
+      </c>
+      <c r="I73" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L73" t="n">
+        <v>32</v>
+      </c>
+      <c r="M73" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>81.757184 Mbyte</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>10.079744 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>18</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>263.584 us</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6.842498</v>
+      </c>
+      <c r="F74" t="n">
+        <v>96.236355</v>
+      </c>
+      <c r="G74" t="n">
+        <v>38.217025</v>
+      </c>
+      <c r="H74" t="n">
+        <v>32.574523</v>
+      </c>
+      <c r="I74" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K74" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L74" t="n">
+        <v>32</v>
+      </c>
+      <c r="M74" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>81.690368 Mbyte</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>10.090368 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>19</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>261.92 us</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6.891282</v>
+      </c>
+      <c r="F75" t="n">
+        <v>96.255655</v>
+      </c>
+      <c r="G75" t="n">
+        <v>38.510219</v>
+      </c>
+      <c r="H75" t="n">
+        <v>32.566437</v>
+      </c>
+      <c r="I75" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L75" t="n">
+        <v>32</v>
+      </c>
+      <c r="M75" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>81.746176 Mbyte</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>10.158208 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>20</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>263.36 us</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6.887735</v>
+      </c>
+      <c r="F76" t="n">
+        <v>96.314137</v>
+      </c>
+      <c r="G76" t="n">
+        <v>38.307678</v>
+      </c>
+      <c r="H76" t="n">
+        <v>32.569651</v>
+      </c>
+      <c r="I76" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L76" t="n">
+        <v>32</v>
+      </c>
+      <c r="M76" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>81.854592 Mbyte</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>10.077952 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>21</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>262.176 us</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6.89219</v>
+      </c>
+      <c r="F77" t="n">
+        <v>96.169397</v>
+      </c>
+      <c r="G77" t="n">
+        <v>38.418853</v>
+      </c>
+      <c r="H77" t="n">
+        <v>32.569409</v>
+      </c>
+      <c r="I77" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L77" t="n">
+        <v>32</v>
+      </c>
+      <c r="M77" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>81.662336 Mbyte</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>10.112128 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>22</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>261.952 us</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6.851282</v>
+      </c>
+      <c r="F78" t="n">
+        <v>96.25175400000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>38.473586</v>
+      </c>
+      <c r="H78" t="n">
+        <v>32.568744</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L78" t="n">
+        <v>32</v>
+      </c>
+      <c r="M78" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>81.735424 Mbyte</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>10.081536 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>23</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>262.048 us</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6.845855</v>
+      </c>
+      <c r="F79" t="n">
+        <v>96.220005</v>
+      </c>
+      <c r="G79" t="n">
+        <v>38.46377</v>
+      </c>
+      <c r="H79" t="n">
+        <v>32.575165</v>
+      </c>
+      <c r="I79" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L79" t="n">
+        <v>32</v>
+      </c>
+      <c r="M79" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>81.741568 Mbyte</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>10.092928 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>24</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>261.888 us</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6.887929</v>
+      </c>
+      <c r="F80" t="n">
+        <v>96.28758999999999</v>
+      </c>
+      <c r="G80" t="n">
+        <v>38.496537</v>
+      </c>
+      <c r="H80" t="n">
+        <v>32.569462</v>
+      </c>
+      <c r="I80" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L80" t="n">
+        <v>32</v>
+      </c>
+      <c r="M80" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>81.759744 Mbyte</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>10.102528 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>25</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>263.552 us</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6.845493</v>
+      </c>
+      <c r="F81" t="n">
+        <v>96.25166</v>
+      </c>
+      <c r="G81" t="n">
+        <v>38.308544</v>
+      </c>
+      <c r="H81" t="n">
+        <v>32.572542</v>
+      </c>
+      <c r="I81" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L81" t="n">
+        <v>32</v>
+      </c>
+      <c r="M81" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>81.828096 Mbyte</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>10.1536 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>26</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>261.856 us</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6.89217</v>
+      </c>
+      <c r="F82" t="n">
+        <v>96.292596</v>
+      </c>
+      <c r="G82" t="n">
+        <v>38.5189</v>
+      </c>
+      <c r="H82" t="n">
+        <v>32.567302</v>
+      </c>
+      <c r="I82" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L82" t="n">
+        <v>32</v>
+      </c>
+      <c r="M82" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>81.79456 Mbyte</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>10.102144 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="18" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>27</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>pagerank_update</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>263.392 us</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6.844887</v>
+      </c>
+      <c r="F83" t="n">
+        <v>96.333033</v>
+      </c>
+      <c r="G83" t="n">
+        <v>38.253091</v>
+      </c>
+      <c r="H83" t="n">
+        <v>32.5683</v>
+      </c>
+      <c r="I83" t="n">
+        <v>33.333333</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>39.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>32768</v>
+      </c>
+      <c r="L83" t="n">
+        <v>32</v>
+      </c>
+      <c r="M83" t="n">
+        <v>24.98</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>81.718912 Mbyte</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>10.092032 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="18" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::mse_partial_kernel</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>384.288 us</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>10.292332</v>
+      </c>
+      <c r="F84" t="n">
+        <v>96.411517</v>
+      </c>
+      <c r="G84" t="n">
+        <v>96.411517</v>
+      </c>
+      <c r="H84" t="n">
+        <v>87.82091800000001</v>
+      </c>
+      <c r="I84" t="n">
+        <v>100</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>24.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>656</v>
+      </c>
+      <c r="L84" t="n">
+        <v>256</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>335.560704 Mbyte</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2.056448 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="18" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::mse_finalize_kernel</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.136 us</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>0.038032</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1.093624</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="H85" t="n">
+        <v>15.235129</v>
+      </c>
+      <c r="I85" t="n">
+        <v>100</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>16.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="n">
+        <v>256</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>0.00832 Mbyte</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>0.0 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::mse_partial_kernel</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>384.32 us</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>10.285178</v>
+      </c>
+      <c r="F86" t="n">
+        <v>96.452887</v>
+      </c>
+      <c r="G86" t="n">
+        <v>96.452887</v>
+      </c>
+      <c r="H86" t="n">
+        <v>87.27867500000001</v>
+      </c>
+      <c r="I86" t="n">
+        <v>100</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>24.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>656</v>
+      </c>
+      <c r="L86" t="n">
+        <v>256</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>335.561216 Mbyte</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2.224512 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::mse_finalize_kernel</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3.104 us</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>0.03844</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.110147</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.316166</v>
+      </c>
+      <c r="H87" t="n">
+        <v>15.405402</v>
+      </c>
+      <c r="I87" t="n">
+        <v>100</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>16.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>256</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>0.008448 Mbyte</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>0.000384 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::kws_postprocess_kernel</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>1.120224 ms</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>80.98921</v>
+      </c>
+      <c r="F88" t="n">
+        <v>75.58993</v>
+      </c>
+      <c r="G88" t="n">
+        <v>26.21965</v>
+      </c>
+      <c r="H88" t="n">
+        <v>84.800596</v>
+      </c>
+      <c r="I88" t="n">
+        <v>100</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>24.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K88" t="n">
+        <v>524288</v>
+      </c>
+      <c r="L88" t="n">
+        <v>256</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1065.63</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>50.345344 Mbyte</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>217.301888 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="18" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::kws_postprocess_kernel</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>1.119968 ms</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>80.988163</v>
+      </c>
+      <c r="F89" t="n">
+        <v>75.58895200000001</v>
+      </c>
+      <c r="G89" t="n">
+        <v>26.231674</v>
+      </c>
+      <c r="H89" t="n">
+        <v>84.800144</v>
+      </c>
+      <c r="I89" t="n">
+        <v>100</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>24.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K89" t="n">
+        <v>524288</v>
+      </c>
+      <c r="L89" t="n">
+        <v>256</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1065.63</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>50.34496 Mbyte</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>217.37344 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="18" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>&lt;unnamed&gt;::vww_preprocess_kernel</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>665.984 us</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>3.161387</v>
-      </c>
-      <c r="F55" t="n">
-        <v>88.344808</v>
-      </c>
-      <c r="G55" t="n">
-        <v>88.344808</v>
-      </c>
-      <c r="H55" t="n">
-        <v>94.283644</v>
-      </c>
-      <c r="I55" t="n">
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>664.96 us</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>3.184013</v>
+      </c>
+      <c r="F90" t="n">
+        <v>88.457606</v>
+      </c>
+      <c r="G90" t="n">
+        <v>88.457606</v>
+      </c>
+      <c r="H90" t="n">
+        <v>93.35373800000001</v>
+      </c>
+      <c r="I90" t="n">
         <v>100</v>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>20.0 register/thread</t>
         </is>
       </c>
-      <c r="K55" t="n">
+      <c r="K90" t="n">
         <v>656</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L90" t="n">
         <v>256</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M90" t="n">
         <v>1.33</v>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>268.492672 Mbyte</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>267.661312 Mbyte</t>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>268.450304 Mbyte</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>267.547648 Mbyte</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="18" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>&lt;unnamed&gt;::vww_preprocess_kernel</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>659.456 us</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>3.153678</v>
+      </c>
+      <c r="F91" t="n">
+        <v>89.196668</v>
+      </c>
+      <c r="G91" t="n">
+        <v>89.196668</v>
+      </c>
+      <c r="H91" t="n">
+        <v>93.17085</v>
+      </c>
+      <c r="I91" t="n">
+        <v>100</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>20.0 register/thread</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>656</v>
+      </c>
+      <c r="L91" t="n">
+        <v>256</v>
+      </c>
+      <c r="M91" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>268.450304 Mbyte</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>267.56864 Mbyte</t>
         </is>
       </c>
     </row>
@@ -5484,6 +7641,42 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/cuda_performance.xlsx
+++ b/results/cuda_performance.xlsx
@@ -42,15 +42,15 @@
       <b val="1"/>
     </font>
     <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
+    <font>
       <color rgb="000563C1"/>
     </font>
     <font>
       <color rgb="000563C1"/>
       <u val="single"/>
-    </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00808080"/>
     </font>
   </fonts>
   <fills count="6">
@@ -67,12 +67,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -122,22 +122,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -152,15 +161,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -168,8 +168,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -252,62 +252,62 @@
     <author>build_spreadsheet.py</author>
   </authors>
   <commentList>
-    <comment ref="O6" authorId="0" shapeId="0">
+    <comment ref="U6" authorId="0" shapeId="0">
       <text>
         <t>DRAM-bound (DRAM 94% busy; SM 5%, L1/L2 94%): data rate 21 / 18.98 Gbps = 1.11x.</t>
       </text>
     </comment>
-    <comment ref="O7" authorId="0" shapeId="0">
+    <comment ref="U7" authorId="0" shapeId="0">
       <text>
         <t>Kernels overlap (their summed ncu time is 105% of this time), so all of it scales with the kernels' 1.11x.</t>
       </text>
     </comment>
-    <comment ref="O9" authorId="0" shapeId="0">
+    <comment ref="U9" authorId="0" shapeId="0">
       <text>
         <t>SM-bound (SM 80% busy; L1/L2 39%, DRAM 0%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
-    <comment ref="O10" authorId="0" shapeId="0">
+    <comment ref="U10" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 95% of the RTX 3090 time and predicted 2.29x faster; the other 5% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="O12" authorId="0" shapeId="0">
+    <comment ref="U12" authorId="0" shapeId="0">
       <text>
         <t>L1/L2-bound (L1/L2 96% busy; SM 7%, DRAM 38%): assumed to scale with SMs x clock, 2.32x.</t>
       </text>
     </comment>
-    <comment ref="O13" authorId="0" shapeId="0">
+    <comment ref="U13" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 70% of the RTX 3090 time and predicted 2.29x faster; the other 30% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="O15" authorId="0" shapeId="0">
+    <comment ref="U15" authorId="0" shapeId="0">
       <text>
         <t>DRAM-bound (DRAM 96% busy; SM 10%, L1/L2 96%): data rate 21 / 18.98 Gbps = 1.11x.</t>
       </text>
     </comment>
-    <comment ref="O16" authorId="0" shapeId="0">
+    <comment ref="U16" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="O18" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <t>SM-bound (SM 81% busy; L1/L2 76%, DRAM 26%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
-    <comment ref="O19" authorId="0" shapeId="0">
+    <comment ref="U19" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 10% of the RTX 3090 time and predicted 2.33x faster; the other 90% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="O21" authorId="0" shapeId="0">
+    <comment ref="U21" authorId="0" shapeId="0">
       <text>
         <t>DRAM-bound (DRAM 88% busy; SM 3%, L1/L2 88%): data rate 21 / 18.98 Gbps = 1.11x.</t>
       </text>
     </comment>
-    <comment ref="O22" authorId="0" shapeId="0">
+    <comment ref="U22" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
       </text>
@@ -605,26 +605,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q22"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="14" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="25" max="25"/>
+    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="11" customWidth="1" min="27" max="27"/>
+    <col width="70" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -634,14 +645,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB), binaries built with CUDA 13.3 GPU (outputs in rtx3090/). Times in microseconds (lower is better). Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so ncu kernel times barely change with launch mode; the CUDA Graph benefit (launch overhead) shows in end-to-end rows. SOTA = the fastest implementation found (&lt;name&gt;_sota.cu), same work per iteration, launched whichever way is fastest; SOTA speedup = Graph / SOTA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB), binaries built with CUDA 13.3 (outputs in rtx3090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Workload</t>
@@ -669,44 +680,60 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>CUDA Graph</t>
+          <t>Direct launch (no graph)</t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Direct launch (no graph)</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>SOTA (state of the art)</t>
-        </is>
-      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>CUDA Graph</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Agentic optimized (formerly SOTA)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="inlineStr">
         <is>
           <t>Graph speedup
 (Direct / Graph)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>SOTA speedup
-(Graph / SOTA)</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Agentic optimized speedup
+(Graph / Agentic)</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration / per iteration in batch
+(launch cost a batch amortizes)</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n"/>
+      <c r="AA4" s="3" t="n"/>
+      <c r="AB4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
@@ -714,52 +741,115 @@
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Time (us)</t>
+          <t>Full batch (ms)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Time (us)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch (ms)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Time (us)</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch (ms)</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="O5" s="3" t="n"/>
-      <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="n"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration</t>
+        </is>
+      </c>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="inlineStr">
+        <is>
+          <t>Direct</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>Graph</t>
+        </is>
+      </c>
+      <c r="AA5" s="3" t="inlineStr">
+        <is>
+          <t>Agentic</t>
+        </is>
+      </c>
+      <c r="AB5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -784,58 +874,92 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F6" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>630.155</v>
+      </c>
+      <c r="I6" s="8" t="inlineStr">
+        <is>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="n">
         <v>629.2910000000001</v>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>nsys-b1024-graph-20261014-215130.sqlite</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="n">
-        <v>630.155</v>
-      </c>
-      <c r="J6" s="9" t="inlineStr">
-        <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>nsys-b1024-direct-20261014-215130.sqlite</t>
-        </is>
-      </c>
-      <c r="L6" s="10" t="n">
+      <c r="O6" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R6" s="13" t="n">
         <v>931.797</v>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="S6" s="14" t="inlineStr">
         <is>
           <t>ncu-sota-large-b1024-graph-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N6" s="11" t="inlineStr">
-        <is>
-          <t>nsys-sota-b1024-graph-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O6" s="12">
-        <f>IF(AND(ISNUMBER(F6),ISNUMBER(I6)),I6/F6,"")</f>
-        <v/>
-      </c>
-      <c r="P6" s="12" t="n">
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c_sota-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="n"/>
+      <c r="V6" s="15" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="W6" s="15" t="n"/>
+      <c r="X6" s="15" t="n">
         <v>1.43</v>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
-        <is>
-          <t>Largest kernel (47% of serialized kernel time under ncu; rmsnorm 20%, softmax 33%). It is a matrix-vector product, so its time does not grow with batch; the three kernels run concurrently on separate streams, so their times overlap. 49% of the whole-application time. SOTA (launch=graph): one fused kernel (llama2c_sota_kernel, one block per 64 KiB row, each row read once from registers) computes rmsnorm, softmax and the matmul, so its time is compared with the three graph kernels' summed ncu time (1,332.8 us).</t>
+      <c r="Y6" s="15" t="n"/>
+      <c r="Z6" s="15" t="n"/>
+      <c r="AA6" s="15" t="n"/>
+      <c r="AB6" s="5" t="inlineStr">
+        <is>
+          <t>Largest kernel (47% of serialized kernel time under ncu; rmsnorm 20%, softmax 33%). It is a matrix-vector product, so its time does not grow with batch; the three kernels run concurrently on separate streams, so their times overlap. 50% of the whole-application time per iteration. Agentic optimized (launch=graph): one fused kernel (llama2c_sota_kernel, one block per 64 KiB row, each row read once from registers) computes rmsnorm, softmax and the matmul, so its time is compared with the three graph kernels' summed ncu time (1,332.8 us).</t>
         </is>
       </c>
     </row>
@@ -862,46 +986,78 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (cudaEvent)</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>1272.245</v>
-      </c>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>nsys-b1024-graph-20261014-215130.sqlite</t>
-        </is>
-      </c>
-      <c r="I7" s="8" t="n">
-        <v>1271.815</v>
-      </c>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>nsys-b1024-direct-20261014-215130.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>63.608</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>1272.156</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1274.272</v>
+      </c>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="n">
+        <v>63.528</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>926.629</v>
-      </c>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="11" t="inlineStr">
-        <is>
-          <t>nsys-sota-b1024-graph-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O7" s="12">
-        <f>IF(AND(ISNUMBER(F7),ISNUMBER(I7)),I7/F7,"")</f>
-        <v/>
-      </c>
-      <c r="P7" s="12" t="n">
-        <v>1.373</v>
-      </c>
-      <c r="Q7" s="5" t="inlineStr">
-        <is>
-          <t>Mean of 3 interleaved trials from the GPU-filling sweep; no per-iteration copies. The nsys traces rerun this configuration (1274.5 / 1272.5 us per iteration). SOTA (launch=graph): mean of 3 runs of llama2c_sota (cudaEvent), the same device-resident nocopy configuration.</t>
+        <v>1270.558</v>
+      </c>
+      <c r="M7" s="10" t="n">
+        <v>1275.408</v>
+      </c>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P7" s="13" t="n">
+        <v>46.333</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>926.653</v>
+      </c>
+      <c r="R7" s="13" t="n">
+        <v>927.744</v>
+      </c>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-llama2c_sota-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U7" s="15" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="V7" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W7" s="15" t="n">
+        <v>1.371</v>
+      </c>
+      <c r="X7" s="15" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="Y7" s="15" t="n">
+        <v>1.002</v>
+      </c>
+      <c r="Z7" s="15" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="AA7" s="15" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AB7" s="5" t="inlineStr">
+        <is>
+          <t>One iteration: rmsnorm + softmax + matmul on device-resident data, no per-iteration copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=graph): llama2c_sota, the same device-resident nocopy configuration, one fused kernel per iteration.</t>
         </is>
       </c>
     </row>
@@ -928,58 +1084,92 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>8174.176</v>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="n">
         <v>8174.304</v>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="N9" s="11" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>nsys-msa_optimized_large-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I9" s="8" t="n">
-        <v>8174.176</v>
-      </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>nsys-msa_optimized_large-direct-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="L9" s="10" t="n">
+      <c r="O9" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R9" s="13" t="n">
         <v>4140.032</v>
       </c>
-      <c r="M9" s="11" t="inlineStr">
+      <c r="S9" s="14" t="inlineStr">
         <is>
           <t>ncu-all-kernels-msa_sota_large_1chunk-direct-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>nsys-msa_sota_large-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O9" s="12">
-        <f>IF(AND(ISNUMBER(F9),ISNUMBER(I9)),I9/F9,"")</f>
-        <v/>
-      </c>
-      <c r="P9" s="12" t="n">
+      <c r="T9" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_sota_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U9" s="15" t="n"/>
+      <c r="V9" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" s="15" t="n"/>
+      <c r="X9" s="15" t="n">
         <v>2.029</v>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
-        <is>
-          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). 92% of the whole-application time. SOTA (launch=direct): msa_sota_attention_kernel (13-way context split, 8 queries per thread) with the projections folded into its loads and the split merge and statistics into its last block. msa_sota_large runs it as 13 concurrent launches, one per imu copy chunk, which ncu would serialize, so ncu profiles msa_sota_large_1chunk, the same kernel as one launch. Compared with the four graph kernels' summed ncu time (8,400.5 us).</t>
+      <c r="Y9" s="15" t="n"/>
+      <c r="Z9" s="15" t="n"/>
+      <c r="AA9" s="15" t="n"/>
+      <c r="AB9" s="5" t="inlineStr">
+        <is>
+          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). 93% of the whole-application time per iteration. Agentic optimized (launch=direct): msa_sota_attention_kernel (13-way context split, 8 queries per thread) with the projections folded into its loads and the split merge and statistics into its last block. msa_sota_large runs it as 13 concurrent launches, one per imu copy chunk, which ncu would serialize, so ncu profiles msa_sota_large_1chunk, the same kernel as one launch. Compared with the four graph kernels' summed ncu time (8,400.5 us).</t>
         </is>
       </c>
     </row>
@@ -1006,46 +1196,78 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (cudaEvent)</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="n">
-        <v>8858.52</v>
-      </c>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>nsys-msa_optimized_large-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>8847.110000000001</v>
-      </c>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>nsys-msa_optimized_large-direct-20261015-224015.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>441.032</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>8820.639999999999</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>8886.379999999999</v>
+      </c>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>440.465</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>4293.51</v>
-      </c>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="11" t="inlineStr">
-        <is>
-          <t>nsys-msa_sota_large-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O10" s="12">
-        <f>IF(AND(ISNUMBER(F10),ISNUMBER(I10)),I10/F10,"")</f>
-        <v/>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>2.063</v>
-      </c>
-      <c r="Q10" s="5" t="inlineStr">
-        <is>
-          <t>benchmark.py: median of 5 runs, random inputs, both launch modes. Includes H2D input and D2H output copies. SOTA (launch=direct): msa_sota in the same benchmark.py runs, rotating over 3 random input sets; output written straight to pinned host memory.</t>
+        <v>8809.299999999999</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>8817.58</v>
+      </c>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>214.376</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>4287.52</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>4283.39</v>
+      </c>
+      <c r="S10" s="18" t="n"/>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_sota_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="V10" s="15" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="W10" s="15" t="n">
+        <v>2.055</v>
+      </c>
+      <c r="X10" s="15" t="n">
+        <v>2.059</v>
+      </c>
+      <c r="Y10" s="15" t="n">
+        <v>1.007</v>
+      </c>
+      <c r="Z10" s="15" t="n">
+        <v>1.001</v>
+      </c>
+      <c r="AA10" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>msa_optimized_large on random inputs, including the H2D input and D2H output copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): msa_sota_large, rotating over 3 random input sets; output written straight to pinned host memory.</t>
         </is>
       </c>
     </row>
@@ -1072,58 +1294,92 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>262.621</v>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="10" t="n">
         <v>262.754</v>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="N12" s="11" t="inlineStr">
         <is>
           <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>nsys-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="n">
-        <v>262.621</v>
-      </c>
-      <c r="J12" s="9" t="inlineStr">
-        <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>nsys-direct-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="L12" s="10" t="n">
+      <c r="O12" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="13" t="n">
         <v>155.326</v>
       </c>
-      <c r="M12" s="11" t="inlineStr">
+      <c r="S12" s="14" t="inlineStr">
         <is>
           <t>ncu-pagerank-sota-direct-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N12" s="11" t="inlineStr">
-        <is>
-          <t>nsys-sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O12" s="12">
-        <f>IF(AND(ISNUMBER(F12),ISNUMBER(I12)),I12/F12,"")</f>
-        <v/>
-      </c>
-      <c r="P12" s="12" t="n">
+      <c r="T12" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U12" s="15" t="n"/>
+      <c r="V12" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W12" s="15" t="n"/>
+      <c r="X12" s="15" t="n">
         <v>1.692</v>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
-        <is>
-          <t>Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks of ~41 us each. 19 full iterations = 65% of the whole-application time. SOTA (launch=direct): binned_update_kernel, summed over iterations 1-19 / 19: a cooperative pull over destination parts that fit in shared memory, with edges sorted by source sector on the GPU during the upload (5.4M instead of 16.8M gathered sectors per iteration).</t>
+      <c r="Y12" s="15" t="n"/>
+      <c r="Z12" s="15" t="n"/>
+      <c r="AA12" s="15" t="n"/>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks of ~41 us each. 19 full iterations = 65% of the whole-application time per iteration. Agentic optimized (launch=direct): binned_update_kernel, summed over iterations 1-19 / 19: a cooperative pull over destination parts that fit in shared memory, with edges sorted by source sector on the GPU during the upload (5.4M instead of 16.8M gathered sectors per iteration).</t>
         </is>
       </c>
     </row>
@@ -1150,46 +1406,78 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>7648.935</v>
-      </c>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="7" t="inlineStr">
-        <is>
-          <t>nsys-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="n">
-        <v>7678.598</v>
-      </c>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>nsys-direct-20261015-224015.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>385.722</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>7714.44</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>7662</v>
+      </c>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K13" s="10" t="n">
+        <v>382.343</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>6019.149</v>
-      </c>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="11" t="inlineStr">
-        <is>
-          <t>nsys-sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O13" s="12">
-        <f>IF(AND(ISNUMBER(F13),ISNUMBER(I13)),I13/F13,"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="12" t="n">
-        <v>1.271</v>
-      </c>
-      <c r="Q13" s="5" t="inlineStr">
-        <is>
-          <t>Median GPU span of the 1292 / 1251 (graph / direct) pagerank.full NVTX ranges in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. The binary's own cudaEvent timing in the same runs: 7.658 / 7.686 ms (graph / direct) with transfers, 4.862 / 4.885 ms compute only. SOTA (launch=direct): median GPU span of the 1320 pagerank.full NVTX ranges, rotating over 3 inputs (the benchmark graph and two random graphs of the same size); includes the on-GPU edge sort.</t>
+        <v>7646.86</v>
+      </c>
+      <c r="M13" s="10" t="n">
+        <v>7642</v>
+      </c>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>297.939</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>5958.78</v>
+      </c>
+      <c r="R13" s="13" t="n">
+        <v>5932</v>
+      </c>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-pagerank_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U13" s="15" t="n">
+        <v>1.009</v>
+      </c>
+      <c r="V13" s="15" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="W13" s="15" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="X13" s="15" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="Y13" s="15" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="Z13" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AA13" s="15" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="AB13" s="5" t="inlineStr">
+        <is>
+          <t>One iteration is one PageRank run: the CSR graph uploaded from pinned memory in 8 chunks overlapped with the first of 20 iterations, then the scores downloaded. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs (the benchmark graph and two random graphs of the same size); includes the on-GPU edge sort.</t>
         </is>
       </c>
     </row>
@@ -1216,58 +1504,92 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>384.32</v>
+      </c>
+      <c r="I15" s="8" t="inlineStr">
+        <is>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J15" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="10" t="n">
         <v>384.288</v>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="N15" s="11" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I15" s="8" t="n">
-        <v>384.32</v>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse-direct-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="L15" s="10" t="n">
+      <c r="O15" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R15" s="13" t="n">
         <v>386.24</v>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="S15" s="14" t="inlineStr">
         <is>
           <t>ncu-anomaly_mse_sota-graph-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse_sota-graph-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O15" s="12">
-        <f>IF(AND(ISNUMBER(F15),ISNUMBER(I15)),I15/F15,"")</f>
-        <v/>
-      </c>
-      <c r="P15" s="12" t="n">
+      <c r="T15" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U15" s="15" t="n"/>
+      <c r="V15" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" s="15" t="n"/>
+      <c r="X15" s="15" t="n">
         <v>1.003</v>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
-        <is>
-          <t>3% of the whole-application time. SOTA (launch=graph): mse_sota_kernel, one single-pass reduction (the last block finishes the sum), compared with mse_partial_kernel + mse_finalize_kernel.</t>
+      <c r="Y15" s="15" t="n"/>
+      <c r="Z15" s="15" t="n"/>
+      <c r="AA15" s="15" t="n"/>
+      <c r="AB15" s="5" t="inlineStr">
+        <is>
+          <t>3% of the whole-application time per iteration. Agentic optimized (launch=graph): mse_sota_kernel, one single-pass reduction (the last block finishes the sum), compared with mse_partial_kernel + mse_finalize_kernel.</t>
         </is>
       </c>
     </row>
@@ -1294,46 +1616,78 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>14200.376</v>
-      </c>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I16" s="8" t="n">
-        <v>14212.283</v>
-      </c>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse-direct-20261015-224015.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>708.449</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>14168.98</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>14165.36</v>
+      </c>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="n">
+        <v>708.564</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>13835.962</v>
-      </c>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="11" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse_sota-graph-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O16" s="12">
-        <f>IF(AND(ISNUMBER(F16),ISNUMBER(I16)),I16/F16,"")</f>
-        <v/>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>1.026</v>
-      </c>
-      <c r="Q16" s="5" t="inlineStr">
-        <is>
-          <t>Median GPU span of the 20 / 20 (graph / direct) anomaly.end_to_end NVTX ranges in the nsys traces. SOTA (launch=graph): median GPU span of the 20 anomaly.end_to_end NVTX ranges, rotating over 3 inputs; the float input is copied in shrinking chunks while a second stream reduces each chunk as it lands; the result is written straight to pinned host memory.</t>
+        <v>14171.28</v>
+      </c>
+      <c r="M16" s="10" t="n">
+        <v>14163.28</v>
+      </c>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P16" s="13" t="n">
+        <v>691.636</v>
+      </c>
+      <c r="Q16" s="13" t="n">
+        <v>13832.72</v>
+      </c>
+      <c r="R16" s="13" t="n">
+        <v>13830.608</v>
+      </c>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" s="15" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="X16" s="15" t="n">
+        <v>1.024</v>
+      </c>
+      <c r="Y16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AA16" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="5" t="inlineStr">
+        <is>
+          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=graph): rotating over 3 inputs; the float input is copied in shrinking chunks while a second stream reduces each chunk as it lands; the result is written straight to pinned host memory.</t>
         </is>
       </c>
     </row>
@@ -1360,58 +1714,92 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>1119.968</v>
+      </c>
+      <c r="I18" s="8" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J18" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="n">
         <v>1120.224</v>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="N18" s="11" t="inlineStr">
         <is>
           <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="n">
-        <v>1119.968</v>
-      </c>
-      <c r="J18" s="9" t="inlineStr">
-        <is>
-          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess-direct-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="L18" s="10" t="n">
+      <c r="O18" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="13" t="n">
         <v>323.072</v>
       </c>
-      <c r="M18" s="11" t="inlineStr">
+      <c r="S18" s="14" t="inlineStr">
         <is>
           <t>ncu-kws_postprocess_sota-direct-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N18" s="11" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess_sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O18" s="12">
-        <f>IF(AND(ISNUMBER(F18),ISNUMBER(I18)),I18/F18,"")</f>
-        <v/>
-      </c>
-      <c r="P18" s="12" t="n">
+      <c r="T18" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U18" s="15" t="n"/>
+      <c r="V18" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n">
         <v>3.467</v>
       </c>
-      <c r="Q18" s="5" t="inlineStr">
-        <is>
-          <t>Only kernel in the application. 10% of the whole-application time. SOTA (launch=direct): kws_postprocess_sota_kernel on device buffers (kernels-only), one row per thread with rows staged through shared memory for coalesced 16 B loads and stores.</t>
+      <c r="Y18" s="15" t="n"/>
+      <c r="Z18" s="15" t="n"/>
+      <c r="AA18" s="15" t="n"/>
+      <c r="AB18" s="5" t="inlineStr">
+        <is>
+          <t>Only kernel in the application. 10% of the whole-application time per iteration. Agentic optimized (launch=direct): kws_postprocess_sota_kernel on device buffers (kernels-only), one row per thread with rows staged through shared memory for coalesced 16 B loads and stores.</t>
         </is>
       </c>
     </row>
@@ -1438,46 +1826,78 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>11451.704</v>
-      </c>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I19" s="8" t="n">
-        <v>11446.14</v>
-      </c>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="9" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess-direct-20261015-224015.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>568.751</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>11375.02</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>11370.864</v>
+      </c>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K19" s="10" t="n">
+        <v>568.535</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>8662.050999999999</v>
-      </c>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="11" t="inlineStr">
-        <is>
-          <t>nsys-kws_postprocess_sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O19" s="12">
-        <f>IF(AND(ISNUMBER(F19),ISNUMBER(I19)),I19/F19,"")</f>
-        <v/>
-      </c>
-      <c r="P19" s="12" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="Q19" s="5" t="inlineStr">
-        <is>
-          <t>Median GPU span of the 20 / 20 (graph / direct) kws.end_to_end NVTX ranges in the nsys traces. SOTA (launch=direct): median GPU span of the 20 kws.end_to_end NVTX ranges, rotating over 3 inputs; one zero-copy kernel reads the int8 rows from and writes the probabilities and argmax to mapped pinned host memory, so both PCIe directions stream at once.</t>
+        <v>11370.7</v>
+      </c>
+      <c r="M19" s="10" t="n">
+        <v>11376.016</v>
+      </c>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P19" s="13" t="n">
+        <v>433.252</v>
+      </c>
+      <c r="Q19" s="13" t="n">
+        <v>8665.040000000001</v>
+      </c>
+      <c r="R19" s="13" t="n">
+        <v>8654.575999999999</v>
+      </c>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" s="15" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="X19" s="15" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="Y19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AB19" s="5" t="inlineStr">
+        <is>
+          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs; one zero-copy kernel reads the int8 rows from and writes the probabilities and argmax to mapped pinned host memory, so both PCIe directions stream at once.</t>
         </is>
       </c>
     </row>
@@ -1504,58 +1924,92 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="n">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>659.456</v>
+      </c>
+      <c r="I21" s="8" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="n">
         <v>664.96</v>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="N21" s="11" t="inlineStr">
         <is>
           <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>659.456</v>
-      </c>
-      <c r="J21" s="9" t="inlineStr">
-        <is>
-          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess-direct-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="L21" s="10" t="n">
+      <c r="O21" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="13" t="n">
         <v>634.72</v>
       </c>
-      <c r="M21" s="11" t="inlineStr">
+      <c r="S21" s="14" t="inlineStr">
         <is>
           <t>ncu-vww_preprocess_sota-direct-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess_sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O21" s="12">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER(I21)),I21/F21,"")</f>
-        <v/>
-      </c>
-      <c r="P21" s="12" t="n">
+      <c r="T21" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U21" s="15" t="n"/>
+      <c r="V21" s="15" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="W21" s="15" t="n"/>
+      <c r="X21" s="15" t="n">
         <v>1.048</v>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
-        <is>
-          <t>Only kernel in the application. 3% of the whole-application time. SOTA (launch=direct): vww_preprocess_sota_kernel on device buffers (kernels-only), four 16 B vectors per thread.</t>
+      <c r="Y21" s="15" t="n"/>
+      <c r="Z21" s="15" t="n"/>
+      <c r="AA21" s="15" t="n"/>
+      <c r="AB21" s="5" t="inlineStr">
+        <is>
+          <t>Only kernel in the application. 3% of the whole-application time per iteration. Agentic optimized (launch=direct): vww_preprocess_sota_kernel on device buffers (kernels-only), four 16 B vectors per thread.</t>
         </is>
       </c>
     </row>
@@ -1582,155 +2036,224 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="n">
-        <v>21910.811</v>
-      </c>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess-graph-20261015-224015.sqlite</t>
-        </is>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>21886.066</v>
-      </c>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess-direct-20261015-224015.sqlite</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1094.1</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>21882</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>21881.408</v>
+      </c>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="n">
+        <v>1093.995</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>12467.632</v>
-      </c>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="11" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess_sota-direct-20261016-145900.sqlite</t>
-        </is>
-      </c>
-      <c r="O22" s="12">
-        <f>IF(AND(ISNUMBER(F22),ISNUMBER(I22)),I22/F22,"")</f>
-        <v/>
-      </c>
-      <c r="P22" s="12" t="n">
-        <v>1.757</v>
-      </c>
-      <c r="Q22" s="5" t="inlineStr">
-        <is>
-          <t>Median GPU span of the 20 / 20 (graph / direct) vww.end_to_end NVTX ranges in the nsys traces. SOTA (launch=direct): median GPU span of the 20 vww.end_to_end NVTX ranges, rotating over 3 inputs; 64 chunks of 4 MiB on separate copy-in, compute and copy-out streams, so H2D and D2H overlap.</t>
+        <v>21879.9</v>
+      </c>
+      <c r="M22" s="10" t="n">
+        <v>21880.512</v>
+      </c>
+      <c r="N22" s="17" t="n"/>
+      <c r="O22" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P22" s="13" t="n">
+        <v>613.24</v>
+      </c>
+      <c r="Q22" s="13" t="n">
+        <v>12264.8</v>
+      </c>
+      <c r="R22" s="13" t="n">
+        <v>12253.552</v>
+      </c>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" s="15" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="X22" s="15" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="Y22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs; 64 chunks of 4 MiB on separate copy-in, compute and copy-out streams, so H2D and D2H overlap.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="A2:AB2"/>
+    <mergeCell ref="P4:T4"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="Q4:Q5"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="O4:O5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="AB4:AB5"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="U4:V4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R6" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S6" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T6" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K9" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K18" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K21" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1742,27 +2265,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R28"/>
+  <dimension ref="A1:Y28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
     <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="14" customWidth="1" min="17" max="17"/>
-    <col width="60" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="11" customWidth="1" min="21" max="21"/>
+    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="11" customWidth="1" min="23" max="23"/>
+    <col width="11" customWidth="1" min="24" max="24"/>
+    <col width="70" customWidth="1" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1772,14 +2302,14 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GPU: NVIDIA GeForce RTX 4090 (sm_89, 24 GB), binaries built with CUDA 12.5 GPU (outputs in rtx4090/). Times in microseconds (lower is better). Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so ncu kernel times barely change with launch mode; the CUDA Graph benefit (launch overhead) shows in end-to-end rows. SOTA = the fastest implementation found (&lt;name&gt;_sota.cu), same work per iteration, launched whichever way is fastest; SOTA speedup = Graph / SOTA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>GPU: NVIDIA GeForce RTX 4090 (sm_89, 24 GB), binaries built with CUDA 12.5 (outputs in rtx4090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Workload</t>
@@ -1807,44 +2337,52 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>CUDA Graph</t>
+          <t>Direct launch (no graph)</t>
         </is>
       </c>
       <c r="G4" s="3" t="n"/>
       <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>Direct launch (no graph)</t>
-        </is>
-      </c>
+      <c r="I4" s="3" t="n"/>
       <c r="J4" s="3" t="n"/>
-      <c r="K4" s="3" t="n"/>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>SOTA (state of the art)</t>
-        </is>
-      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>CUDA Graph</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="n"/>
       <c r="M4" s="3" t="n"/>
       <c r="N4" s="3" t="n"/>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>Speedup vs RTX 3090 (CUDA Graph time)</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>SOTA speedup
-(Graph / SOTA)</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="n"/>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Agentic optimized (formerly SOTA)</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n"/>
+      <c r="R4" s="3" t="n"/>
+      <c r="S4" s="3" t="n"/>
+      <c r="T4" s="3" t="n"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Speedup vs RTX 3090
+(CUDA Graph)</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="n"/>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>Agentic optimized speedup
+(Graph / Agentic)</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="n"/>
+      <c r="Y4" s="3" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="n"/>
       <c r="B5" s="3" t="n"/>
       <c r="C5" s="3" t="n"/>
@@ -1852,62 +2390,101 @@
       <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Time (us)</t>
+          <t>Full batch (ms)</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Time (us)</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch (ms)</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
         <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="O5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Time (us)</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch (ms)</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Per iteration in batch (us)</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration (us)</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t>ncu-rep</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
+      <c r="T5" s="3" t="inlineStr">
         <is>
           <t>nsys sqlite</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Predicted</t>
         </is>
       </c>
-      <c r="P5" s="3" t="inlineStr">
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t>Measured
 (RTX 3090 / RTX 4090)</t>
         </is>
       </c>
-      <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
+      <c r="W5" s="3" t="inlineStr">
+        <is>
+          <t>Full batch</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>Single iteration</t>
+        </is>
+      </c>
+      <c r="Y5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1932,51 +2509,78 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G6" s="13" t="n"/>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="16" t="n"/>
+      <c r="J6" s="8" t="inlineStr">
+        <is>
+          <t>nsys-node-direct-20261015-091935.sqlite</t>
+        </is>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="9" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="N6" s="17" t="n"/>
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>nsys-node-graph-20261015-091930.sqlite</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>pending (ncu not run yet)</t>
-        </is>
-      </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>nsys-node-direct-20261015-091935.sqlite</t>
-        </is>
-      </c>
-      <c r="L6" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M6" s="15" t="n"/>
-      <c r="N6" s="15" t="n"/>
-      <c r="O6" s="12" t="n">
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q6" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R6" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S6" s="18" t="n"/>
+      <c r="T6" s="18" t="n"/>
+      <c r="U6" s="15" t="n">
         <v>1.106</v>
       </c>
-      <c r="P6" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F6),ISNUMBER(F6)),'RTX 3090'!F6/F6,"pending")</f>
+      <c r="V6" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M6),ISNUMBER(M6)),'RTX 3090'!M6/M6,"pending")</f>
         <v/>
       </c>
-      <c r="Q6" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
+      <c r="W6" s="15" t="n"/>
+      <c r="X6" s="15" t="n"/>
+      <c r="Y6" s="5" t="inlineStr">
         <is>
           <t>Largest kernel. It is a matrix-vector product, so its time does not grow with batch; the three kernels run concurrently on separate streams, so their times overlap.</t>
         </is>
@@ -2008,46 +2612,65 @@
           <t>Iteration time (cudaEvent)</t>
         </is>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>963.302</v>
+      </c>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="n"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>nsys-node-direct-20261015-091935.sqlite</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L7" s="10" t="n">
         <v>962.42</v>
       </c>
-      <c r="G7" s="13" t="n"/>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="11" t="inlineStr">
         <is>
           <t>nsys-node-graph-20261015-091930.sqlite</t>
         </is>
       </c>
-      <c r="I7" s="8" t="n">
-        <v>963.302</v>
-      </c>
-      <c r="J7" s="14" t="n"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>nsys-node-direct-20261015-091935.sqlite</t>
-        </is>
-      </c>
-      <c r="L7" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M7" s="15" t="n"/>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="12" t="n">
+      <c r="P7" s="18" t="n"/>
+      <c r="Q7" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R7" s="18" t="n"/>
+      <c r="S7" s="18" t="n"/>
+      <c r="T7" s="18" t="n"/>
+      <c r="U7" s="15" t="n">
         <v>1.106</v>
       </c>
-      <c r="P7" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F7),ISNUMBER(F7)),'RTX 3090'!F7/F7,"pending")</f>
+      <c r="V7" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L7),ISNUMBER(L7)),'RTX 3090'!L7/L7,"pending")</f>
         <v/>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>Mean of 3 interleaved trials from the GPU-filling sweep; no per-iteration copies. The nsys traces rerun this configuration (963.0 / 962.1 us per iteration).</t>
+      <c r="W7" s="15" t="n"/>
+      <c r="X7" s="15" t="n"/>
+      <c r="Y7" s="5" t="inlineStr">
+        <is>
+          <t>Mean of 3 interleaved trials from the GPU-filling sweep; no per-iteration copies. The nsys traces rerun this configuration (963.0 / 962.1 us per iteration, graph / direct).</t>
         </is>
       </c>
     </row>
@@ -2074,47 +2697,74 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="11" t="inlineStr">
         <is>
           <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M9" s="15" t="n"/>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="12" t="n">
+      <c r="P9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q9" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R9" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S9" s="18" t="n"/>
+      <c r="T9" s="18" t="n"/>
+      <c r="U9" s="15" t="n">
         <v>2.327</v>
       </c>
-      <c r="P9" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F9),ISNUMBER(F9)),'RTX 3090'!F9/F9,"pending")</f>
+      <c r="V9" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M9),ISNUMBER(M9)),'RTX 3090'!M9/M9,"pending")</f>
         <v/>
       </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R9" s="5" t="inlineStr">
+      <c r="W9" s="15" t="n"/>
+      <c r="X9" s="15" t="n"/>
+      <c r="Y9" s="5" t="inlineStr">
         <is>
           <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style).</t>
         </is>
@@ -2146,42 +2796,53 @@
           <t>Iteration time (cudaEvent)</t>
         </is>
       </c>
-      <c r="F10" s="6" t="n">
+      <c r="F10" s="16" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="n"/>
+      <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L10" s="10" t="n">
         <v>3835.57</v>
       </c>
-      <c r="G10" s="13" t="n"/>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N10" s="17" t="n"/>
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J10" s="14" t="n"/>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M10" s="15" t="n"/>
-      <c r="N10" s="15" t="n"/>
-      <c r="O10" s="12" t="n">
-        <v>2.148</v>
-      </c>
-      <c r="P10" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F10),ISNUMBER(F10)),'RTX 3090'!F10/F10,"pending")</f>
+      <c r="P10" s="18" t="n"/>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R10" s="18" t="n"/>
+      <c r="S10" s="18" t="n"/>
+      <c r="T10" s="18" t="n"/>
+      <c r="U10" s="15" t="n">
+        <v>2.162</v>
+      </c>
+      <c r="V10" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L10),ISNUMBER(L10)),'RTX 3090'!L10/L10,"pending")</f>
         <v/>
       </c>
-      <c r="Q10" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
+      <c r="W10" s="15" t="n"/>
+      <c r="X10" s="15" t="n"/>
+      <c r="Y10" s="5" t="inlineStr">
         <is>
           <t>benchmark.py: median of 5 runs, random inputs, CUDA graph only. Includes H2D input and D2H output copies.</t>
         </is>
@@ -2210,47 +2871,74 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G12" s="13" t="n"/>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="11" t="inlineStr">
         <is>
           <t>nsys-20261015-091708.sqlite</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="n"/>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M12" s="15" t="n"/>
-      <c r="N12" s="15" t="n"/>
-      <c r="O12" s="12" t="n">
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q12" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R12" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="n"/>
+      <c r="U12" s="15" t="n">
         <v>2.325</v>
       </c>
-      <c r="P12" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F12),ISNUMBER(F12)),'RTX 3090'!F12/F12,"pending")</f>
+      <c r="V12" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M12),ISNUMBER(M12)),'RTX 3090'!M12/M12,"pending")</f>
         <v/>
       </c>
-      <c r="Q12" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R12" s="5" t="inlineStr">
+      <c r="W12" s="15" t="n"/>
+      <c r="X12" s="15" t="n"/>
+      <c r="Y12" s="5" t="inlineStr">
         <is>
           <t>Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks.</t>
         </is>
@@ -2282,42 +2970,53 @@
           <t>Iteration time (nsys)</t>
         </is>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="16" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="n"/>
+      <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>5754.945</v>
       </c>
-      <c r="G13" s="13" t="n"/>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="11" t="inlineStr">
         <is>
           <t>nsys-20261015-091708.sqlite</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M13" s="15" t="n"/>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="12" t="n">
-        <v>1.647</v>
-      </c>
-      <c r="P13" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F13),ISNUMBER(F13)),'RTX 3090'!F13/F13,"pending")</f>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R13" s="18" t="n"/>
+      <c r="S13" s="18" t="n"/>
+      <c r="T13" s="18" t="n"/>
+      <c r="U13" s="15" t="n">
+        <v>1.648</v>
+      </c>
+      <c r="V13" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L13),ISNUMBER(L13)),'RTX 3090'!L13/L13,"pending")</f>
         <v/>
       </c>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
+      <c r="W13" s="15" t="n"/>
+      <c r="X13" s="15" t="n"/>
+      <c r="Y13" s="5" t="inlineStr">
         <is>
           <t>Median GPU span of the 1693 graph replays with copies in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
         </is>
@@ -2346,47 +3045,74 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L15" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G15" s="13" t="n"/>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="n"/>
-      <c r="K15" s="14" t="n"/>
-      <c r="L15" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M15" s="15" t="n"/>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="12" t="n">
+      <c r="P15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q15" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R15" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S15" s="18" t="n"/>
+      <c r="T15" s="18" t="n"/>
+      <c r="U15" s="15" t="n">
         <v>1.106</v>
       </c>
-      <c r="P15" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F15),ISNUMBER(F15)),'RTX 3090'!F15/F15,"pending")</f>
+      <c r="V15" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M15),ISNUMBER(M15)),'RTX 3090'!M15/M15,"pending")</f>
         <v/>
       </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R15" s="5" t="inlineStr"/>
+      <c r="W15" s="15" t="n"/>
+      <c r="X15" s="15" t="n"/>
+      <c r="Y15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -2414,42 +3140,53 @@
           <t>Iteration time (nsys)</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="16" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H16" s="16" t="n"/>
+      <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="n">
         <v>13698.465</v>
       </c>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N16" s="17" t="n"/>
+      <c r="O16" s="11" t="inlineStr">
         <is>
           <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J16" s="14" t="n"/>
-      <c r="K16" s="14" t="n"/>
-      <c r="L16" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M16" s="15" t="n"/>
-      <c r="N16" s="15" t="n"/>
-      <c r="O16" s="12" t="n">
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="n"/>
+      <c r="U16" s="15" t="n">
         <v>1.003</v>
       </c>
-      <c r="P16" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F16),ISNUMBER(F16)),'RTX 3090'!F16/F16,"pending")</f>
+      <c r="V16" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L16),ISNUMBER(L16)),'RTX 3090'!L16/L16,"pending")</f>
         <v/>
       </c>
-      <c r="Q16" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R16" s="5" t="inlineStr">
+      <c r="W16" s="15" t="n"/>
+      <c r="X16" s="15" t="n"/>
+      <c r="Y16" s="5" t="inlineStr">
         <is>
           <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
@@ -2478,47 +3215,74 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G18" s="13" t="n"/>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="N18" s="17" t="n"/>
+      <c r="O18" s="11" t="inlineStr">
         <is>
           <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
         </is>
       </c>
-      <c r="I18" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M18" s="15" t="n"/>
-      <c r="N18" s="15" t="n"/>
-      <c r="O18" s="12" t="n">
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R18" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S18" s="18" t="n"/>
+      <c r="T18" s="18" t="n"/>
+      <c r="U18" s="15" t="n">
         <v>2.325</v>
       </c>
-      <c r="P18" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F18),ISNUMBER(F18)),'RTX 3090'!F18/F18,"pending")</f>
+      <c r="V18" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M18),ISNUMBER(M18)),'RTX 3090'!M18/M18,"pending")</f>
         <v/>
       </c>
-      <c r="Q18" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R18" s="5" t="inlineStr">
+      <c r="W18" s="15" t="n"/>
+      <c r="X18" s="15" t="n"/>
+      <c r="Y18" s="5" t="inlineStr">
         <is>
           <t>Only kernel in the application.</t>
         </is>
@@ -2550,42 +3314,53 @@
           <t>Iteration time (nsys)</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="n"/>
+      <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L19" s="10" t="n">
         <v>11226.082</v>
       </c>
-      <c r="G19" s="13" t="n"/>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N19" s="17" t="n"/>
+      <c r="O19" s="11" t="inlineStr">
         <is>
           <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J19" s="14" t="n"/>
-      <c r="K19" s="14" t="n"/>
-      <c r="L19" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M19" s="15" t="n"/>
-      <c r="N19" s="15" t="n"/>
-      <c r="O19" s="12" t="n">
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R19" s="18" t="n"/>
+      <c r="S19" s="18" t="n"/>
+      <c r="T19" s="18" t="n"/>
+      <c r="U19" s="15" t="n">
         <v>1.059</v>
       </c>
-      <c r="P19" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F19),ISNUMBER(F19)),'RTX 3090'!F19/F19,"pending")</f>
+      <c r="V19" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L19),ISNUMBER(L19)),'RTX 3090'!L19/L19,"pending")</f>
         <v/>
       </c>
-      <c r="Q19" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R19" s="5" t="inlineStr">
+      <c r="W19" s="15" t="n"/>
+      <c r="X19" s="15" t="n"/>
+      <c r="Y19" s="5" t="inlineStr">
         <is>
           <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
@@ -2614,47 +3389,74 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="n"/>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L21" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>pending (ncu not run yet)</t>
         </is>
       </c>
-      <c r="G21" s="13" t="n"/>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="N21" s="17" t="n"/>
+      <c r="O21" s="11" t="inlineStr">
         <is>
           <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
         </is>
       </c>
-      <c r="I21" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J21" s="14" t="n"/>
-      <c r="K21" s="14" t="n"/>
-      <c r="L21" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M21" s="15" t="n"/>
-      <c r="N21" s="15" t="n"/>
-      <c r="O21" s="12" t="n">
+      <c r="P21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q21" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R21" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S21" s="18" t="n"/>
+      <c r="T21" s="18" t="n"/>
+      <c r="U21" s="15" t="n">
         <v>1.106</v>
       </c>
-      <c r="P21" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F21),ISNUMBER(F21)),'RTX 3090'!F21/F21,"pending")</f>
+      <c r="V21" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M21),ISNUMBER(M21)),'RTX 3090'!M21/M21,"pending")</f>
         <v/>
       </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R21" s="5" t="inlineStr">
+      <c r="W21" s="15" t="n"/>
+      <c r="X21" s="15" t="n"/>
+      <c r="Y21" s="5" t="inlineStr">
         <is>
           <t>Only kernel in the application.</t>
         </is>
@@ -2686,42 +3488,53 @@
           <t>Iteration time (nsys)</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n">
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H22" s="16" t="n"/>
+      <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="n">
         <v>21789.123</v>
       </c>
-      <c r="G22" s="13" t="n"/>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N22" s="17" t="n"/>
+      <c r="O22" s="11" t="inlineStr">
         <is>
           <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
         </is>
       </c>
-      <c r="I22" s="17" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="J22" s="14" t="n"/>
-      <c r="K22" s="14" t="n"/>
-      <c r="L22" s="18" t="inlineStr">
-        <is>
-          <t>pending (SOTA not profiled yet)</t>
-        </is>
-      </c>
-      <c r="M22" s="15" t="n"/>
-      <c r="N22" s="15" t="n"/>
-      <c r="O22" s="12" t="n">
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R22" s="18" t="n"/>
+      <c r="S22" s="18" t="n"/>
+      <c r="T22" s="18" t="n"/>
+      <c r="U22" s="15" t="n">
         <v>1.003</v>
       </c>
-      <c r="P22" s="12">
-        <f>IF(AND(ISNUMBER('RTX 3090'!F22),ISNUMBER(F22)),'RTX 3090'!F22/F22,"pending")</f>
+      <c r="V22" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L22),ISNUMBER(L22)),'RTX 3090'!L22/L22,"pending")</f>
         <v/>
       </c>
-      <c r="Q22" s="12" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R22" s="5" t="inlineStr">
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n"/>
+      <c r="Y22" s="5" t="inlineStr">
         <is>
           <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
@@ -2764,45 +3577,45 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A26:R26"/>
+    <mergeCell ref="W4:X4"/>
+    <mergeCell ref="A25:Y25"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="P4:T4"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="Q4:Q5"/>
-    <mergeCell ref="R4:R5"/>
+    <mergeCell ref="A28:Y28"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A25:R25"/>
+    <mergeCell ref="E4:E5"/>
     <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="A27:R27"/>
-    <mergeCell ref="A28:R28"/>
-    <mergeCell ref="A2:Q2"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Y4:Y5"/>
+    <mergeCell ref="A27:Y27"/>
+    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="K4:O4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="U4:V4"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I7" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J6" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
@@ -2915,7 +3728,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -2928,20 +3741,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>269.792 us</t>
+          <t>269.056 us</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12.649193</v>
+        <v>12.541522</v>
       </c>
       <c r="F2" t="n">
-        <v>80.729253</v>
+        <v>80.987652</v>
       </c>
       <c r="G2" t="n">
-        <v>80.729253</v>
+        <v>80.987652</v>
       </c>
       <c r="H2" t="n">
-        <v>94.44363800000001</v>
+        <v>94.59914499999999</v>
       </c>
       <c r="I2" t="n">
         <v>100</v>
@@ -2966,7 +3779,7 @@
     <row r="3">
       <c r="A3" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -2979,20 +3792,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>435.168 us</t>
+          <t>434.752 us</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12.880227</v>
+        <v>13.006426</v>
       </c>
       <c r="F3" t="n">
-        <v>82.724726</v>
+        <v>82.874893</v>
       </c>
       <c r="G3" t="n">
-        <v>82.724726</v>
+        <v>82.874893</v>
       </c>
       <c r="H3" t="n">
-        <v>96.83955899999999</v>
+        <v>97.328231</v>
       </c>
       <c r="I3" t="n">
         <v>100</v>
@@ -3017,7 +3830,7 @@
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -3030,20 +3843,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>627.968 us</t>
+          <t>632.608 us</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.98322</v>
+        <v>4.973674</v>
       </c>
       <c r="F4" t="n">
-        <v>94.15696</v>
+        <v>93.453981</v>
       </c>
       <c r="G4" t="n">
-        <v>94.15696</v>
+        <v>93.453981</v>
       </c>
       <c r="H4" t="n">
-        <v>96.47936900000001</v>
+        <v>96.463639</v>
       </c>
       <c r="I4" t="n">
         <v>100</v>
@@ -3068,7 +3881,7 @@
     <row r="5">
       <c r="A5" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -3081,20 +3894,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>267.232 us</t>
+          <t>268.512 us</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.689767</v>
+        <v>12.60658</v>
       </c>
       <c r="F5" t="n">
-        <v>81.42889099999999</v>
+        <v>81.03238399999999</v>
       </c>
       <c r="G5" t="n">
-        <v>81.42889099999999</v>
+        <v>81.03238399999999</v>
       </c>
       <c r="H5" t="n">
-        <v>94.652483</v>
+        <v>94.15025</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
@@ -3119,7 +3932,7 @@
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -3132,20 +3945,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>435.904 us</t>
+          <t>435.328 us</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>12.897291</v>
+        <v>12.920949</v>
       </c>
       <c r="F6" t="n">
-        <v>82.675376</v>
+        <v>82.86177600000001</v>
       </c>
       <c r="G6" t="n">
-        <v>82.675376</v>
+        <v>82.86177600000001</v>
       </c>
       <c r="H6" t="n">
-        <v>97.382305</v>
+        <v>97.4602</v>
       </c>
       <c r="I6" t="n">
         <v>100</v>
@@ -3170,7 +3983,7 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -3183,20 +3996,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>630.624 us</t>
+          <t>629.056 us</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.999857</v>
+        <v>4.985303</v>
       </c>
       <c r="F7" t="n">
-        <v>93.832617</v>
+        <v>94.042863</v>
       </c>
       <c r="G7" t="n">
-        <v>93.832617</v>
+        <v>94.042863</v>
       </c>
       <c r="H7" t="n">
-        <v>96.417575</v>
+        <v>96.527649</v>
       </c>
       <c r="I7" t="n">
         <v>100</v>
@@ -3221,7 +4034,7 @@
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -3234,20 +4047,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>268.608 us</t>
+          <t>267.936 us</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12.569806</v>
+        <v>12.590349</v>
       </c>
       <c r="F8" t="n">
-        <v>81.037284</v>
+        <v>81.259491</v>
       </c>
       <c r="G8" t="n">
-        <v>81.037284</v>
+        <v>81.259491</v>
       </c>
       <c r="H8" t="n">
-        <v>94.103589</v>
+        <v>95.26650600000001</v>
       </c>
       <c r="I8" t="n">
         <v>100</v>
@@ -3272,7 +4085,7 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -3285,20 +4098,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>433.888 us</t>
+          <t>432.128 us</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12.933639</v>
+        <v>12.939862</v>
       </c>
       <c r="F9" t="n">
-        <v>83.02358700000001</v>
+        <v>83.522707</v>
       </c>
       <c r="G9" t="n">
-        <v>83.02358700000001</v>
+        <v>83.522707</v>
       </c>
       <c r="H9" t="n">
-        <v>96.793463</v>
+        <v>97.167548</v>
       </c>
       <c r="I9" t="n">
         <v>100</v>
@@ -3323,7 +4136,7 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -3336,20 +4149,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>629.28 us</t>
+          <t>628.8 us</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.005558</v>
+        <v>5.003584</v>
       </c>
       <c r="F10" t="n">
-        <v>93.960883</v>
+        <v>94.025649</v>
       </c>
       <c r="G10" t="n">
-        <v>93.960883</v>
+        <v>94.025649</v>
       </c>
       <c r="H10" t="n">
-        <v>96.567188</v>
+        <v>96.597978</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
@@ -3374,7 +4187,7 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -3387,20 +4200,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>269.056 us</t>
+          <t>269.792 us</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>12.541522</v>
+        <v>12.649193</v>
       </c>
       <c r="F11" t="n">
-        <v>80.987652</v>
+        <v>80.729253</v>
       </c>
       <c r="G11" t="n">
-        <v>80.987652</v>
+        <v>80.729253</v>
       </c>
       <c r="H11" t="n">
-        <v>94.59914499999999</v>
+        <v>94.44363800000001</v>
       </c>
       <c r="I11" t="n">
         <v>100</v>
@@ -3425,7 +4238,7 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -3438,20 +4251,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>434.752 us</t>
+          <t>435.168 us</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13.006426</v>
+        <v>12.880227</v>
       </c>
       <c r="F12" t="n">
-        <v>82.874893</v>
+        <v>82.724726</v>
       </c>
       <c r="G12" t="n">
-        <v>82.874893</v>
+        <v>82.724726</v>
       </c>
       <c r="H12" t="n">
-        <v>97.328231</v>
+        <v>96.83955899999999</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
@@ -3476,7 +4289,7 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -3489,20 +4302,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>632.608 us</t>
+          <t>627.968 us</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.973674</v>
+        <v>4.98322</v>
       </c>
       <c r="F13" t="n">
-        <v>93.453981</v>
+        <v>94.15696</v>
       </c>
       <c r="G13" t="n">
-        <v>93.453981</v>
+        <v>94.15696</v>
       </c>
       <c r="H13" t="n">
-        <v>96.463639</v>
+        <v>96.47936900000001</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
@@ -3527,7 +4340,7 @@
     <row r="14">
       <c r="A14" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -3540,20 +4353,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>268.512 us</t>
+          <t>267.232 us</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.60658</v>
+        <v>12.689767</v>
       </c>
       <c r="F14" t="n">
-        <v>81.03238399999999</v>
+        <v>81.42889099999999</v>
       </c>
       <c r="G14" t="n">
-        <v>81.03238399999999</v>
+        <v>81.42889099999999</v>
       </c>
       <c r="H14" t="n">
-        <v>94.15025</v>
+        <v>94.652483</v>
       </c>
       <c r="I14" t="n">
         <v>100</v>
@@ -3578,7 +4391,7 @@
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -3591,20 +4404,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>435.328 us</t>
+          <t>435.904 us</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>12.920949</v>
+        <v>12.897291</v>
       </c>
       <c r="F15" t="n">
-        <v>82.86177600000001</v>
+        <v>82.675376</v>
       </c>
       <c r="G15" t="n">
-        <v>82.86177600000001</v>
+        <v>82.675376</v>
       </c>
       <c r="H15" t="n">
-        <v>97.4602</v>
+        <v>97.382305</v>
       </c>
       <c r="I15" t="n">
         <v>100</v>
@@ -3629,7 +4442,7 @@
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -3642,20 +4455,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>629.056 us</t>
+          <t>630.624 us</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.985303</v>
+        <v>4.999857</v>
       </c>
       <c r="F16" t="n">
-        <v>94.042863</v>
+        <v>93.832617</v>
       </c>
       <c r="G16" t="n">
-        <v>94.042863</v>
+        <v>93.832617</v>
       </c>
       <c r="H16" t="n">
-        <v>96.527649</v>
+        <v>96.417575</v>
       </c>
       <c r="I16" t="n">
         <v>100</v>
@@ -3680,7 +4493,7 @@
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -3693,20 +4506,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>267.936 us</t>
+          <t>268.608 us</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.590349</v>
+        <v>12.569806</v>
       </c>
       <c r="F17" t="n">
-        <v>81.259491</v>
+        <v>81.037284</v>
       </c>
       <c r="G17" t="n">
-        <v>81.259491</v>
+        <v>81.037284</v>
       </c>
       <c r="H17" t="n">
-        <v>95.26650600000001</v>
+        <v>94.103589</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
@@ -3731,7 +4544,7 @@
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -3744,20 +4557,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>432.128 us</t>
+          <t>433.888 us</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.939862</v>
+        <v>12.933639</v>
       </c>
       <c r="F18" t="n">
-        <v>83.522707</v>
+        <v>83.02358700000001</v>
       </c>
       <c r="G18" t="n">
-        <v>83.522707</v>
+        <v>83.02358700000001</v>
       </c>
       <c r="H18" t="n">
-        <v>97.167548</v>
+        <v>96.793463</v>
       </c>
       <c r="I18" t="n">
         <v>100</v>
@@ -3782,7 +4595,7 @@
     <row r="19">
       <c r="A19" s="22" t="inlineStr">
         <is>
-          <t>ncu-large-coalesced-b1024-direct-20261014-215130.ncu-rep</t>
+          <t>ncu-large-coalesced-b1024-graph-20261014-215130.ncu-rep</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -3795,20 +4608,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>628.8 us</t>
+          <t>629.28 us</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5.003584</v>
+        <v>5.005558</v>
       </c>
       <c r="F19" t="n">
-        <v>94.025649</v>
+        <v>93.960883</v>
       </c>
       <c r="G19" t="n">
-        <v>94.025649</v>
+        <v>93.960883</v>
       </c>
       <c r="H19" t="n">
-        <v>96.597978</v>
+        <v>96.567188</v>
       </c>
       <c r="I19" t="n">
         <v>100</v>
@@ -3986,7 +4799,7 @@
     <row r="23">
       <c r="A23" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -3999,20 +4812,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.002656 ms</t>
+          <t>0.002688 ms</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.47518</v>
+        <v>3.556429</v>
       </c>
       <c r="F23" t="n">
-        <v>12.842466</v>
+        <v>13.110017</v>
       </c>
       <c r="G23" t="n">
-        <v>12.842466</v>
+        <v>13.110017</v>
       </c>
       <c r="H23" t="n">
-        <v>17.177384</v>
+        <v>17.134164</v>
       </c>
       <c r="I23" t="n">
         <v>100</v>
@@ -4037,7 +4850,7 @@
     <row r="24">
       <c r="A24" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4050,20 +4863,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.008 ms</t>
+          <t>0.008032 ms</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13.299701</v>
+        <v>13.564387</v>
       </c>
       <c r="F24" t="n">
-        <v>78.633516</v>
+        <v>78.51781699999999</v>
       </c>
       <c r="G24" t="n">
-        <v>78.633516</v>
+        <v>78.51781699999999</v>
       </c>
       <c r="H24" t="n">
-        <v>62.987278</v>
+        <v>62.51766</v>
       </c>
       <c r="I24" t="n">
         <v>100</v>
@@ -4088,7 +4901,7 @@
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -4101,20 +4914,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>8.174304 ms</t>
+          <t>8.174176 ms</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>80.44577700000001</v>
+        <v>80.459727</v>
       </c>
       <c r="F25" t="n">
-        <v>38.915152</v>
+        <v>38.921768</v>
       </c>
       <c r="G25" t="n">
-        <v>0.116579</v>
+        <v>0.118669</v>
       </c>
       <c r="H25" t="n">
-        <v>41.259225</v>
+        <v>41.258928</v>
       </c>
       <c r="I25" t="n">
         <v>41.666667</v>
@@ -4139,7 +4952,7 @@
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -4152,20 +4965,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.21552 ms</t>
+          <t>0.216288 ms</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.16962</v>
+        <v>0.169864</v>
       </c>
       <c r="F26" t="n">
-        <v>3.184194</v>
+        <v>3.213787</v>
       </c>
       <c r="G26" t="n">
-        <v>3.184194</v>
+        <v>3.213787</v>
       </c>
       <c r="H26" t="n">
-        <v>16.654817</v>
+        <v>16.654818</v>
       </c>
       <c r="I26" t="n">
         <v>83.333333</v>
@@ -4190,7 +5003,7 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -4203,20 +5016,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.002688 ms</t>
+          <t>0.002656 ms</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3.556429</v>
+        <v>3.47518</v>
       </c>
       <c r="F27" t="n">
-        <v>13.110017</v>
+        <v>12.842466</v>
       </c>
       <c r="G27" t="n">
-        <v>13.110017</v>
+        <v>12.842466</v>
       </c>
       <c r="H27" t="n">
-        <v>17.134164</v>
+        <v>17.177384</v>
       </c>
       <c r="I27" t="n">
         <v>100</v>
@@ -4241,7 +5054,7 @@
     <row r="28">
       <c r="A28" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -4254,20 +5067,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>0.008032 ms</t>
+          <t>0.008 ms</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13.564387</v>
+        <v>13.299701</v>
       </c>
       <c r="F28" t="n">
-        <v>78.51781699999999</v>
+        <v>78.633516</v>
       </c>
       <c r="G28" t="n">
-        <v>78.51781699999999</v>
+        <v>78.633516</v>
       </c>
       <c r="H28" t="n">
-        <v>62.51766</v>
+        <v>62.987278</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
@@ -4292,7 +5105,7 @@
     <row r="29">
       <c r="A29" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -4305,20 +5118,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.174176 ms</t>
+          <t>8.174304 ms</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>80.459727</v>
+        <v>80.44577700000001</v>
       </c>
       <c r="F29" t="n">
-        <v>38.921768</v>
+        <v>38.915152</v>
       </c>
       <c r="G29" t="n">
-        <v>0.118669</v>
+        <v>0.116579</v>
       </c>
       <c r="H29" t="n">
-        <v>41.258928</v>
+        <v>41.259225</v>
       </c>
       <c r="I29" t="n">
         <v>41.666667</v>
@@ -4343,7 +5156,7 @@
     <row r="30">
       <c r="A30" s="22" t="inlineStr">
         <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -4356,20 +5169,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.216288 ms</t>
+          <t>0.21552 ms</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.169864</v>
+        <v>0.16962</v>
       </c>
       <c r="F30" t="n">
-        <v>3.213787</v>
+        <v>3.184194</v>
       </c>
       <c r="G30" t="n">
-        <v>3.213787</v>
+        <v>3.184194</v>
       </c>
       <c r="H30" t="n">
-        <v>16.654818</v>
+        <v>16.654817</v>
       </c>
       <c r="I30" t="n">
         <v>83.333333</v>
@@ -4445,7 +5258,7 @@
     <row r="32">
       <c r="A32" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -4458,20 +5271,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>25.728 us</t>
+          <t>25.824 us</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>10.890063</v>
+        <v>10.877459</v>
       </c>
       <c r="F32" t="n">
-        <v>49.26792</v>
+        <v>49.056943</v>
       </c>
       <c r="G32" t="n">
-        <v>49.26792</v>
+        <v>49.056943</v>
       </c>
       <c r="H32" t="n">
-        <v>19.760892</v>
+        <v>19.739888</v>
       </c>
       <c r="I32" t="n">
         <v>33.333333</v>
@@ -4492,19 +5305,19 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>4.201856 Mbyte</t>
+          <t>4.206592 Mbyte</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>7.341184 Mbyte</t>
+          <t>7.319168 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -4517,20 +5330,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>40.416 us</t>
+          <t>40.736 us</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5.773206</v>
+        <v>5.805545</v>
       </c>
       <c r="F33" t="n">
-        <v>78.87038200000001</v>
+        <v>78.169856</v>
       </c>
       <c r="G33" t="n">
-        <v>46.605831</v>
+        <v>46.249516</v>
       </c>
       <c r="H33" t="n">
-        <v>30.340962</v>
+        <v>30.350646</v>
       </c>
       <c r="I33" t="n">
         <v>33.333333</v>
@@ -4551,19 +5364,19 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>14.420864 Mbyte</t>
+          <t>14.387584 Mbyte</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2.733184 Mbyte</t>
+          <t>2.752768 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -4576,20 +5389,20 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40.672 us</t>
+          <t>40.48 us</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5.764894</v>
+        <v>5.74774</v>
       </c>
       <c r="F34" t="n">
-        <v>78.376588</v>
+        <v>78.652164</v>
       </c>
       <c r="G34" t="n">
-        <v>46.713255</v>
+        <v>46.496623</v>
       </c>
       <c r="H34" t="n">
-        <v>30.371009</v>
+        <v>30.34208</v>
       </c>
       <c r="I34" t="n">
         <v>33.333333</v>
@@ -4610,19 +5423,19 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>14.519424 Mbyte</t>
+          <t>14.400768 Mbyte</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>2.781312 Mbyte</t>
+          <t>2.72832 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -4635,20 +5448,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>40.448 us</t>
+          <t>40.864 us</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5.800137</v>
+        <v>5.763605</v>
       </c>
       <c r="F35" t="n">
-        <v>79.203608</v>
+        <v>78.299513</v>
       </c>
       <c r="G35" t="n">
-        <v>46.456225</v>
+        <v>46.192525</v>
       </c>
       <c r="H35" t="n">
-        <v>30.361409</v>
+        <v>30.342844</v>
       </c>
       <c r="I35" t="n">
         <v>33.333333</v>
@@ -4669,19 +5482,19 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>14.40832 Mbyte</t>
+          <t>14.428544 Mbyte</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2.70208 Mbyte</t>
+          <t>2.751232 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -4694,20 +5507,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>40.992 us</t>
+          <t>40.832 us</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5.775927</v>
+        <v>5.712442</v>
       </c>
       <c r="F36" t="n">
-        <v>77.786952</v>
+        <v>77.951116</v>
       </c>
       <c r="G36" t="n">
-        <v>46.38541</v>
+        <v>46.345444</v>
       </c>
       <c r="H36" t="n">
-        <v>30.322205</v>
+        <v>30.3306</v>
       </c>
       <c r="I36" t="n">
         <v>33.333333</v>
@@ -4728,19 +5541,19 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>14.534656 Mbyte</t>
+          <t>14.486656 Mbyte</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>2.758656 Mbyte</t>
+          <t>2.7424 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -4753,20 +5566,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>41.088 us</t>
+          <t>41.6 us</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5.656753</v>
+        <v>5.759529</v>
       </c>
       <c r="F37" t="n">
-        <v>78.029509</v>
+        <v>76.955658</v>
       </c>
       <c r="G37" t="n">
-        <v>45.854221</v>
+        <v>45.410515</v>
       </c>
       <c r="H37" t="n">
-        <v>30.384827</v>
+        <v>30.344492</v>
       </c>
       <c r="I37" t="n">
         <v>33.333333</v>
@@ -4787,19 +5600,19 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>14.370048 Mbyte</t>
+          <t>14.378624 Mbyte</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.770304 Mbyte</t>
+          <t>2.819072 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -4812,20 +5625,20 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>40.864 us</t>
+          <t>41.504 us</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5.78772</v>
+        <v>5.784515</v>
       </c>
       <c r="F38" t="n">
-        <v>78.104333</v>
+        <v>76.66707599999999</v>
       </c>
       <c r="G38" t="n">
-        <v>46.460881</v>
+        <v>46.270598</v>
       </c>
       <c r="H38" t="n">
-        <v>30.333385</v>
+        <v>30.328672</v>
       </c>
       <c r="I38" t="n">
         <v>33.333333</v>
@@ -4846,19 +5659,19 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>14.488064 Mbyte</t>
+          <t>14.650496 Mbyte</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>2.787712 Mbyte</t>
+          <t>2.831232 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -4871,20 +5684,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>40.832 us</t>
+          <t>40.736 us</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5.761913</v>
+        <v>5.786246</v>
       </c>
       <c r="F39" t="n">
-        <v>78.049094</v>
+        <v>78.139859</v>
       </c>
       <c r="G39" t="n">
-        <v>45.86879</v>
+        <v>45.437417</v>
       </c>
       <c r="H39" t="n">
-        <v>30.304531</v>
+        <v>30.348963</v>
       </c>
       <c r="I39" t="n">
         <v>33.333333</v>
@@ -4905,19 +5718,19 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>14.347776 Mbyte</t>
+          <t>14.163072 Mbyte</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2.70784 Mbyte</t>
+          <t>2.6912 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -4934,16 +5747,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5.750203</v>
+        <v>5.799694</v>
       </c>
       <c r="F40" t="n">
-        <v>78.529796</v>
+        <v>77.920129</v>
       </c>
       <c r="G40" t="n">
-        <v>46.471641</v>
+        <v>46.611313</v>
       </c>
       <c r="H40" t="n">
-        <v>30.319598</v>
+        <v>30.346429</v>
       </c>
       <c r="I40" t="n">
         <v>33.333333</v>
@@ -4964,19 +5777,19 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>14.502272 Mbyte</t>
+          <t>14.597376 Mbyte</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2.781312 Mbyte</t>
+          <t>2.734336 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -4989,20 +5802,20 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>264.064 us</t>
+          <t>262.24 us</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6.889017</v>
+        <v>6.895505</v>
       </c>
       <c r="F41" t="n">
-        <v>96.29396199999999</v>
+        <v>96.16476900000001</v>
       </c>
       <c r="G41" t="n">
-        <v>38.144759</v>
+        <v>38.424835</v>
       </c>
       <c r="H41" t="n">
-        <v>32.574188</v>
+        <v>32.571271</v>
       </c>
       <c r="I41" t="n">
         <v>33.333333</v>
@@ -5023,19 +5836,19 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>81.698944 Mbyte</t>
+          <t>81.701504 Mbyte</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>10.073856 Mbyte</t>
+          <t>10.09984 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -5048,20 +5861,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>261.984 us</t>
+          <t>263.648 us</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6.895241</v>
+        <v>6.849166</v>
       </c>
       <c r="F42" t="n">
-        <v>96.26137199999999</v>
+        <v>96.19049099999999</v>
       </c>
       <c r="G42" t="n">
-        <v>38.440095</v>
+        <v>38.224158</v>
       </c>
       <c r="H42" t="n">
-        <v>32.571375</v>
+        <v>32.571055</v>
       </c>
       <c r="I42" t="n">
         <v>33.333333</v>
@@ -5082,19 +5895,19 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>81.69344 Mbyte</t>
+          <t>81.751552 Mbyte</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>10.071936 Mbyte</t>
+          <t>10.074496 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -5107,20 +5920,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>262.208 us</t>
+          <t>261.792 us</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6.895088</v>
+        <v>6.886829</v>
       </c>
       <c r="F43" t="n">
-        <v>96.188607</v>
+        <v>96.325785</v>
       </c>
       <c r="G43" t="n">
-        <v>38.499539</v>
+        <v>38.537803</v>
       </c>
       <c r="H43" t="n">
-        <v>32.564324</v>
+        <v>32.569066</v>
       </c>
       <c r="I43" t="n">
         <v>33.333333</v>
@@ -5141,19 +5954,19 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>81.865728 Mbyte</t>
+          <t>81.801856 Mbyte</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>10.117248 Mbyte</t>
+          <t>10.12416 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -5170,16 +5983,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6.889272</v>
+        <v>6.850185</v>
       </c>
       <c r="F44" t="n">
-        <v>96.323176</v>
+        <v>96.245718</v>
       </c>
       <c r="G44" t="n">
-        <v>38.365225</v>
+        <v>38.24335</v>
       </c>
       <c r="H44" t="n">
-        <v>32.574026</v>
+        <v>32.568792</v>
       </c>
       <c r="I44" t="n">
         <v>33.333333</v>
@@ -5200,19 +6013,19 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>81.79584 Mbyte</t>
+          <t>81.698304 Mbyte</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>10.337664 Mbyte</t>
+          <t>10.13312 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -5225,20 +6038,20 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>261.792 us</t>
+          <t>263.552 us</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6.886739</v>
+        <v>6.894557</v>
       </c>
       <c r="F45" t="n">
-        <v>96.343954</v>
+        <v>96.27703</v>
       </c>
       <c r="G45" t="n">
-        <v>38.49865</v>
+        <v>38.290364</v>
       </c>
       <c r="H45" t="n">
-        <v>32.569317</v>
+        <v>32.568962</v>
       </c>
       <c r="I45" t="n">
         <v>33.333333</v>
@@ -5259,19 +6072,19 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>81.744384 Mbyte</t>
+          <t>81.828992 Mbyte</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>10.091392 Mbyte</t>
+          <t>10.127872 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -5284,20 +6097,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>263.744 us</t>
+          <t>261.824 us</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6.843444</v>
+        <v>6.885321</v>
       </c>
       <c r="F46" t="n">
-        <v>96.26432699999999</v>
+        <v>96.31959000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>38.237625</v>
+        <v>38.503123</v>
       </c>
       <c r="H46" t="n">
-        <v>32.569524</v>
+        <v>32.567834</v>
       </c>
       <c r="I46" t="n">
         <v>33.333333</v>
@@ -5318,19 +6131,19 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>81.754624 Mbyte</t>
+          <t>81.778048 Mbyte</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>10.131968 Mbyte</t>
+          <t>10.071552 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5343,20 +6156,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>261.984 us</t>
+          <t>261.76 us</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6.884972</v>
+        <v>6.898733</v>
       </c>
       <c r="F47" t="n">
-        <v>96.290837</v>
+        <v>96.291757</v>
       </c>
       <c r="G47" t="n">
-        <v>38.501948</v>
+        <v>38.518161</v>
       </c>
       <c r="H47" t="n">
-        <v>32.568833</v>
+        <v>32.568335</v>
       </c>
       <c r="I47" t="n">
         <v>33.333333</v>
@@ -5377,19 +6190,19 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>81.774592 Mbyte</t>
+          <t>81.760896 Mbyte</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>10.125824 Mbyte</t>
+          <t>10.1088 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -5402,20 +6215,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>261.824 us</t>
+          <t>263.68 us</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6.884805</v>
+        <v>6.879953</v>
       </c>
       <c r="F48" t="n">
-        <v>96.37597</v>
+        <v>96.201206</v>
       </c>
       <c r="G48" t="n">
-        <v>38.426951</v>
+        <v>38.239644</v>
       </c>
       <c r="H48" t="n">
-        <v>32.569863</v>
+        <v>32.570855</v>
       </c>
       <c r="I48" t="n">
         <v>33.333333</v>
@@ -5436,19 +6249,19 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>81.599488 Mbyte</t>
+          <t>81.771392 Mbyte</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>10.071552 Mbyte</t>
+          <t>10.10752 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -5461,20 +6274,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>263.936 us</t>
+          <t>262.016 us</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6.840552</v>
+        <v>6.85042</v>
       </c>
       <c r="F49" t="n">
-        <v>96.298384</v>
+        <v>96.233647</v>
       </c>
       <c r="G49" t="n">
-        <v>38.219401</v>
+        <v>38.467428</v>
       </c>
       <c r="H49" t="n">
-        <v>32.572821</v>
+        <v>32.574187</v>
       </c>
       <c r="I49" t="n">
         <v>33.333333</v>
@@ -5495,19 +6308,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>81.804416 Mbyte</t>
+          <t>81.757184 Mbyte</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>10.107264 Mbyte</t>
+          <t>10.079744 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -5520,20 +6333,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>261.824 us</t>
+          <t>263.584 us</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6.879849</v>
+        <v>6.842498</v>
       </c>
       <c r="F50" t="n">
-        <v>96.347562</v>
+        <v>96.236355</v>
       </c>
       <c r="G50" t="n">
-        <v>38.630291</v>
+        <v>38.217025</v>
       </c>
       <c r="H50" t="n">
-        <v>32.565578</v>
+        <v>32.574523</v>
       </c>
       <c r="I50" t="n">
         <v>33.333333</v>
@@ -5554,19 +6367,19 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>81.864832 Mbyte</t>
+          <t>81.690368 Mbyte</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>10.288128 Mbyte</t>
+          <t>10.090368 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -5579,20 +6392,20 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>263.712 us</t>
+          <t>261.92 us</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6.885424</v>
+        <v>6.891282</v>
       </c>
       <c r="F51" t="n">
-        <v>96.36948</v>
+        <v>96.255655</v>
       </c>
       <c r="G51" t="n">
-        <v>38.214683</v>
+        <v>38.510219</v>
       </c>
       <c r="H51" t="n">
-        <v>32.579621</v>
+        <v>32.566437</v>
       </c>
       <c r="I51" t="n">
         <v>33.333333</v>
@@ -5613,19 +6426,19 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>81.745664 Mbyte</t>
+          <t>81.746176 Mbyte</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>10.070144 Mbyte</t>
+          <t>10.158208 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -5638,20 +6451,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>263.616 us</t>
+          <t>263.36 us</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6.838532</v>
+        <v>6.887735</v>
       </c>
       <c r="F52" t="n">
-        <v>96.31980299999999</v>
+        <v>96.314137</v>
       </c>
       <c r="G52" t="n">
-        <v>38.213066</v>
+        <v>38.307678</v>
       </c>
       <c r="H52" t="n">
-        <v>32.580223</v>
+        <v>32.569651</v>
       </c>
       <c r="I52" t="n">
         <v>33.333333</v>
@@ -5672,19 +6485,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>81.690368 Mbyte</t>
+          <t>81.854592 Mbyte</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>10.096512 Mbyte</t>
+          <t>10.077952 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -5697,20 +6510,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>262.144 us</t>
+          <t>262.176 us</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6.837447</v>
+        <v>6.89219</v>
       </c>
       <c r="F53" t="n">
-        <v>96.248293</v>
+        <v>96.169397</v>
       </c>
       <c r="G53" t="n">
-        <v>38.715689</v>
+        <v>38.418853</v>
       </c>
       <c r="H53" t="n">
-        <v>32.568851</v>
+        <v>32.569409</v>
       </c>
       <c r="I53" t="n">
         <v>33.333333</v>
@@ -5731,19 +6544,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>82.05184 Mbyte</t>
+          <t>81.662336 Mbyte</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>10.412672 Mbyte</t>
+          <t>10.112128 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -5756,20 +6569,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>262.272 us</t>
+          <t>261.952 us</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6.888228</v>
+        <v>6.851282</v>
       </c>
       <c r="F54" t="n">
-        <v>96.173063</v>
+        <v>96.25175400000001</v>
       </c>
       <c r="G54" t="n">
-        <v>38.452885</v>
+        <v>38.473586</v>
       </c>
       <c r="H54" t="n">
-        <v>32.560925</v>
+        <v>32.568744</v>
       </c>
       <c r="I54" t="n">
         <v>33.333333</v>
@@ -5790,19 +6603,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>81.747584 Mbyte</t>
+          <t>81.735424 Mbyte</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>10.133376 Mbyte</t>
+          <t>10.081536 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -5815,20 +6628,20 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>261.696 us</t>
+          <t>262.048 us</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6.882413</v>
+        <v>6.845855</v>
       </c>
       <c r="F55" t="n">
-        <v>96.3886</v>
+        <v>96.220005</v>
       </c>
       <c r="G55" t="n">
-        <v>38.485446</v>
+        <v>38.46377</v>
       </c>
       <c r="H55" t="n">
-        <v>32.566455</v>
+        <v>32.575165</v>
       </c>
       <c r="I55" t="n">
         <v>33.333333</v>
@@ -5849,19 +6662,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>81.679488 Mbyte</t>
+          <t>81.741568 Mbyte</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>10.090112 Mbyte</t>
+          <t>10.092928 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -5874,20 +6687,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>263.776 us</t>
+          <t>261.888 us</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6.833415</v>
+        <v>6.887929</v>
       </c>
       <c r="F56" t="n">
-        <v>96.259393</v>
+        <v>96.28758999999999</v>
       </c>
       <c r="G56" t="n">
-        <v>38.287428</v>
+        <v>38.496537</v>
       </c>
       <c r="H56" t="n">
-        <v>32.569779</v>
+        <v>32.569462</v>
       </c>
       <c r="I56" t="n">
         <v>33.333333</v>
@@ -5908,19 +6721,19 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>81.737088 Mbyte</t>
+          <t>81.759744 Mbyte</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>10.288 Mbyte</t>
+          <t>10.102528 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -5933,20 +6746,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>262.368 us</t>
+          <t>263.552 us</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6.884495</v>
+        <v>6.845493</v>
       </c>
       <c r="F57" t="n">
-        <v>96.145937</v>
+        <v>96.25166</v>
       </c>
       <c r="G57" t="n">
-        <v>38.449581</v>
+        <v>38.308544</v>
       </c>
       <c r="H57" t="n">
-        <v>32.563338</v>
+        <v>32.572542</v>
       </c>
       <c r="I57" t="n">
         <v>33.333333</v>
@@ -5967,19 +6780,19 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>81.785088 Mbyte</t>
+          <t>81.828096 Mbyte</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>10.122624 Mbyte</t>
+          <t>10.1536 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -5992,20 +6805,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>261.952 us</t>
+          <t>261.856 us</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6.892467</v>
+        <v>6.89217</v>
       </c>
       <c r="F58" t="n">
-        <v>96.30693599999999</v>
+        <v>96.292596</v>
       </c>
       <c r="G58" t="n">
-        <v>38.429724</v>
+        <v>38.5189</v>
       </c>
       <c r="H58" t="n">
-        <v>32.570514</v>
+        <v>32.567302</v>
       </c>
       <c r="I58" t="n">
         <v>33.333333</v>
@@ -6026,19 +6839,19 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>81.664512 Mbyte</t>
+          <t>81.79456 Mbyte</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>10.057216 Mbyte</t>
+          <t>10.102144 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -6051,20 +6864,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>263.872 us</t>
+          <t>263.392 us</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6.833276</v>
+        <v>6.844887</v>
       </c>
       <c r="F59" t="n">
-        <v>96.264078</v>
+        <v>96.333033</v>
       </c>
       <c r="G59" t="n">
-        <v>38.34479</v>
+        <v>38.253091</v>
       </c>
       <c r="H59" t="n">
-        <v>32.574914</v>
+        <v>32.5683</v>
       </c>
       <c r="I59" t="n">
         <v>33.333333</v>
@@ -6085,19 +6898,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>81.928192 Mbyte</t>
+          <t>81.718912 Mbyte</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>10.26304 Mbyte</t>
+          <t>10.092032 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -6110,20 +6923,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>25.824 us</t>
+          <t>25.728 us</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>10.877459</v>
+        <v>10.890063</v>
       </c>
       <c r="F60" t="n">
-        <v>49.056943</v>
+        <v>49.26792</v>
       </c>
       <c r="G60" t="n">
-        <v>49.056943</v>
+        <v>49.26792</v>
       </c>
       <c r="H60" t="n">
-        <v>19.739888</v>
+        <v>19.760892</v>
       </c>
       <c r="I60" t="n">
         <v>33.333333</v>
@@ -6144,19 +6957,19 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>4.206592 Mbyte</t>
+          <t>4.201856 Mbyte</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>7.319168 Mbyte</t>
+          <t>7.341184 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -6169,20 +6982,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>40.736 us</t>
+          <t>40.416 us</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5.805545</v>
+        <v>5.773206</v>
       </c>
       <c r="F61" t="n">
-        <v>78.169856</v>
+        <v>78.87038200000001</v>
       </c>
       <c r="G61" t="n">
-        <v>46.249516</v>
+        <v>46.605831</v>
       </c>
       <c r="H61" t="n">
-        <v>30.350646</v>
+        <v>30.340962</v>
       </c>
       <c r="I61" t="n">
         <v>33.333333</v>
@@ -6203,19 +7016,19 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>14.387584 Mbyte</t>
+          <t>14.420864 Mbyte</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2.752768 Mbyte</t>
+          <t>2.733184 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -6228,20 +7041,20 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>40.48 us</t>
+          <t>40.672 us</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5.74774</v>
+        <v>5.764894</v>
       </c>
       <c r="F62" t="n">
-        <v>78.652164</v>
+        <v>78.376588</v>
       </c>
       <c r="G62" t="n">
-        <v>46.496623</v>
+        <v>46.713255</v>
       </c>
       <c r="H62" t="n">
-        <v>30.34208</v>
+        <v>30.371009</v>
       </c>
       <c r="I62" t="n">
         <v>33.333333</v>
@@ -6262,19 +7075,19 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>14.400768 Mbyte</t>
+          <t>14.519424 Mbyte</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2.72832 Mbyte</t>
+          <t>2.781312 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -6287,20 +7100,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>40.864 us</t>
+          <t>40.448 us</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5.763605</v>
+        <v>5.800137</v>
       </c>
       <c r="F63" t="n">
-        <v>78.299513</v>
+        <v>79.203608</v>
       </c>
       <c r="G63" t="n">
-        <v>46.192525</v>
+        <v>46.456225</v>
       </c>
       <c r="H63" t="n">
-        <v>30.342844</v>
+        <v>30.361409</v>
       </c>
       <c r="I63" t="n">
         <v>33.333333</v>
@@ -6321,19 +7134,19 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>14.428544 Mbyte</t>
+          <t>14.40832 Mbyte</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2.751232 Mbyte</t>
+          <t>2.70208 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -6346,20 +7159,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>40.832 us</t>
+          <t>40.992 us</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5.712442</v>
+        <v>5.775927</v>
       </c>
       <c r="F64" t="n">
-        <v>77.951116</v>
+        <v>77.786952</v>
       </c>
       <c r="G64" t="n">
-        <v>46.345444</v>
+        <v>46.38541</v>
       </c>
       <c r="H64" t="n">
-        <v>30.3306</v>
+        <v>30.322205</v>
       </c>
       <c r="I64" t="n">
         <v>33.333333</v>
@@ -6380,19 +7193,19 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>14.486656 Mbyte</t>
+          <t>14.534656 Mbyte</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2.7424 Mbyte</t>
+          <t>2.758656 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -6405,20 +7218,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>41.6 us</t>
+          <t>41.088 us</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5.759529</v>
+        <v>5.656753</v>
       </c>
       <c r="F65" t="n">
-        <v>76.955658</v>
+        <v>78.029509</v>
       </c>
       <c r="G65" t="n">
-        <v>45.410515</v>
+        <v>45.854221</v>
       </c>
       <c r="H65" t="n">
-        <v>30.344492</v>
+        <v>30.384827</v>
       </c>
       <c r="I65" t="n">
         <v>33.333333</v>
@@ -6439,19 +7252,19 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>14.378624 Mbyte</t>
+          <t>14.370048 Mbyte</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2.819072 Mbyte</t>
+          <t>2.770304 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6464,20 +7277,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>41.504 us</t>
+          <t>40.864 us</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5.784515</v>
+        <v>5.78772</v>
       </c>
       <c r="F66" t="n">
-        <v>76.66707599999999</v>
+        <v>78.104333</v>
       </c>
       <c r="G66" t="n">
-        <v>46.270598</v>
+        <v>46.460881</v>
       </c>
       <c r="H66" t="n">
-        <v>30.328672</v>
+        <v>30.333385</v>
       </c>
       <c r="I66" t="n">
         <v>33.333333</v>
@@ -6498,19 +7311,19 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>14.650496 Mbyte</t>
+          <t>14.488064 Mbyte</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>2.831232 Mbyte</t>
+          <t>2.787712 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6523,20 +7336,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>40.736 us</t>
+          <t>40.832 us</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5.786246</v>
+        <v>5.761913</v>
       </c>
       <c r="F67" t="n">
-        <v>78.139859</v>
+        <v>78.049094</v>
       </c>
       <c r="G67" t="n">
-        <v>45.437417</v>
+        <v>45.86879</v>
       </c>
       <c r="H67" t="n">
-        <v>30.348963</v>
+        <v>30.304531</v>
       </c>
       <c r="I67" t="n">
         <v>33.333333</v>
@@ -6557,19 +7370,19 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>14.163072 Mbyte</t>
+          <t>14.347776 Mbyte</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2.6912 Mbyte</t>
+          <t>2.70784 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -6586,16 +7399,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5.799694</v>
+        <v>5.750203</v>
       </c>
       <c r="F68" t="n">
-        <v>77.920129</v>
+        <v>78.529796</v>
       </c>
       <c r="G68" t="n">
-        <v>46.611313</v>
+        <v>46.471641</v>
       </c>
       <c r="H68" t="n">
-        <v>30.346429</v>
+        <v>30.319598</v>
       </c>
       <c r="I68" t="n">
         <v>33.333333</v>
@@ -6616,19 +7429,19 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>14.597376 Mbyte</t>
+          <t>14.502272 Mbyte</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2.734336 Mbyte</t>
+          <t>2.781312 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -6641,20 +7454,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>262.24 us</t>
+          <t>264.064 us</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6.895505</v>
+        <v>6.889017</v>
       </c>
       <c r="F69" t="n">
-        <v>96.16476900000001</v>
+        <v>96.29396199999999</v>
       </c>
       <c r="G69" t="n">
-        <v>38.424835</v>
+        <v>38.144759</v>
       </c>
       <c r="H69" t="n">
-        <v>32.571271</v>
+        <v>32.574188</v>
       </c>
       <c r="I69" t="n">
         <v>33.333333</v>
@@ -6675,19 +7488,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>81.701504 Mbyte</t>
+          <t>81.698944 Mbyte</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>10.09984 Mbyte</t>
+          <t>10.073856 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -6700,20 +7513,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>263.648 us</t>
+          <t>261.984 us</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6.849166</v>
+        <v>6.895241</v>
       </c>
       <c r="F70" t="n">
-        <v>96.19049099999999</v>
+        <v>96.26137199999999</v>
       </c>
       <c r="G70" t="n">
-        <v>38.224158</v>
+        <v>38.440095</v>
       </c>
       <c r="H70" t="n">
-        <v>32.571055</v>
+        <v>32.571375</v>
       </c>
       <c r="I70" t="n">
         <v>33.333333</v>
@@ -6734,19 +7547,19 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>81.751552 Mbyte</t>
+          <t>81.69344 Mbyte</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>10.074496 Mbyte</t>
+          <t>10.071936 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -6759,20 +7572,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>261.792 us</t>
+          <t>262.208 us</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6.886829</v>
+        <v>6.895088</v>
       </c>
       <c r="F71" t="n">
-        <v>96.325785</v>
+        <v>96.188607</v>
       </c>
       <c r="G71" t="n">
-        <v>38.537803</v>
+        <v>38.499539</v>
       </c>
       <c r="H71" t="n">
-        <v>32.569066</v>
+        <v>32.564324</v>
       </c>
       <c r="I71" t="n">
         <v>33.333333</v>
@@ -6793,19 +7606,19 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>81.801856 Mbyte</t>
+          <t>81.865728 Mbyte</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>10.12416 Mbyte</t>
+          <t>10.117248 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -6822,16 +7635,16 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6.850185</v>
+        <v>6.889272</v>
       </c>
       <c r="F72" t="n">
-        <v>96.245718</v>
+        <v>96.323176</v>
       </c>
       <c r="G72" t="n">
-        <v>38.24335</v>
+        <v>38.365225</v>
       </c>
       <c r="H72" t="n">
-        <v>32.568792</v>
+        <v>32.574026</v>
       </c>
       <c r="I72" t="n">
         <v>33.333333</v>
@@ -6852,19 +7665,19 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>81.698304 Mbyte</t>
+          <t>81.79584 Mbyte</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>10.13312 Mbyte</t>
+          <t>10.337664 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -6877,20 +7690,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>263.552 us</t>
+          <t>261.792 us</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6.894557</v>
+        <v>6.886739</v>
       </c>
       <c r="F73" t="n">
-        <v>96.27703</v>
+        <v>96.343954</v>
       </c>
       <c r="G73" t="n">
-        <v>38.290364</v>
+        <v>38.49865</v>
       </c>
       <c r="H73" t="n">
-        <v>32.568962</v>
+        <v>32.569317</v>
       </c>
       <c r="I73" t="n">
         <v>33.333333</v>
@@ -6911,19 +7724,19 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>81.828992 Mbyte</t>
+          <t>81.744384 Mbyte</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>10.127872 Mbyte</t>
+          <t>10.091392 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -6936,20 +7749,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>261.824 us</t>
+          <t>263.744 us</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6.885321</v>
+        <v>6.843444</v>
       </c>
       <c r="F74" t="n">
-        <v>96.31959000000001</v>
+        <v>96.26432699999999</v>
       </c>
       <c r="G74" t="n">
-        <v>38.503123</v>
+        <v>38.237625</v>
       </c>
       <c r="H74" t="n">
-        <v>32.567834</v>
+        <v>32.569524</v>
       </c>
       <c r="I74" t="n">
         <v>33.333333</v>
@@ -6970,19 +7783,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>81.778048 Mbyte</t>
+          <t>81.754624 Mbyte</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>10.071552 Mbyte</t>
+          <t>10.131968 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -6995,20 +7808,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>261.76 us</t>
+          <t>261.984 us</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6.898733</v>
+        <v>6.884972</v>
       </c>
       <c r="F75" t="n">
-        <v>96.291757</v>
+        <v>96.290837</v>
       </c>
       <c r="G75" t="n">
-        <v>38.518161</v>
+        <v>38.501948</v>
       </c>
       <c r="H75" t="n">
-        <v>32.568335</v>
+        <v>32.568833</v>
       </c>
       <c r="I75" t="n">
         <v>33.333333</v>
@@ -7029,19 +7842,19 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>81.760896 Mbyte</t>
+          <t>81.774592 Mbyte</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>10.1088 Mbyte</t>
+          <t>10.125824 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -7054,20 +7867,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>263.68 us</t>
+          <t>261.824 us</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6.879953</v>
+        <v>6.884805</v>
       </c>
       <c r="F76" t="n">
-        <v>96.201206</v>
+        <v>96.37597</v>
       </c>
       <c r="G76" t="n">
-        <v>38.239644</v>
+        <v>38.426951</v>
       </c>
       <c r="H76" t="n">
-        <v>32.570855</v>
+        <v>32.569863</v>
       </c>
       <c r="I76" t="n">
         <v>33.333333</v>
@@ -7088,19 +7901,19 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>81.771392 Mbyte</t>
+          <t>81.599488 Mbyte</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>10.10752 Mbyte</t>
+          <t>10.071552 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -7113,20 +7926,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>262.016 us</t>
+          <t>263.936 us</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6.85042</v>
+        <v>6.840552</v>
       </c>
       <c r="F77" t="n">
-        <v>96.233647</v>
+        <v>96.298384</v>
       </c>
       <c r="G77" t="n">
-        <v>38.467428</v>
+        <v>38.219401</v>
       </c>
       <c r="H77" t="n">
-        <v>32.574187</v>
+        <v>32.572821</v>
       </c>
       <c r="I77" t="n">
         <v>33.333333</v>
@@ -7147,19 +7960,19 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>81.757184 Mbyte</t>
+          <t>81.804416 Mbyte</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>10.079744 Mbyte</t>
+          <t>10.107264 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -7172,20 +7985,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>263.584 us</t>
+          <t>261.824 us</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6.842498</v>
+        <v>6.879849</v>
       </c>
       <c r="F78" t="n">
-        <v>96.236355</v>
+        <v>96.347562</v>
       </c>
       <c r="G78" t="n">
-        <v>38.217025</v>
+        <v>38.630291</v>
       </c>
       <c r="H78" t="n">
-        <v>32.574523</v>
+        <v>32.565578</v>
       </c>
       <c r="I78" t="n">
         <v>33.333333</v>
@@ -7206,19 +8019,19 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>81.690368 Mbyte</t>
+          <t>81.864832 Mbyte</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>10.090368 Mbyte</t>
+          <t>10.288128 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -7231,20 +8044,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>261.92 us</t>
+          <t>263.712 us</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6.891282</v>
+        <v>6.885424</v>
       </c>
       <c r="F79" t="n">
-        <v>96.255655</v>
+        <v>96.36948</v>
       </c>
       <c r="G79" t="n">
-        <v>38.510219</v>
+        <v>38.214683</v>
       </c>
       <c r="H79" t="n">
-        <v>32.566437</v>
+        <v>32.579621</v>
       </c>
       <c r="I79" t="n">
         <v>33.333333</v>
@@ -7265,19 +8078,19 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>81.746176 Mbyte</t>
+          <t>81.745664 Mbyte</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>10.158208 Mbyte</t>
+          <t>10.070144 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -7290,20 +8103,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>263.36 us</t>
+          <t>263.616 us</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6.887735</v>
+        <v>6.838532</v>
       </c>
       <c r="F80" t="n">
-        <v>96.314137</v>
+        <v>96.31980299999999</v>
       </c>
       <c r="G80" t="n">
-        <v>38.307678</v>
+        <v>38.213066</v>
       </c>
       <c r="H80" t="n">
-        <v>32.569651</v>
+        <v>32.580223</v>
       </c>
       <c r="I80" t="n">
         <v>33.333333</v>
@@ -7324,19 +8137,19 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>81.854592 Mbyte</t>
+          <t>81.690368 Mbyte</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>10.077952 Mbyte</t>
+          <t>10.096512 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -7349,20 +8162,20 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>262.176 us</t>
+          <t>262.144 us</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6.89219</v>
+        <v>6.837447</v>
       </c>
       <c r="F81" t="n">
-        <v>96.169397</v>
+        <v>96.248293</v>
       </c>
       <c r="G81" t="n">
-        <v>38.418853</v>
+        <v>38.715689</v>
       </c>
       <c r="H81" t="n">
-        <v>32.569409</v>
+        <v>32.568851</v>
       </c>
       <c r="I81" t="n">
         <v>33.333333</v>
@@ -7383,19 +8196,19 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>81.662336 Mbyte</t>
+          <t>82.05184 Mbyte</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>10.112128 Mbyte</t>
+          <t>10.412672 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -7408,20 +8221,20 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>261.952 us</t>
+          <t>262.272 us</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6.851282</v>
+        <v>6.888228</v>
       </c>
       <c r="F82" t="n">
-        <v>96.25175400000001</v>
+        <v>96.173063</v>
       </c>
       <c r="G82" t="n">
-        <v>38.473586</v>
+        <v>38.452885</v>
       </c>
       <c r="H82" t="n">
-        <v>32.568744</v>
+        <v>32.560925</v>
       </c>
       <c r="I82" t="n">
         <v>33.333333</v>
@@ -7442,19 +8255,19 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>81.735424 Mbyte</t>
+          <t>81.747584 Mbyte</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>10.081536 Mbyte</t>
+          <t>10.133376 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7467,20 +8280,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>262.048 us</t>
+          <t>261.696 us</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6.845855</v>
+        <v>6.882413</v>
       </c>
       <c r="F83" t="n">
-        <v>96.220005</v>
+        <v>96.3886</v>
       </c>
       <c r="G83" t="n">
-        <v>38.46377</v>
+        <v>38.485446</v>
       </c>
       <c r="H83" t="n">
-        <v>32.575165</v>
+        <v>32.566455</v>
       </c>
       <c r="I83" t="n">
         <v>33.333333</v>
@@ -7501,19 +8314,19 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>81.741568 Mbyte</t>
+          <t>81.679488 Mbyte</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>10.092928 Mbyte</t>
+          <t>10.090112 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -7526,20 +8339,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>261.888 us</t>
+          <t>263.776 us</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6.887929</v>
+        <v>6.833415</v>
       </c>
       <c r="F84" t="n">
-        <v>96.28758999999999</v>
+        <v>96.259393</v>
       </c>
       <c r="G84" t="n">
-        <v>38.496537</v>
+        <v>38.287428</v>
       </c>
       <c r="H84" t="n">
-        <v>32.569462</v>
+        <v>32.569779</v>
       </c>
       <c r="I84" t="n">
         <v>33.333333</v>
@@ -7560,19 +8373,19 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>81.759744 Mbyte</t>
+          <t>81.737088 Mbyte</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>10.102528 Mbyte</t>
+          <t>10.288 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -7585,20 +8398,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>263.552 us</t>
+          <t>262.368 us</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6.845493</v>
+        <v>6.884495</v>
       </c>
       <c r="F85" t="n">
-        <v>96.25166</v>
+        <v>96.145937</v>
       </c>
       <c r="G85" t="n">
-        <v>38.308544</v>
+        <v>38.449581</v>
       </c>
       <c r="H85" t="n">
-        <v>32.572542</v>
+        <v>32.563338</v>
       </c>
       <c r="I85" t="n">
         <v>33.333333</v>
@@ -7619,19 +8432,19 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>81.828096 Mbyte</t>
+          <t>81.785088 Mbyte</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>10.1536 Mbyte</t>
+          <t>10.122624 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -7644,20 +8457,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>261.856 us</t>
+          <t>261.952 us</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6.89217</v>
+        <v>6.892467</v>
       </c>
       <c r="F86" t="n">
-        <v>96.292596</v>
+        <v>96.30693599999999</v>
       </c>
       <c r="G86" t="n">
-        <v>38.5189</v>
+        <v>38.429724</v>
       </c>
       <c r="H86" t="n">
-        <v>32.567302</v>
+        <v>32.570514</v>
       </c>
       <c r="I86" t="n">
         <v>33.333333</v>
@@ -7678,19 +8491,19 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>81.79456 Mbyte</t>
+          <t>81.664512 Mbyte</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>10.102144 Mbyte</t>
+          <t>10.057216 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="22" t="inlineStr">
         <is>
-          <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -7703,20 +8516,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>263.392 us</t>
+          <t>263.872 us</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6.844887</v>
+        <v>6.833276</v>
       </c>
       <c r="F87" t="n">
-        <v>96.333033</v>
+        <v>96.264078</v>
       </c>
       <c r="G87" t="n">
-        <v>38.253091</v>
+        <v>38.34479</v>
       </c>
       <c r="H87" t="n">
-        <v>32.5683</v>
+        <v>32.574914</v>
       </c>
       <c r="I87" t="n">
         <v>33.333333</v>
@@ -7737,12 +8550,12 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>81.718912 Mbyte</t>
+          <t>81.928192 Mbyte</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>10.092032 Mbyte</t>
+          <t>10.26304 Mbyte</t>
         </is>
       </c>
     </row>
@@ -12292,7 +13105,7 @@
     <row r="165">
       <c r="A165" s="22" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -12305,20 +13118,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>384.288 us</t>
+          <t>384.32 us</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>10.292332</v>
+        <v>10.285178</v>
       </c>
       <c r="F165" t="n">
-        <v>96.411517</v>
+        <v>96.452887</v>
       </c>
       <c r="G165" t="n">
-        <v>96.411517</v>
+        <v>96.452887</v>
       </c>
       <c r="H165" t="n">
-        <v>87.82091800000001</v>
+        <v>87.27867500000001</v>
       </c>
       <c r="I165" t="n">
         <v>100</v>
@@ -12339,19 +13152,19 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>335.560704 Mbyte</t>
+          <t>335.561216 Mbyte</t>
         </is>
       </c>
       <c r="O165" t="inlineStr">
         <is>
-          <t>2.056448 Mbyte</t>
+          <t>2.224512 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="22" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -12364,20 +13177,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>3.136 us</t>
+          <t>3.104 us</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.038032</v>
+        <v>0.03844</v>
       </c>
       <c r="F166" t="n">
-        <v>1.093624</v>
+        <v>1.110147</v>
       </c>
       <c r="G166" t="n">
-        <v>0.29524</v>
+        <v>0.316166</v>
       </c>
       <c r="H166" t="n">
-        <v>15.235129</v>
+        <v>15.405402</v>
       </c>
       <c r="I166" t="n">
         <v>100</v>
@@ -12398,19 +13211,19 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>0.00832 Mbyte</t>
+          <t>0.008448 Mbyte</t>
         </is>
       </c>
       <c r="O166" t="inlineStr">
         <is>
-          <t>0.0 Mbyte</t>
+          <t>0.000384 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="22" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -12423,20 +13236,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>384.32 us</t>
+          <t>384.288 us</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>10.285178</v>
+        <v>10.292332</v>
       </c>
       <c r="F167" t="n">
-        <v>96.452887</v>
+        <v>96.411517</v>
       </c>
       <c r="G167" t="n">
-        <v>96.452887</v>
+        <v>96.411517</v>
       </c>
       <c r="H167" t="n">
-        <v>87.27867500000001</v>
+        <v>87.82091800000001</v>
       </c>
       <c r="I167" t="n">
         <v>100</v>
@@ -12457,19 +13270,19 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>335.561216 Mbyte</t>
+          <t>335.560704 Mbyte</t>
         </is>
       </c>
       <c r="O167" t="inlineStr">
         <is>
-          <t>2.224512 Mbyte</t>
+          <t>2.056448 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="22" t="inlineStr">
         <is>
-          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -12482,20 +13295,20 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>3.104 us</t>
+          <t>3.136 us</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.03844</v>
+        <v>0.038032</v>
       </c>
       <c r="F168" t="n">
-        <v>1.110147</v>
+        <v>1.093624</v>
       </c>
       <c r="G168" t="n">
-        <v>0.316166</v>
+        <v>0.29524</v>
       </c>
       <c r="H168" t="n">
-        <v>15.405402</v>
+        <v>15.235129</v>
       </c>
       <c r="I168" t="n">
         <v>100</v>
@@ -12516,12 +13329,12 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>0.008448 Mbyte</t>
+          <t>0.00832 Mbyte</t>
         </is>
       </c>
       <c r="O168" t="inlineStr">
         <is>
-          <t>0.000384 Mbyte</t>
+          <t>0.0 Mbyte</t>
         </is>
       </c>
     </row>
@@ -12587,7 +13400,7 @@
     <row r="170">
       <c r="A170" s="22" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -12600,20 +13413,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>1.120224 ms</t>
+          <t>1.119968 ms</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>80.98921</v>
+        <v>80.988163</v>
       </c>
       <c r="F170" t="n">
-        <v>75.58993</v>
+        <v>75.58895200000001</v>
       </c>
       <c r="G170" t="n">
-        <v>26.21965</v>
+        <v>26.231674</v>
       </c>
       <c r="H170" t="n">
-        <v>84.800596</v>
+        <v>84.800144</v>
       </c>
       <c r="I170" t="n">
         <v>100</v>
@@ -12634,19 +13447,19 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>50.345344 Mbyte</t>
+          <t>50.34496 Mbyte</t>
         </is>
       </c>
       <c r="O170" t="inlineStr">
         <is>
-          <t>217.301888 Mbyte</t>
+          <t>217.37344 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="22" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -12659,20 +13472,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>1.119968 ms</t>
+          <t>1.120224 ms</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>80.988163</v>
+        <v>80.98921</v>
       </c>
       <c r="F171" t="n">
-        <v>75.58895200000001</v>
+        <v>75.58993</v>
       </c>
       <c r="G171" t="n">
-        <v>26.231674</v>
+        <v>26.21965</v>
       </c>
       <c r="H171" t="n">
-        <v>84.800144</v>
+        <v>84.800596</v>
       </c>
       <c r="I171" t="n">
         <v>100</v>
@@ -12693,12 +13506,12 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>50.34496 Mbyte</t>
+          <t>50.345344 Mbyte</t>
         </is>
       </c>
       <c r="O171" t="inlineStr">
         <is>
-          <t>217.37344 Mbyte</t>
+          <t>217.301888 Mbyte</t>
         </is>
       </c>
     </row>
@@ -12764,7 +13577,7 @@
     <row r="173">
       <c r="A173" s="22" t="inlineStr">
         <is>
-          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -12777,20 +13590,20 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>664.96 us</t>
+          <t>659.456 us</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>3.184013</v>
+        <v>3.153678</v>
       </c>
       <c r="F173" t="n">
-        <v>88.457606</v>
+        <v>89.196668</v>
       </c>
       <c r="G173" t="n">
-        <v>88.457606</v>
+        <v>89.196668</v>
       </c>
       <c r="H173" t="n">
-        <v>93.35373800000001</v>
+        <v>93.17085</v>
       </c>
       <c r="I173" t="n">
         <v>100</v>
@@ -12816,14 +13629,14 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>267.547648 Mbyte</t>
+          <t>267.56864 Mbyte</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="22" t="inlineStr">
         <is>
-          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -12836,20 +13649,20 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>659.456 us</t>
+          <t>664.96 us</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3.153678</v>
+        <v>3.184013</v>
       </c>
       <c r="F174" t="n">
-        <v>89.196668</v>
+        <v>88.457606</v>
       </c>
       <c r="G174" t="n">
-        <v>89.196668</v>
+        <v>88.457606</v>
       </c>
       <c r="H174" t="n">
-        <v>93.17085</v>
+        <v>93.35373800000001</v>
       </c>
       <c r="I174" t="n">
         <v>100</v>
@@ -12875,7 +13688,7 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>267.56864 Mbyte</t>
+          <t>267.547648 Mbyte</t>
         </is>
       </c>
     </row>

--- a/results/cuda_performance.xlsx
+++ b/results/cuda_performance.xlsx
@@ -262,52 +262,52 @@
         <t>Kernels overlap (their summed ncu time is 105% of this time), so all of it scales with the kernels' 1.11x.</t>
       </text>
     </comment>
-    <comment ref="U9" authorId="0" shapeId="0">
+    <comment ref="U10" authorId="0" shapeId="0">
       <text>
         <t>SM-bound (SM 80% busy; L1/L2 39%, DRAM 0%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
-    <comment ref="U10" authorId="0" shapeId="0">
+    <comment ref="U11" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 95% of the RTX 3090 time and predicted 2.29x faster; the other 5% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="U12" authorId="0" shapeId="0">
+    <comment ref="U14" authorId="0" shapeId="0">
       <text>
         <t>L1/L2-bound (L1/L2 96% busy; SM 7%, DRAM 38%): assumed to scale with SMs x clock, 2.32x.</t>
       </text>
     </comment>
-    <comment ref="U13" authorId="0" shapeId="0">
+    <comment ref="U15" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 70% of the RTX 3090 time and predicted 2.29x faster; the other 30% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="U15" authorId="0" shapeId="0">
+    <comment ref="U18" authorId="0" shapeId="0">
       <text>
         <t>DRAM-bound (DRAM 96% busy; SM 10%, L1/L2 96%): data rate 21 / 18.98 Gbps = 1.11x.</t>
       </text>
     </comment>
-    <comment ref="U16" authorId="0" shapeId="0">
+    <comment ref="U19" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="U18" authorId="0" shapeId="0">
+    <comment ref="U22" authorId="0" shapeId="0">
       <text>
         <t>SM-bound (SM 81% busy; L1/L2 76%, DRAM 26%): SMs x clock 128 x 2.52 / (82 x 1.69) GHz = 2.33x.</t>
       </text>
     </comment>
-    <comment ref="U19" authorId="0" shapeId="0">
+    <comment ref="U23" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 10% of the RTX 3090 time and predicted 2.33x faster; the other 90% (copies, gaps) is unchanged.</t>
       </text>
     </comment>
-    <comment ref="U21" authorId="0" shapeId="0">
+    <comment ref="U26" authorId="0" shapeId="0">
       <text>
         <t>DRAM-bound (DRAM 88% busy; SM 3%, L1/L2 88%): data rate 21 / 18.98 Gbps = 1.11x.</t>
       </text>
     </comment>
-    <comment ref="U22" authorId="0" shapeId="0">
+    <comment ref="U27" authorId="0" shapeId="0">
       <text>
         <t>Kernels are 3% of the RTX 3090 time and predicted 1.11x faster; the other 97% (copies, gaps) is unchanged.</t>
       </text>
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB22"/>
+  <dimension ref="A1:AB28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -648,7 +648,7 @@
     <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB), binaries built with CUDA 13.3 (outputs in rtx3090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
+          <t>GPU: NVIDIA GeForce RTX 3090 (sm_86, 24 GB), binaries built with CUDA 13.3 (outputs in rtx3090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, plus the whole application at a small shape where launch cost dominates, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
         </is>
       </c>
     </row>
@@ -1061,115 +1061,89 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>loom_msa (multi-sensor attention)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>fuse_attention_kernel</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>25,000 queries x 250,000 context</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>llama2c (coalesced matmul)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>batch=64, dim=256, rows=512, 32 repeats</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>RTX 3090 (sm_86, 24 GB)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>8174.176</v>
-      </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>nsys-timing-msa_optimized_large-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>8174.304</v>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
-        <is>
-          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>nsys-timing-msa_optimized_large-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" s="13" t="n">
-        <v>4140.032</v>
-      </c>
-      <c r="S9" s="14" t="inlineStr">
-        <is>
-          <t>ncu-all-kernels-msa_sota_large_1chunk-direct-20261016-145900.ncu-rep</t>
-        </is>
-      </c>
-      <c r="T9" s="14" t="inlineStr">
-        <is>
-          <t>nsys-timing-msa_sota_large-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="U9" s="15" t="n"/>
-      <c r="V9" s="15" t="n">
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>112.853</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>112.853</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>113.584</v>
+      </c>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="10" t="n">
+        <v>91.084</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>91.084</v>
+      </c>
+      <c r="M8" s="10" t="n">
+        <v>91.12</v>
+      </c>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="13" t="n">
+        <v>70.877</v>
+      </c>
+      <c r="Q8" s="13" t="n">
+        <v>70.877</v>
+      </c>
+      <c r="R8" s="13" t="n">
+        <v>71.68000000000001</v>
+      </c>
+      <c r="S8" s="18" t="n"/>
+      <c r="T8" s="18" t="n"/>
+      <c r="U8" s="15" t="n">
+        <v>1.239</v>
+      </c>
+      <c r="V8" s="15" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="W8" s="15" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="X8" s="15" t="n">
+        <v>1.271</v>
+      </c>
+      <c r="Y8" s="15" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="Z8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="W9" s="15" t="n"/>
-      <c r="X9" s="15" t="n">
-        <v>2.029</v>
-      </c>
-      <c r="Y9" s="15" t="n"/>
-      <c r="Z9" s="15" t="n"/>
-      <c r="AA9" s="15" t="n"/>
-      <c r="AB9" s="5" t="inlineStr">
-        <is>
-          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). 93% of the whole-application time per iteration. Agentic optimized (launch=direct): msa_sota_attention_kernel (13-way context split, 8 queries per thread) with the projections folded into its loads and the split merge and statistics into its last block. msa_sota_large runs it as 13 concurrent launches, one per imu copy chunk, which ncu would serialize, so ncu profiles msa_sota_large_1chunk, the same kernel as one launch. Compared with the four graph kernels' summed ncu time (8,400.5 us).</t>
+      <c r="AA8" s="15" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="AB8" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. One iteration: 32 repeats of rmsnorm + softmax + matmul (96 kernels of about a microsecond each) on device-resident data, no per-iteration copies. Full batch: 1000 back-to-back iterations between CUDA events (per iteration = full batch / 1000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=graph): llama2c_sota_small, the same implementation at this shape.</t>
         </is>
       </c>
     </row>
@@ -1181,91 +1155,203 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
+          <t>fuse_attention_kernel</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>25,000 queries x 250,000 context</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>8174.176</v>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>ncu-all-kernels-msa_optimized_large-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>8174.304</v>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>ncu-all-kernels-msa_optimized_large-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="O10" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_optimized_large-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>4140.032</v>
+      </c>
+      <c r="S10" s="14" t="inlineStr">
+        <is>
+          <t>ncu-all-kernels-msa_sota_large_1chunk-direct-20261016-145900.ncu-rep</t>
+        </is>
+      </c>
+      <c r="T10" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-msa_sota_large-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U10" s="15" t="n"/>
+      <c r="V10" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" s="15" t="n"/>
+      <c r="X10" s="15" t="n">
+        <v>2.029</v>
+      </c>
+      <c r="Y10" s="15" t="n"/>
+      <c r="Z10" s="15" t="n"/>
+      <c r="AA10" s="15" t="n"/>
+      <c r="AB10" s="5" t="inlineStr">
+        <is>
+          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style). 93% of the whole-application time per iteration. Agentic optimized (launch=direct): msa_sota_attention_kernel (13-way context split, 8 queries per thread) with the projections folded into its loads and the split merge and statistics into its last block. msa_sota_large runs it as 13 concurrent launches, one per imu copy chunk, which ncu would serialize, so ncu profiles msa_sota_large_1chunk, the same kernel as one launch. Compared with the four graph kernels' summed ncu time (8,400.5 us).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>loom_msa (multi-sensor attention)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
           <t>Whole application (H2D + kernels + D2H)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>25,000 queries x 250,000 context</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>RTX 3090 (sm_86, 24 GB)</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Batch and single iteration (cudaEvent)</t>
         </is>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F11" s="7" t="n">
         <v>441.032</v>
       </c>
-      <c r="G10" s="7" t="n">
+      <c r="G11" s="7" t="n">
         <v>8820.639999999999</v>
       </c>
-      <c r="H10" s="7" t="n">
+      <c r="H11" s="7" t="n">
         <v>8886.379999999999</v>
       </c>
-      <c r="I10" s="16" t="n"/>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="8" t="inlineStr">
         <is>
           <t>nsys-timing-msa_optimized_large-direct-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K11" s="10" t="n">
         <v>440.465</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L11" s="10" t="n">
         <v>8809.299999999999</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M11" s="10" t="n">
         <v>8817.58</v>
       </c>
-      <c r="N10" s="17" t="n"/>
-      <c r="O10" s="11" t="inlineStr">
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="11" t="inlineStr">
         <is>
           <t>nsys-timing-msa_optimized_large-graph-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P11" s="13" t="n">
         <v>214.376</v>
       </c>
-      <c r="Q10" s="13" t="n">
+      <c r="Q11" s="13" t="n">
         <v>4287.52</v>
       </c>
-      <c r="R10" s="13" t="n">
+      <c r="R11" s="13" t="n">
         <v>4283.39</v>
       </c>
-      <c r="S10" s="18" t="n"/>
-      <c r="T10" s="14" t="inlineStr">
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="14" t="inlineStr">
         <is>
           <t>nsys-timing-msa_sota_large-direct-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="U10" s="15" t="n">
+      <c r="U11" s="15" t="n">
         <v>1.001</v>
       </c>
-      <c r="V10" s="15" t="n">
+      <c r="V11" s="15" t="n">
         <v>1.008</v>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W11" s="15" t="n">
         <v>2.055</v>
       </c>
-      <c r="X10" s="15" t="n">
+      <c r="X11" s="15" t="n">
         <v>2.059</v>
       </c>
-      <c r="Y10" s="15" t="n">
+      <c r="Y11" s="15" t="n">
         <v>1.007</v>
       </c>
-      <c r="Z10" s="15" t="n">
+      <c r="Z11" s="15" t="n">
         <v>1.001</v>
       </c>
-      <c r="AA10" s="15" t="n">
+      <c r="AA11" s="15" t="n">
         <v>0.999</v>
       </c>
-      <c r="AB10" s="5" t="inlineStr">
+      <c r="AB11" s="5" t="inlineStr">
         <is>
           <t>msa_optimized_large on random inputs, including the H2D input and D2H output copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): msa_sota_large, rotating over 3 random input sets; output written straight to pinned host memory.</t>
         </is>
@@ -1274,227 +1360,215 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>loom_msa (multi-sensor attention)</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>4 queries x 4 context (main.c)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>111.933</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>22.387</v>
+      </c>
+      <c r="H12" s="7" t="n">
+        <v>16.624</v>
+      </c>
+      <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
+      <c r="K12" s="10" t="n">
+        <v>87.453</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>17.491</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>14.336</v>
+      </c>
+      <c r="N12" s="17" t="n"/>
+      <c r="O12" s="17" t="n"/>
+      <c r="P12" s="13" t="n">
+        <v>38.76</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>7.752</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>9.215999999999999</v>
+      </c>
+      <c r="S12" s="18" t="n"/>
+      <c r="T12" s="18" t="n"/>
+      <c r="U12" s="15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V12" s="15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W12" s="15" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="X12" s="15" t="n">
+        <v>1.556</v>
+      </c>
+      <c r="Y12" s="15" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="Z12" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AA12" s="15" t="n">
+        <v>1.189</v>
+      </c>
+      <c r="AB12" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. msa_optimized_4x4 (main.c's shape) on random inputs, including the H2D input and D2H output copies; every copy and kernel moves a few hundred bytes. Full batch: 5000 back-to-back iterations between CUDA events (per iteration = full batch / 5000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=direct): msa_sota_4x4, the same implementation at this shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>pagerank (GAPBS)</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>pagerank_update (one iteration)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>RTX 3090 (sm_86, 24 GB)</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Kernel time (ncu, one launch)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H12" s="7" t="n">
+      <c r="H14" s="7" t="n">
         <v>262.621</v>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>ncu-pagerank-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>nsys-timing-pagerank-direct-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M12" s="10" t="n">
+      <c r="M14" s="10" t="n">
         <v>262.754</v>
       </c>
-      <c r="N12" s="11" t="inlineStr">
+      <c r="N14" s="11" t="inlineStr">
         <is>
           <t>ncu-pagerank-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
-      <c r="O12" s="11" t="inlineStr">
+      <c r="O14" s="11" t="inlineStr">
         <is>
           <t>nsys-timing-pagerank-graph-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="P12" s="12" t="inlineStr">
+      <c r="P14" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="Q12" s="12" t="inlineStr">
+      <c r="Q14" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="R12" s="13" t="n">
+      <c r="R14" s="13" t="n">
         <v>155.326</v>
       </c>
-      <c r="S12" s="14" t="inlineStr">
+      <c r="S14" s="14" t="inlineStr">
         <is>
           <t>ncu-pagerank-sota-direct-20261016-145900.ncu-rep</t>
         </is>
       </c>
-      <c r="T12" s="14" t="inlineStr">
+      <c r="T14" s="14" t="inlineStr">
         <is>
           <t>nsys-timing-pagerank_sota-direct-20261020-161213.sqlite</t>
         </is>
       </c>
-      <c r="U12" s="15" t="n"/>
-      <c r="V12" s="15" t="n">
+      <c r="U14" s="15" t="n"/>
+      <c r="V14" s="15" t="n">
         <v>0.999</v>
       </c>
-      <c r="W12" s="15" t="n"/>
-      <c r="X12" s="15" t="n">
+      <c r="W14" s="15" t="n"/>
+      <c r="X14" s="15" t="n">
         <v>1.692</v>
       </c>
-      <c r="Y12" s="15" t="n"/>
-      <c r="Z12" s="15" t="n"/>
-      <c r="AA12" s="15" t="n"/>
-      <c r="AB12" s="5" t="inlineStr">
+      <c r="Y14" s="15" t="n"/>
+      <c r="Z14" s="15" t="n"/>
+      <c r="AA14" s="15" t="n"/>
+      <c r="AB14" s="5" t="inlineStr">
         <is>
           <t>Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks of ~41 us each. 19 full iterations = 65% of the whole-application time per iteration. Agentic optimized (launch=direct): binned_update_kernel, summed over iterations 1-19 / 19: a cooperative pull over destination parts that fit in shared memory, with edges sorted by source sector on the GPU during the upload (5.4M instead of 16.8M gathered sectors per iteration).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>pagerank (GAPBS)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Whole application (H2D + 20 iterations + D2H)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>RTX 3090 (sm_86, 24 GB)</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Batch and single iteration (cudaEvent)</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>385.722</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>7714.44</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>7662</v>
-      </c>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>nsys-timing-pagerank-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="K13" s="10" t="n">
-        <v>382.343</v>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>7646.86</v>
-      </c>
-      <c r="M13" s="10" t="n">
-        <v>7642</v>
-      </c>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>nsys-timing-pagerank-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>297.939</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>5958.78</v>
-      </c>
-      <c r="R13" s="13" t="n">
-        <v>5932</v>
-      </c>
-      <c r="S13" s="18" t="n"/>
-      <c r="T13" s="14" t="inlineStr">
-        <is>
-          <t>nsys-timing-pagerank_sota-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="U13" s="15" t="n">
-        <v>1.009</v>
-      </c>
-      <c r="V13" s="15" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="W13" s="15" t="n">
-        <v>1.283</v>
-      </c>
-      <c r="X13" s="15" t="n">
-        <v>1.288</v>
-      </c>
-      <c r="Y13" s="15" t="n">
-        <v>0.993</v>
-      </c>
-      <c r="Z13" s="15" t="n">
-        <v>0.999</v>
-      </c>
-      <c r="AA13" s="15" t="n">
-        <v>0.996</v>
-      </c>
-      <c r="AB13" s="5" t="inlineStr">
-        <is>
-          <t>One iteration is one PageRank run: the CSR graph uploaded from pinned memory in 8 chunks overlapped with the first of 20 iterations, then the scores downloaded. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs (the benchmark graph and two random graphs of the same size); includes the on-GPU edge sort.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny anomaly</t>
+          <t>pagerank (GAPBS)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>mse_partial_kernel</t>
+          <t>Whole application (H2D + 20 iterations + D2H)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>64M elements</t>
+          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1504,109 +1578,95 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>385.722</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>7714.44</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>384.32</v>
-      </c>
-      <c r="I15" s="8" t="inlineStr">
-        <is>
-          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
+        <v>7662</v>
+      </c>
+      <c r="I15" s="16" t="n"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="K15" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>nsys-timing-pagerank-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K15" s="10" t="n">
+        <v>382.343</v>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>7646.86</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>384.288</v>
-      </c>
-      <c r="N15" s="11" t="inlineStr">
-        <is>
-          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
+        <v>7642</v>
+      </c>
+      <c r="N15" s="17" t="n"/>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="P15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>nsys-timing-pagerank-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>297.939</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>5958.78</v>
       </c>
       <c r="R15" s="13" t="n">
-        <v>386.24</v>
-      </c>
-      <c r="S15" s="14" t="inlineStr">
-        <is>
-          <t>ncu-anomaly_mse_sota-graph-20261016-145900.ncu-rep</t>
-        </is>
-      </c>
+        <v>5932</v>
+      </c>
+      <c r="S15" s="18" t="n"/>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="U15" s="15" t="n"/>
+          <t>nsys-timing-pagerank_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U15" s="15" t="n">
+        <v>1.009</v>
+      </c>
       <c r="V15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="W15" s="15" t="n"/>
+        <v>1.003</v>
+      </c>
+      <c r="W15" s="15" t="n">
+        <v>1.283</v>
+      </c>
       <c r="X15" s="15" t="n">
-        <v>1.003</v>
-      </c>
-      <c r="Y15" s="15" t="n"/>
-      <c r="Z15" s="15" t="n"/>
-      <c r="AA15" s="15" t="n"/>
+        <v>1.288</v>
+      </c>
+      <c r="Y15" s="15" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="Z15" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AA15" s="15" t="n">
+        <v>0.996</v>
+      </c>
       <c r="AB15" s="5" t="inlineStr">
         <is>
-          <t>3% of the whole-application time per iteration. Agentic optimized (launch=graph): mse_sota_kernel, one single-pass reduction (the last block finishes the sum), compared with mse_partial_kernel + mse_finalize_kernel.</t>
+          <t>One iteration is one PageRank run: the CSR graph uploaded from pinned memory in 8 chunks overlapped with the first of 20 iterations, then the scores downloaded. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs (the benchmark graph and two random graphs of the same size); includes the on-GPU edge sort.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny anomaly</t>
+          <t>pagerank (GAPBS)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Whole application (H2D + kernels + D2H)</t>
+          <t>Whole application, small shape (launch-bound)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>64M elements</t>
+          <t>2^14 vertices, 16 edges/vertex, 20 iterations</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1620,91 +1680,79 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>708.449</v>
+        <v>168.731</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>14168.98</v>
+        <v>168.731</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>14165.36</v>
+        <v>170</v>
       </c>
       <c r="I16" s="16" t="n"/>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
+      <c r="J16" s="16" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>708.564</v>
+        <v>159.4</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>14171.28</v>
+        <v>159.4</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>14163.28</v>
+        <v>156</v>
       </c>
       <c r="N16" s="17" t="n"/>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
+      <c r="O16" s="17" t="n"/>
       <c r="P16" s="13" t="n">
-        <v>691.636</v>
+        <v>602.149</v>
       </c>
       <c r="Q16" s="13" t="n">
-        <v>13832.72</v>
+        <v>602.149</v>
       </c>
       <c r="R16" s="13" t="n">
-        <v>13830.608</v>
+        <v>605</v>
       </c>
       <c r="S16" s="18" t="n"/>
-      <c r="T16" s="14" t="inlineStr">
-        <is>
-          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
+      <c r="T16" s="18" t="n"/>
       <c r="U16" s="15" t="n">
-        <v>1</v>
+        <v>1.059</v>
       </c>
       <c r="V16" s="15" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="W16" s="15" t="n">
-        <v>1.024</v>
+        <v>0.265</v>
       </c>
       <c r="X16" s="15" t="n">
-        <v>1.024</v>
+        <v>0.258</v>
       </c>
       <c r="Y16" s="15" t="n">
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="Z16" s="15" t="n">
-        <v>0.999</v>
+        <v>0.979</v>
       </c>
       <c r="AA16" s="15" t="n">
-        <v>1</v>
+        <v>1.005</v>
       </c>
       <c r="AB16" s="5" t="inlineStr">
         <is>
-          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=graph): rotating over 3 inputs; the float input is copied in shrinking chunks while a second stream reduces each chunk as it lands; the result is written straight to pinned host memory.</t>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The same PageRank run on a 2^14-vertex graph (make -C pagerank small): upload, 20 iterations of a few microseconds each, download. Full batch: 1000 back-to-back iterations between CUDA events (per iteration = full batch / 1000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=direct): pagerank_sota_small, the same implementation at this shape.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny KWS</t>
+          <t>mlperf-tiny anomaly</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>kws_postprocess_kernel</t>
+          <t>mse_partial_kernel</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>12 classes x 4M rows</t>
+          <t>64M elements</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1728,16 +1776,16 @@
         </is>
       </c>
       <c r="H18" s="7" t="n">
-        <v>1119.968</v>
+        <v>384.32</v>
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-direct-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="J18" s="8" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -1751,16 +1799,16 @@
         </is>
       </c>
       <c r="M18" s="10" t="n">
-        <v>1120.224</v>
+        <v>384.288</v>
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
+          <t>ncu-anomaly_mse-graph-20261015-224015.ncu-rep</t>
         </is>
       </c>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
@@ -1774,16 +1822,16 @@
         </is>
       </c>
       <c r="R18" s="13" t="n">
-        <v>323.072</v>
+        <v>386.24</v>
       </c>
       <c r="S18" s="14" t="inlineStr">
         <is>
-          <t>ncu-kws_postprocess_sota-direct-20261016-145900.ncu-rep</t>
+          <t>ncu-anomaly_mse_sota-graph-20261016-145900.ncu-rep</t>
         </is>
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="U18" s="15" t="n"/>
@@ -1792,21 +1840,21 @@
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="15" t="n">
-        <v>3.467</v>
+        <v>1.003</v>
       </c>
       <c r="Y18" s="15" t="n"/>
       <c r="Z18" s="15" t="n"/>
       <c r="AA18" s="15" t="n"/>
       <c r="AB18" s="5" t="inlineStr">
         <is>
-          <t>Only kernel in the application. 10% of the whole-application time per iteration. Agentic optimized (launch=direct): kws_postprocess_sota_kernel on device buffers (kernels-only), one row per thread with rows staged through shared memory for coalesced 16 B loads and stores.</t>
+          <t>3% of the whole-application time per iteration. Agentic optimized (launch=graph): mse_sota_kernel, one single-pass reduction (the last block finishes the sum), compared with mse_partial_kernel + mse_finalize_kernel.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny KWS</t>
+          <t>mlperf-tiny anomaly</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1816,7 +1864,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>12 classes x 4M rows</t>
+          <t>64M elements</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1830,48 +1878,48 @@
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>568.751</v>
+        <v>708.449</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>11375.02</v>
+        <v>14168.98</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>11370.864</v>
+        <v>14165.36</v>
       </c>
       <c r="I19" s="16" t="n"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse-direct-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="K19" s="10" t="n">
-        <v>568.535</v>
+        <v>708.564</v>
       </c>
       <c r="L19" s="10" t="n">
-        <v>11370.7</v>
+        <v>14171.28</v>
       </c>
       <c r="M19" s="10" t="n">
-        <v>11376.016</v>
+        <v>14163.28</v>
       </c>
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse-graph-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="P19" s="13" t="n">
-        <v>433.252</v>
+        <v>691.636</v>
       </c>
       <c r="Q19" s="13" t="n">
-        <v>8665.040000000001</v>
+        <v>13832.72</v>
       </c>
       <c r="R19" s="13" t="n">
-        <v>8654.575999999999</v>
+        <v>13830.608</v>
       </c>
       <c r="S19" s="18" t="n"/>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+          <t>nsys-timing-anomaly_mse_sota-graph-20261020-161213.sqlite</t>
         </is>
       </c>
       <c r="U19" s="15" t="n">
@@ -1881,152 +1929,126 @@
         <v>1</v>
       </c>
       <c r="W19" s="15" t="n">
-        <v>1.312</v>
+        <v>1.024</v>
       </c>
       <c r="X19" s="15" t="n">
-        <v>1.314</v>
+        <v>1.024</v>
       </c>
       <c r="Y19" s="15" t="n">
         <v>1</v>
       </c>
       <c r="Z19" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AA19" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AA19" s="15" t="n">
-        <v>0.999</v>
-      </c>
       <c r="AB19" s="5" t="inlineStr">
         <is>
-          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs; one zero-copy kernel reads the int8 rows from and writes the probabilities and argmax to mapped pinned host memory, so both PCIe directions stream at once.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>mlperf-tiny VWW</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>vww_preprocess_kernel</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>256M bytes</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=graph): rotating over 3 inputs; the float input is copied in shrinking chunks while a second stream reduces each chunk as it lands; the result is written straight to pinned host memory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny anomaly</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>16 elements (smoke)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>RTX 3090 (sm_86, 24 GB)</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="n">
-        <v>659.456</v>
-      </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="10" t="n">
-        <v>664.96</v>
-      </c>
-      <c r="N21" s="11" t="inlineStr">
-        <is>
-          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
-        </is>
-      </c>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="P21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" s="13" t="n">
-        <v>634.72</v>
-      </c>
-      <c r="S21" s="14" t="inlineStr">
-        <is>
-          <t>ncu-vww_preprocess_sota-direct-20261016-145900.ncu-rep</t>
-        </is>
-      </c>
-      <c r="T21" s="14" t="inlineStr">
-        <is>
-          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="U21" s="15" t="n"/>
-      <c r="V21" s="15" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="W21" s="15" t="n"/>
-      <c r="X21" s="15" t="n">
-        <v>1.048</v>
-      </c>
-      <c r="Y21" s="15" t="n"/>
-      <c r="Z21" s="15" t="n"/>
-      <c r="AA21" s="15" t="n"/>
-      <c r="AB21" s="5" t="inlineStr">
-        <is>
-          <t>Only kernel in the application. 3% of the whole-application time per iteration. Agentic optimized (launch=direct): vww_preprocess_sota_kernel on device buffers (kernels-only), four 16 B vectors per thread.</t>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>17.533</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>17.533</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>13.616</v>
+      </c>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="10" t="n">
+        <v>17.393</v>
+      </c>
+      <c r="L20" s="10" t="n">
+        <v>17.393</v>
+      </c>
+      <c r="M20" s="10" t="n">
+        <v>20.272</v>
+      </c>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="17" t="n"/>
+      <c r="P20" s="13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q20" s="13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R20" s="13" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" s="18" t="n"/>
+      <c r="U20" s="15" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="V20" s="15" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="W20" s="15" t="n">
+        <v>5.352</v>
+      </c>
+      <c r="X20" s="15" t="n">
+        <v>4.949</v>
+      </c>
+      <c r="Y20" s="15" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="Z20" s="15" t="n">
+        <v>1.166</v>
+      </c>
+      <c r="AA20" s="15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AB20" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each. Full batch: 1000 back-to-back iterations between CUDA events (per iteration = full batch / 1000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=graph): anomaly_mse_sota_small, the same implementation at this shape.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny VWW</t>
+          <t>mlperf-tiny KWS</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Whole application (H2D + kernels + D2H)</t>
+          <t>kws_postprocess_kernel</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>256M bytes</t>
+          <t>12 classes x 4M rows</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -2036,78 +2058,572 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Batch and single iteration (cudaEvent)</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1094.1</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <v>21882</v>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="H22" s="7" t="n">
-        <v>21881.408</v>
-      </c>
-      <c r="I22" s="16" t="n"/>
+        <v>1119.968</v>
+      </c>
+      <c r="I22" s="8" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
       <c r="J22" s="8" t="inlineStr">
         <is>
-          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="K22" s="10" t="n">
-        <v>1093.995</v>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>21879.9</v>
+          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M22" s="10" t="n">
-        <v>21880.512</v>
-      </c>
-      <c r="N22" s="17" t="n"/>
+        <v>1120.224</v>
+      </c>
+      <c r="N22" s="11" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="P22" s="13" t="n">
-        <v>613.24</v>
-      </c>
-      <c r="Q22" s="13" t="n">
-        <v>12264.8</v>
+          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="R22" s="13" t="n">
-        <v>12253.552</v>
-      </c>
-      <c r="S22" s="18" t="n"/>
+        <v>323.072</v>
+      </c>
+      <c r="S22" s="14" t="inlineStr">
+        <is>
+          <t>ncu-kws_postprocess_sota-direct-20261016-145900.ncu-rep</t>
+        </is>
+      </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
-        </is>
-      </c>
-      <c r="U22" s="15" t="n">
-        <v>1</v>
-      </c>
+          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U22" s="15" t="n"/>
       <c r="V22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="W22" s="15" t="n">
+      <c r="W22" s="15" t="n"/>
+      <c r="X22" s="15" t="n">
+        <v>3.467</v>
+      </c>
+      <c r="Y22" s="15" t="n"/>
+      <c r="Z22" s="15" t="n"/>
+      <c r="AA22" s="15" t="n"/>
+      <c r="AB22" s="5" t="inlineStr">
+        <is>
+          <t>Only kernel in the application. 10% of the whole-application time per iteration. Agentic optimized (launch=direct): kws_postprocess_sota_kernel on device buffers (kernels-only), one row per thread with rows staged through shared memory for coalesced 16 B loads and stores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 4M rows</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>568.751</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>11375.02</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>11370.864</v>
+      </c>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="n">
+        <v>568.535</v>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>11370.7</v>
+      </c>
+      <c r="M23" s="10" t="n">
+        <v>11376.016</v>
+      </c>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P23" s="13" t="n">
+        <v>433.252</v>
+      </c>
+      <c r="Q23" s="13" t="n">
+        <v>8665.040000000001</v>
+      </c>
+      <c r="R23" s="13" t="n">
+        <v>8654.575999999999</v>
+      </c>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-kws_postprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" s="15" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="X23" s="15" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="Y23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="AB23" s="5" t="inlineStr">
+        <is>
+          <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs; one zero-copy kernel reads the int8 rows from and writes the probabilities and argmax to mapped pinned host memory, so both PCIe directions stream at once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 1 row (smoke)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>10.668</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>10.668</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>20.832</v>
+      </c>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="10" t="n">
+        <v>9.369</v>
+      </c>
+      <c r="L24" s="10" t="n">
+        <v>9.369</v>
+      </c>
+      <c r="M24" s="10" t="n">
+        <v>20.752</v>
+      </c>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="17" t="n"/>
+      <c r="P24" s="13" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="Q24" s="13" t="n">
+        <v>2.838</v>
+      </c>
+      <c r="R24" s="13" t="n">
+        <v>4.096</v>
+      </c>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="n"/>
+      <c r="U24" s="15" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="V24" s="15" t="n">
+        <v>1.004</v>
+      </c>
+      <c r="W24" s="15" t="n">
+        <v>3.301</v>
+      </c>
+      <c r="X24" s="15" t="n">
+        <v>5.066</v>
+      </c>
+      <c r="Y24" s="15" t="n">
+        <v>1.953</v>
+      </c>
+      <c r="Z24" s="15" t="n">
+        <v>2.215</v>
+      </c>
+      <c r="AA24" s="15" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="AB24" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each. Full batch: 1000 back-to-back iterations between CUDA events (per iteration = full batch / 1000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=direct): kws_postprocess_sota_small, the same implementation at this shape.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>vww_preprocess_kernel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>659.456</v>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-direct-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="n">
+        <v>664.96</v>
+      </c>
+      <c r="N26" s="11" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess-graph-20261015-224015.ncu-rep</t>
+        </is>
+      </c>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R26" s="13" t="n">
+        <v>634.72</v>
+      </c>
+      <c r="S26" s="14" t="inlineStr">
+        <is>
+          <t>ncu-vww_preprocess_sota-direct-20261016-145900.ncu-rep</t>
+        </is>
+      </c>
+      <c r="T26" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U26" s="15" t="n"/>
+      <c r="V26" s="15" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="W26" s="15" t="n"/>
+      <c r="X26" s="15" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="Y26" s="15" t="n"/>
+      <c r="Z26" s="15" t="n"/>
+      <c r="AA26" s="15" t="n"/>
+      <c r="AB26" s="5" t="inlineStr">
+        <is>
+          <t>Only kernel in the application. 3% of the whole-application time per iteration. Agentic optimized (launch=direct): vww_preprocess_sota_kernel on device buffers (kernels-only), four 16 B vectors per thread.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>1094.1</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>21882</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>21881.408</v>
+      </c>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="n">
+        <v>1093.995</v>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>21879.9</v>
+      </c>
+      <c r="M27" s="10" t="n">
+        <v>21880.512</v>
+      </c>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess-graph-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="P27" s="13" t="n">
+        <v>613.24</v>
+      </c>
+      <c r="Q27" s="13" t="n">
+        <v>12264.8</v>
+      </c>
+      <c r="R27" s="13" t="n">
+        <v>12253.552</v>
+      </c>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="14" t="inlineStr">
+        <is>
+          <t>nsys-timing-vww_preprocess_sota-direct-20261020-161213.sqlite</t>
+        </is>
+      </c>
+      <c r="U27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="V27" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" s="15" t="n">
         <v>1.784</v>
       </c>
-      <c r="X22" s="15" t="n">
+      <c r="X27" s="15" t="n">
         <v>1.786</v>
       </c>
-      <c r="Y22" s="15" t="n">
+      <c r="Y27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="Z22" s="15" t="n">
+      <c r="Z27" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="AA22" s="15" t="n">
+      <c r="AA27" s="15" t="n">
         <v>0.999</v>
       </c>
-      <c r="AB22" s="5" t="inlineStr">
+      <c r="AB27" s="5" t="inlineStr">
         <is>
           <t>Random inputs, including the H2D and D2H copies. Full batch: 50 back-to-back iterations between CUDA events (per iteration = full batch / 50). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 5 interleaved runs (time_all.sh). Agentic optimized (launch=direct): rotating over 3 inputs; 64 chunks of 4 MiB on separate copy-in, compute and copy-out streams, so H2D and D2H overlap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>16 bytes (smoke)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>RTX 3090 (sm_86, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>8.733000000000001</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>8.733000000000001</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>19.76</v>
+      </c>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="10" t="n">
+        <v>8.074999999999999</v>
+      </c>
+      <c r="L28" s="10" t="n">
+        <v>8.074999999999999</v>
+      </c>
+      <c r="M28" s="10" t="n">
+        <v>19.776</v>
+      </c>
+      <c r="N28" s="17" t="n"/>
+      <c r="O28" s="17" t="n"/>
+      <c r="P28" s="13" t="n">
+        <v>12.097</v>
+      </c>
+      <c r="Q28" s="13" t="n">
+        <v>12.097</v>
+      </c>
+      <c r="R28" s="13" t="n">
+        <v>21.376</v>
+      </c>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="n"/>
+      <c r="U28" s="15" t="n">
+        <v>1.081</v>
+      </c>
+      <c r="V28" s="15" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="W28" s="15" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="X28" s="15" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="Y28" s="15" t="n">
+        <v>2.263</v>
+      </c>
+      <c r="Z28" s="15" t="n">
+        <v>2.449</v>
+      </c>
+      <c r="AA28" s="15" t="n">
+        <v>1.767</v>
+      </c>
+      <c r="AB28" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each. Full batch: 1000 back-to-back iterations between CUDA events (per iteration = full batch / 1000). Single iteration: median of 20 iterations, each launched alone on an idle device, so its launch cost is not hidden behind the previous iteration's work. Each time is the median of 9 interleaved runs (time_all.sh). Agentic optimized (launch=direct): vww_preprocess_sota_small, the same implementation at this shape.</t>
         </is>
       </c>
     </row>
@@ -2149,111 +2665,165 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R7" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T7" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J9" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R9" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S9" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T9" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F10" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K10" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J12" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S12" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T12" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J13" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K13" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R13" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T13" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S15" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J16" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T16" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H21" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J21" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R21" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S21" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T21" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K22" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F8" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K8" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R8" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H10" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J10" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R10" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S10" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T10" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F11" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J11" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K11" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R11" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T11" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K12" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R12" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J14" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R14" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S14" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T14" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F15" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J15" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K15" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R15" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T15" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K16" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R16" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H18" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J18" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R18" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S18" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T18" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H19" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J19" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K19" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R19" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T19" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H20" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K20" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R20" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H22" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J22" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R22" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S22" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T22" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F23" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H23" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J23" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K23" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R23" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T23" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F24" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H24" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K24" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R24" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H26" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J26" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R26" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S26" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T26" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H27" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J27" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K27" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P27" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R27" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="T27" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H28" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K28" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P28" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="R28" r:id="rId180"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2265,7 +2835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y28"/>
+  <dimension ref="A1:Y34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2305,7 +2875,7 @@
     <row r="2" ht="75" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GPU: NVIDIA GeForce RTX 4090 (sm_89, 24 GB), binaries built with CUDA 12.5 (outputs in rtx4090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
+          <t>GPU: NVIDIA GeForce RTX 4090 (sm_89, 24 GB), binaries built with CUDA 12.5 (outputs in rtx4090/). Lower is better. Latest run of each workload's current implementation at the largest problem size tested: the dominant kernel (if one dominates) and the whole application, plus the whole application at a small shape where launch cost dominates, launched directly, as a CUDA Graph, and as the agentic optimized version (&lt;name&gt;_sota.cu, formerly SOTA: the fastest implementation found, same work per iteration, launched whichever way is fastest). Full batch = one batch of back-to-back iterations; per iteration = full batch / iterations; single iteration = median of iterations each launched alone on an idle device, so launch cost is exposed rather than overlapped with the previous iteration. Each value links to its source; the ncu-rep / nsys sqlite columns link the profile files on GitHub. ncu replays each kernel in isolation, so kernel rows have one single-launch time.</t>
         </is>
       </c>
     </row>
@@ -2674,99 +3244,69 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>loom_msa (multi-sensor attention)</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>fuse_attention_kernel</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>25,000 queries x 250,000 context</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>llama2c (coalesced matmul)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>batch=64, dim=256, rows=512, 32 repeats</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>RTX 4090 (sm_89, 24 GB)</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="n"/>
-      <c r="J9" s="16" t="n"/>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>pending (ncu not run yet)</t>
-        </is>
-      </c>
-      <c r="N9" s="17" t="n"/>
-      <c r="O9" s="11" t="inlineStr">
-        <is>
-          <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
-        </is>
-      </c>
-      <c r="P9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q9" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R9" s="12" t="inlineStr">
-        <is>
-          <t>pending (agentic optimized not profiled yet)</t>
-        </is>
-      </c>
-      <c r="S9" s="18" t="n"/>
-      <c r="T9" s="18" t="n"/>
-      <c r="U9" s="15" t="n">
-        <v>2.327</v>
-      </c>
-      <c r="V9" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!M9),ISNUMBER(M9)),'RTX 3090'!M9/M9,"pending")</f>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F8" s="16" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="H8" s="16" t="n"/>
+      <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="17" t="n"/>
+      <c r="L8" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="M8" s="17" t="n"/>
+      <c r="N8" s="17" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="18" t="n"/>
+      <c r="Q8" s="12" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="R8" s="18" t="n"/>
+      <c r="S8" s="18" t="n"/>
+      <c r="T8" s="18" t="n"/>
+      <c r="U8" s="15" t="n"/>
+      <c r="V8" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L8),ISNUMBER(L8)),'RTX 3090'!L8/L8,"pending")</f>
         <v/>
       </c>
-      <c r="W9" s="15" t="n"/>
-      <c r="X9" s="15" t="n"/>
-      <c r="Y9" s="5" t="inlineStr">
-        <is>
-          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style).</t>
+      <c r="W8" s="15" t="n"/>
+      <c r="X8" s="15" t="n"/>
+      <c r="Y8" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. One iteration: 32 repeats of rmsnorm + softmax + matmul (96 kernels of about a microsecond each) on device-resident data, no per-iteration copies.</t>
         </is>
       </c>
     </row>
@@ -2778,7 +3318,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Whole application (H2D + kernels + D2H)</t>
+          <t>fuse_attention_kernel</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2793,29 +3333,39 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (cudaEvent)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="n"/>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
           <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
-      <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n"/>
       <c r="J10" s="16" t="n"/>
       <c r="K10" s="9" t="inlineStr">
         <is>
-          <t>pending (time_all.sh not run yet)</t>
-        </is>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>3835.57</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
-          <t>pending (time_all.sh not run yet)</t>
+          <t>pending (ncu not run yet)</t>
         </is>
       </c>
       <c r="N10" s="17" t="n"/>
@@ -2824,26 +3374,112 @@
           <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
         </is>
       </c>
-      <c r="P10" s="18" t="n"/>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q10" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R10" s="12" t="inlineStr">
+        <is>
           <t>pending (agentic optimized not profiled yet)</t>
         </is>
       </c>
-      <c r="R10" s="18" t="n"/>
       <c r="S10" s="18" t="n"/>
       <c r="T10" s="18" t="n"/>
       <c r="U10" s="15" t="n">
-        <v>2.162</v>
+        <v>2.327</v>
       </c>
       <c r="V10" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!L10),ISNUMBER(L10)),'RTX 3090'!L10/L10,"pending")</f>
+        <f>IF(AND(ISNUMBER('RTX 3090'!M10),ISNUMBER(M10)),'RTX 3090'!M10/M10,"pending")</f>
         <v/>
       </c>
       <c r="W10" s="15" t="n"/>
       <c r="X10" s="15" t="n"/>
       <c r="Y10" s="5" t="inlineStr">
         <is>
+          <t>Single-pass online softmax, shared-memory context tiles, 8-way context split (FlashAttention-style).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>loom_msa (multi-sensor attention)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>25,000 queries x 250,000 context</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Iteration time (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F11" s="16" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H11" s="16" t="n"/>
+      <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>3835.57</v>
+      </c>
+      <c r="M11" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="11" t="inlineStr">
+        <is>
+          <t>nsys-msa_optimized_large-20261015-091307.sqlite</t>
+        </is>
+      </c>
+      <c r="P11" s="18" t="n"/>
+      <c r="Q11" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R11" s="18" t="n"/>
+      <c r="S11" s="18" t="n"/>
+      <c r="T11" s="18" t="n"/>
+      <c r="U11" s="15" t="n">
+        <v>2.162</v>
+      </c>
+      <c r="V11" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L11),ISNUMBER(L11)),'RTX 3090'!L11/L11,"pending")</f>
+        <v/>
+      </c>
+      <c r="W11" s="15" t="n"/>
+      <c r="X11" s="15" t="n"/>
+      <c r="Y11" s="5" t="inlineStr">
+        <is>
           <t>benchmark.py: median of 5 runs, random inputs, CUDA graph only. Includes H2D input and D2H output copies.</t>
         </is>
       </c>
@@ -2851,17 +3487,17 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>pagerank (GAPBS)</t>
+          <t>loom_msa (multi-sensor attention)</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>pagerank_update (one iteration)</t>
+          <t>Whole application, small shape (launch-bound)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
+          <t>4 queries x 4 context (main.c)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -2871,171 +3507,159 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="n"/>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n"/>
       <c r="J12" s="16" t="n"/>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="K12" s="17" t="n"/>
       <c r="L12" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M12" s="9" t="inlineStr">
-        <is>
-          <t>pending (ncu not run yet)</t>
-        </is>
-      </c>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n"/>
       <c r="N12" s="17" t="n"/>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>nsys-20261015-091708.sqlite</t>
-        </is>
-      </c>
-      <c r="P12" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="O12" s="17" t="n"/>
+      <c r="P12" s="18" t="n"/>
       <c r="Q12" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R12" s="12" t="inlineStr">
-        <is>
-          <t>pending (agentic optimized not profiled yet)</t>
-        </is>
-      </c>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="R12" s="18" t="n"/>
       <c r="S12" s="18" t="n"/>
       <c r="T12" s="18" t="n"/>
-      <c r="U12" s="15" t="n">
-        <v>2.325</v>
-      </c>
+      <c r="U12" s="15" t="n"/>
       <c r="V12" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!M12),ISNUMBER(M12)),'RTX 3090'!M12/M12,"pending")</f>
+        <f>IF(AND(ISNUMBER('RTX 3090'!L12),ISNUMBER(L12)),'RTX 3090'!L12/L12,"pending")</f>
         <v/>
       </c>
       <c r="W12" s="15" t="n"/>
       <c r="X12" s="15" t="n"/>
       <c r="Y12" s="5" t="inlineStr">
         <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. msa_optimized_4x4 (main.c's shape) on random inputs, including the H2D input and D2H output copies; every copy and kernel moves a few hundred bytes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>pagerank (GAPBS)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>pagerank_update (one iteration)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L14" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="9" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="N14" s="17" t="n"/>
+      <c r="O14" s="11" t="inlineStr">
+        <is>
+          <t>nsys-20261015-091708.sqlite</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q14" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R14" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S14" s="18" t="n"/>
+      <c r="T14" s="18" t="n"/>
+      <c r="U14" s="15" t="n">
+        <v>2.325</v>
+      </c>
+      <c r="V14" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M14),ISNUMBER(M14)),'RTX 3090'!M14/M14,"pending")</f>
+        <v/>
+      </c>
+      <c r="W14" s="15" t="n"/>
+      <c r="X14" s="15" t="n"/>
+      <c r="Y14" s="5" t="inlineStr">
+        <is>
           <t>Pull gather of precomputed contributions. Full-graph iterations only; the first iteration runs as 8 upload-overlapped chunks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>pagerank (GAPBS)</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>Whole application (H2D + 20 iterations + D2H)</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>RTX 4090 (sm_89, 24 GB)</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="n"/>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="n"/>
-      <c r="I13" s="16" t="n"/>
-      <c r="J13" s="16" t="n"/>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>pending (time_all.sh not run yet)</t>
-        </is>
-      </c>
-      <c r="L13" s="10" t="n">
-        <v>5754.945</v>
-      </c>
-      <c r="M13" s="9" t="inlineStr">
-        <is>
-          <t>pending (time_all.sh not run yet)</t>
-        </is>
-      </c>
-      <c r="N13" s="17" t="n"/>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>nsys-20261015-091708.sqlite</t>
-        </is>
-      </c>
-      <c r="P13" s="18" t="n"/>
-      <c r="Q13" s="12" t="inlineStr">
-        <is>
-          <t>pending (agentic optimized not profiled yet)</t>
-        </is>
-      </c>
-      <c r="R13" s="18" t="n"/>
-      <c r="S13" s="18" t="n"/>
-      <c r="T13" s="18" t="n"/>
-      <c r="U13" s="15" t="n">
-        <v>1.648</v>
-      </c>
-      <c r="V13" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!L13),ISNUMBER(L13)),'RTX 3090'!L13/L13,"pending")</f>
-        <v/>
-      </c>
-      <c r="W13" s="15" t="n"/>
-      <c r="X13" s="15" t="n"/>
-      <c r="Y13" s="5" t="inlineStr">
-        <is>
-          <t>Median GPU span of the 1693 graph replays with copies in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny anomaly</t>
+          <t>pagerank (GAPBS)</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>mse_partial_kernel</t>
+          <t>Whole application (H2D + 20 iterations + D2H)</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>64M elements</t>
+          <t>2^20 vertices, 16 edges/vertex, 20 iterations</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -3045,89 +3669,75 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>Iteration time (nsys)</t>
+        </is>
+      </c>
+      <c r="F15" s="16" t="n"/>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
           <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
+      <c r="H15" s="16" t="n"/>
       <c r="I15" s="16" t="n"/>
       <c r="J15" s="16" t="n"/>
       <c r="K15" s="9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L15" s="10" t="n">
+        <v>5754.945</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
-          <t>pending (ncu not run yet)</t>
+          <t>pending (time_all.sh not run yet)</t>
         </is>
       </c>
       <c r="N15" s="17" t="n"/>
       <c r="O15" s="11" t="inlineStr">
         <is>
-          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
-        </is>
-      </c>
-      <c r="P15" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>nsys-20261015-091708.sqlite</t>
+        </is>
+      </c>
+      <c r="P15" s="18" t="n"/>
       <c r="Q15" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R15" s="12" t="inlineStr">
-        <is>
           <t>pending (agentic optimized not profiled yet)</t>
         </is>
       </c>
+      <c r="R15" s="18" t="n"/>
       <c r="S15" s="18" t="n"/>
       <c r="T15" s="18" t="n"/>
       <c r="U15" s="15" t="n">
-        <v>1.106</v>
+        <v>1.648</v>
       </c>
       <c r="V15" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!M15),ISNUMBER(M15)),'RTX 3090'!M15/M15,"pending")</f>
+        <f>IF(AND(ISNUMBER('RTX 3090'!L15),ISNUMBER(L15)),'RTX 3090'!L15/L15,"pending")</f>
         <v/>
       </c>
       <c r="W15" s="15" t="n"/>
       <c r="X15" s="15" t="n"/>
-      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="Y15" s="5" t="inlineStr">
+        <is>
+          <t>Median GPU span of the 1693 graph replays with copies in the nsys traces. The CSR graph is uploaded from pinned memory in 8 chunks overlapped with the first iteration. A separate uninstrumented run of the binary (profiles/bench-20261015-091815.txt): 5.714 ms with transfers, 2.651 ms compute only.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny anomaly</t>
+          <t>pagerank (GAPBS)</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Whole application (H2D + kernels + D2H)</t>
+          <t>Whole application, small shape (launch-bound)</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>64M elements</t>
+          <t>2^14 vertices, 16 edges/vertex, 20 iterations</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -3137,49 +3747,37 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
+          <t>Batch and single iteration (cudaEvent)</t>
         </is>
       </c>
       <c r="F16" s="16" t="n"/>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>pending (direct mode not profiled yet)</t>
+          <t>pending (time_all.sh not run yet)</t>
         </is>
       </c>
       <c r="H16" s="16" t="n"/>
       <c r="I16" s="16" t="n"/>
       <c r="J16" s="16" t="n"/>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="K16" s="17" t="n"/>
+      <c r="L16" s="9" t="inlineStr">
         <is>
           <t>pending (time_all.sh not run yet)</t>
         </is>
       </c>
-      <c r="L16" s="10" t="n">
-        <v>13698.465</v>
-      </c>
-      <c r="M16" s="9" t="inlineStr">
-        <is>
-          <t>pending (time_all.sh not run yet)</t>
-        </is>
-      </c>
+      <c r="M16" s="17" t="n"/>
       <c r="N16" s="17" t="n"/>
-      <c r="O16" s="11" t="inlineStr">
-        <is>
-          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
-        </is>
-      </c>
+      <c r="O16" s="17" t="n"/>
       <c r="P16" s="18" t="n"/>
       <c r="Q16" s="12" t="inlineStr">
         <is>
-          <t>pending (agentic optimized not profiled yet)</t>
+          <t>pending (time_all.sh not run yet)</t>
         </is>
       </c>
       <c r="R16" s="18" t="n"/>
       <c r="S16" s="18" t="n"/>
       <c r="T16" s="18" t="n"/>
-      <c r="U16" s="15" t="n">
-        <v>1.003</v>
-      </c>
+      <c r="U16" s="15" t="n"/>
       <c r="V16" s="15">
         <f>IF(AND(ISNUMBER('RTX 3090'!L16),ISNUMBER(L16)),'RTX 3090'!L16/L16,"pending")</f>
         <v/>
@@ -3188,24 +3786,24 @@
       <c r="X16" s="15" t="n"/>
       <c r="Y16" s="5" t="inlineStr">
         <is>
-          <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The same PageRank run on a 2^14-vertex graph (make -C pagerank small): upload, 20 iterations of a few microseconds each, download.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny KWS</t>
+          <t>mlperf-tiny anomaly</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>kws_postprocess_kernel</t>
+          <t>mse_partial_kernel</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>12 classes x 4M rows</t>
+          <t>64M elements</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -3253,7 +3851,7 @@
       <c r="N18" s="17" t="n"/>
       <c r="O18" s="11" t="inlineStr">
         <is>
-          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
       <c r="P18" s="12" t="inlineStr">
@@ -3274,7 +3872,7 @@
       <c r="S18" s="18" t="n"/>
       <c r="T18" s="18" t="n"/>
       <c r="U18" s="15" t="n">
-        <v>2.325</v>
+        <v>1.106</v>
       </c>
       <c r="V18" s="15">
         <f>IF(AND(ISNUMBER('RTX 3090'!M18),ISNUMBER(M18)),'RTX 3090'!M18/M18,"pending")</f>
@@ -3282,16 +3880,12 @@
       </c>
       <c r="W18" s="15" t="n"/>
       <c r="X18" s="15" t="n"/>
-      <c r="Y18" s="5" t="inlineStr">
-        <is>
-          <t>Only kernel in the application.</t>
-        </is>
-      </c>
+      <c r="Y18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny KWS</t>
+          <t>mlperf-tiny anomaly</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3301,7 +3895,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>12 classes x 4M rows</t>
+          <t>64M elements</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -3329,7 +3923,7 @@
         </is>
       </c>
       <c r="L19" s="10" t="n">
-        <v>11226.082</v>
+        <v>13698.465</v>
       </c>
       <c r="M19" s="9" t="inlineStr">
         <is>
@@ -3339,7 +3933,7 @@
       <c r="N19" s="17" t="n"/>
       <c r="O19" s="11" t="inlineStr">
         <is>
-          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+          <t>nsys-anomaly_mse-20261015-091800.sqlite</t>
         </is>
       </c>
       <c r="P19" s="18" t="n"/>
@@ -3352,7 +3946,7 @@
       <c r="S19" s="18" t="n"/>
       <c r="T19" s="18" t="n"/>
       <c r="U19" s="15" t="n">
-        <v>1.059</v>
+        <v>1.003</v>
       </c>
       <c r="V19" s="15">
         <f>IF(AND(ISNUMBER('RTX 3090'!L19),ISNUMBER(L19)),'RTX 3090'!L19/L19,"pending")</f>
@@ -3366,116 +3960,86 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>mlperf-tiny VWW</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>vww_preprocess_kernel</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>256M bytes</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny anomaly</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>16 elements (smoke)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>RTX 4090 (sm_89, 24 GB)</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Kernel time (ncu, one launch)</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H21" s="6" t="inlineStr">
-        <is>
-          <t>pending (direct mode not profiled yet)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="n"/>
-      <c r="J21" s="16" t="n"/>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L21" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="9" t="inlineStr">
-        <is>
-          <t>pending (ncu not run yet)</t>
-        </is>
-      </c>
-      <c r="N21" s="17" t="n"/>
-      <c r="O21" s="11" t="inlineStr">
-        <is>
-          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
-        </is>
-      </c>
-      <c r="P21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R21" s="12" t="inlineStr">
-        <is>
-          <t>pending (agentic optimized not profiled yet)</t>
-        </is>
-      </c>
-      <c r="S21" s="18" t="n"/>
-      <c r="T21" s="18" t="n"/>
-      <c r="U21" s="15" t="n">
-        <v>1.106</v>
-      </c>
-      <c r="V21" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!M21),ISNUMBER(M21)),'RTX 3090'!M21/M21,"pending")</f>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="n"/>
+      <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
+      <c r="K20" s="17" t="n"/>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="M20" s="17" t="n"/>
+      <c r="N20" s="17" t="n"/>
+      <c r="O20" s="17" t="n"/>
+      <c r="P20" s="18" t="n"/>
+      <c r="Q20" s="12" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="R20" s="18" t="n"/>
+      <c r="S20" s="18" t="n"/>
+      <c r="T20" s="18" t="n"/>
+      <c r="U20" s="15" t="n"/>
+      <c r="V20" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L20),ISNUMBER(L20)),'RTX 3090'!L20/L20,"pending")</f>
         <v/>
       </c>
-      <c r="W21" s="15" t="n"/>
-      <c r="X21" s="15" t="n"/>
-      <c r="Y21" s="5" t="inlineStr">
-        <is>
-          <t>Only kernel in the application.</t>
+      <c r="W20" s="15" t="n"/>
+      <c r="X20" s="15" t="n"/>
+      <c r="Y20" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>mlperf-tiny VWW</t>
+          <t>mlperf-tiny KWS</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Whole application (H2D + kernels + D2H)</t>
+          <t>kws_postprocess_kernel</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>256M bytes</t>
+          <t>12 classes x 4M rows</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -3485,91 +4049,493 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Iteration time (nsys)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="n"/>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
           <t>pending (direct mode not profiled yet)</t>
         </is>
       </c>
-      <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="n"/>
       <c r="J22" s="16" t="n"/>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>pending (time_all.sh not run yet)</t>
-        </is>
-      </c>
-      <c r="L22" s="10" t="n">
-        <v>21789.123</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="M22" s="9" t="inlineStr">
         <is>
-          <t>pending (time_all.sh not run yet)</t>
+          <t>pending (ncu not run yet)</t>
         </is>
       </c>
       <c r="N22" s="17" t="n"/>
       <c r="O22" s="11" t="inlineStr">
         <is>
-          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
-        </is>
-      </c>
-      <c r="P22" s="18" t="n"/>
+          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+        </is>
+      </c>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="Q22" s="12" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R22" s="12" t="inlineStr">
+        <is>
           <t>pending (agentic optimized not profiled yet)</t>
         </is>
       </c>
-      <c r="R22" s="18" t="n"/>
       <c r="S22" s="18" t="n"/>
       <c r="T22" s="18" t="n"/>
       <c r="U22" s="15" t="n">
-        <v>1.003</v>
+        <v>2.325</v>
       </c>
       <c r="V22" s="15">
-        <f>IF(AND(ISNUMBER('RTX 3090'!L22),ISNUMBER(L22)),'RTX 3090'!L22/L22,"pending")</f>
+        <f>IF(AND(ISNUMBER('RTX 3090'!M22),ISNUMBER(M22)),'RTX 3090'!M22/M22,"pending")</f>
         <v/>
       </c>
       <c r="W22" s="15" t="n"/>
       <c r="X22" s="15" t="n"/>
       <c r="Y22" s="5" t="inlineStr">
         <is>
+          <t>Only kernel in the application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 4M rows</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Iteration time (nsys)</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H23" s="16" t="n"/>
+      <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="n">
+        <v>11226.082</v>
+      </c>
+      <c r="M23" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N23" s="17" t="n"/>
+      <c r="O23" s="11" t="inlineStr">
+        <is>
+          <t>nsys-kws_postprocess-20261015-091805.sqlite</t>
+        </is>
+      </c>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="18" t="n"/>
+      <c r="T23" s="18" t="n"/>
+      <c r="U23" s="15" t="n">
+        <v>1.059</v>
+      </c>
+      <c r="V23" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L23),ISNUMBER(L23)),'RTX 3090'!L23/L23,"pending")</f>
+        <v/>
+      </c>
+      <c r="W23" s="15" t="n"/>
+      <c r="X23" s="15" t="n"/>
+      <c r="Y23" s="5" t="inlineStr">
+        <is>
           <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny KWS</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>12 classes x 1 row (smoke)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="H24" s="16" t="n"/>
+      <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
+      <c r="K24" s="17" t="n"/>
+      <c r="L24" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="M24" s="17" t="n"/>
+      <c r="N24" s="17" t="n"/>
+      <c r="O24" s="17" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="12" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="R24" s="18" t="n"/>
+      <c r="S24" s="18" t="n"/>
+      <c r="T24" s="18" t="n"/>
+      <c r="U24" s="15" t="n"/>
+      <c r="V24" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L24),ISNUMBER(L24)),'RTX 3090'!L24/L24,"pending")</f>
+        <v/>
+      </c>
+      <c r="W24" s="15" t="n"/>
+      <c r="X24" s="15" t="n"/>
+      <c r="Y24" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>vww_preprocess_kernel</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Kernel time (ncu, one launch)</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="n"/>
+      <c r="K26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L26" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="inlineStr">
+        <is>
+          <t>pending (ncu not run yet)</t>
+        </is>
+      </c>
+      <c r="N26" s="17" t="n"/>
+      <c r="O26" s="11" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
+        </is>
+      </c>
+      <c r="P26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q26" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="R26" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="S26" s="18" t="n"/>
+      <c r="T26" s="18" t="n"/>
+      <c r="U26" s="15" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="V26" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!M26),ISNUMBER(M26)),'RTX 3090'!M26/M26,"pending")</f>
+        <v/>
+      </c>
+      <c r="W26" s="15" t="n"/>
+      <c r="X26" s="15" t="n"/>
+      <c r="Y26" s="5" t="inlineStr">
+        <is>
+          <t>Only kernel in the application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Whole application (H2D + kernels + D2H)</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>256M bytes</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>Iteration time (nsys)</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>pending (direct mode not profiled yet)</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="n"/>
+      <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n"/>
+      <c r="K27" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="n">
+        <v>21789.123</v>
+      </c>
+      <c r="M27" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="N27" s="17" t="n"/>
+      <c r="O27" s="11" t="inlineStr">
+        <is>
+          <t>nsys-vww_preprocess-20261015-091810.sqlite</t>
+        </is>
+      </c>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="12" t="inlineStr">
+        <is>
+          <t>pending (agentic optimized not profiled yet)</t>
+        </is>
+      </c>
+      <c r="R27" s="18" t="n"/>
+      <c r="S27" s="18" t="n"/>
+      <c r="T27" s="18" t="n"/>
+      <c r="U27" s="15" t="n">
+        <v>1.003</v>
+      </c>
+      <c r="V27" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L27),ISNUMBER(L27)),'RTX 3090'!L27/L27,"pending")</f>
+        <v/>
+      </c>
+      <c r="W27" s="15" t="n"/>
+      <c r="X27" s="15" t="n"/>
+      <c r="Y27" s="5" t="inlineStr">
+        <is>
+          <t>Median GPU span of the 41 graph replays with copies in the nsys traces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>mlperf-tiny VWW</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Whole application, small shape (launch-bound)</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>16 bytes (smoke)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>RTX 4090 (sm_89, 24 GB)</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Batch and single iteration (cudaEvent)</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="n"/>
+      <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
+      <c r="K28" s="17" t="n"/>
+      <c r="L28" s="9" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="M28" s="17" t="n"/>
+      <c r="N28" s="17" t="n"/>
+      <c r="O28" s="17" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="12" t="inlineStr">
+        <is>
+          <t>pending (time_all.sh not run yet)</t>
+        </is>
+      </c>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="18" t="n"/>
+      <c r="T28" s="18" t="n"/>
+      <c r="U28" s="15" t="n"/>
+      <c r="V28" s="15">
+        <f>IF(AND(ISNUMBER('RTX 3090'!L28),ISNUMBER(L28)),'RTX 3090'!L28/L28,"pending")</f>
+        <v/>
+      </c>
+      <c r="W28" s="15" t="n"/>
+      <c r="X28" s="15" t="n"/>
+      <c r="Y28" s="5" t="inlineStr">
+        <is>
+          <t>Small shape, so launch cost dominates: compare the Graph speedup and Single / batch columns with the large-shape row above. A Single / batch below 1x means back-to-back iterations run slower than one alone, i.e. the batch is limited by how fast the host enqueues iterations rather than by the GPU. The smoke size on random inputs, including the H2D and D2H copies of a few bytes each.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>How the predicted speedup is calculated (hover a Predicted value for that row's reason)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="20" t="inlineStr">
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>The predicted speedup uses only the RTX 3090's ncu reports and the two GPUs' published specs (RTX 3090: 82 SMs, 1.695 GHz boost, 19.5 Gbps GDDR6X; RTX 4090: 128 SMs, 2.52 GHz boost, 21 Gbps GDDR6X; both 384-bit, PCIe 4.0 x16), so it is fixed before any 4090 measurement. Each unit's peak scales by its hardware ratio: SM compute by SMs x SM clock, L1/L2 cache throughput assumed to scale the same way, DRAM by memory data rate (the 3090's own SM and memory clocks come from its ncu report: 1.69 GHz and 18.98 Gbps, so the ratios are about 2.32x and 1.11x).</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="20" t="inlineStr">
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Kernel rows: ncu gives each launch's SM, memory (L1/L2) and DRAM throughput as a percent of the 3090's peak. Keeping the work per unit fixed, a unit at u% that is r times faster needs u/r% of the old time, and the slowest unit sets the new time: speedup = max(u) / max(u / r). So a DRAM-bound kernel gets ~1.11x and a compute- or cache-bound one ~2.32x. A launch below 60% on every unit is latency-bound and gets the SM clock ratio (1.49x). A kernel with several launches combines them weighted by time.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="20" t="inlineStr">
+    <row r="33" ht="48" customHeight="1">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Whole-application rows: the kernels in that workload's ncu report (one run of the application) scale by their predicted speedups; the rest of the 3090 time (H2D/D2H copies over the same PCIe 4.0 link, launch gaps) is assumed unchanged. Where the kernels overlap (llama2c's three streams; their summed time exceeds the iteration time), the whole time scales with the kernels.</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="20" t="inlineStr">
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Not modelled: cache capacity (the 4090's L2 is 72 MB vs 6 MB, so data that spilled to DRAM on the 3090 can stay in L2), kernels overlapping copies (pagerank's first iteration), clocks above rated boost, and compiler differences (CUDA 13.3 vs 12.5). Measured = 3090 time / 4090 time for the CUDA Graph column; kernel rows read pending until the 4090 ncu reports exist.</t>
         </is>
@@ -3578,18 +4544,18 @@
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="W4:X4"/>
-    <mergeCell ref="A25:Y25"/>
     <mergeCell ref="A2:Y2"/>
     <mergeCell ref="P4:T4"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A28:Y28"/>
+    <mergeCell ref="A33:Y33"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A32:Y32"/>
     <mergeCell ref="E4:E5"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="Y4:Y5"/>
-    <mergeCell ref="A27:Y27"/>
-    <mergeCell ref="A26:Y26"/>
+    <mergeCell ref="A31:Y31"/>
+    <mergeCell ref="A34:Y34"/>
     <mergeCell ref="K4:O4"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="U4:V4"/>
@@ -3601,21 +4567,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J7" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O9" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O12" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O21" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O10" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O11" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O14" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O15" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O18" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O19" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O22" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O23" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O26" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="O27" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
